--- a/quizzes/peinture-17e-niveau3.xlsx
+++ b/quizzes/peinture-17e-niveau3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A65D32FE-9ECB-45CF-9923-F963C1BE2D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371C2F2F-C433-4B80-8558-56AA96A1E421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -175,9 +175,6 @@
     <t>Les Amours des dieux (plafond de la galerie Farnèse)</t>
   </si>
   <si>
-    <t>Anthony van Dyck</t>
-  </si>
-  <si>
     <t>1635</t>
   </si>
   <si>
@@ -364,12 +361,6 @@
     <t>Staatliches Museum, Schwerin</t>
   </si>
   <si>
-    <t>Le Sentinelle</t>
-  </si>
-  <si>
-    <t>Charles Le Brun</t>
-  </si>
-  <si>
     <t>1660-1661</t>
   </si>
   <si>
@@ -430,9 +421,6 @@
     <t>Paysage avec Narcisse et Écho</t>
   </si>
   <si>
-    <t>David Teniers le Jeune</t>
-  </si>
-  <si>
     <t>1642</t>
   </si>
   <si>
@@ -511,9 +499,6 @@
     <t>La Sibylle de Cumes</t>
   </si>
   <si>
-    <t>Eustache Le Sueur</t>
-  </si>
-  <si>
     <t>1652-1655</t>
   </si>
   <si>
@@ -1174,9 +1159,6 @@
     <t>Le Temps vaincu par l'Amour, l'Espérance et la Beauté</t>
   </si>
   <si>
-    <t>Willem Claesz. Heda</t>
-  </si>
-  <si>
     <t>Nature morte avec coupe dorée</t>
   </si>
   <si>
@@ -1189,9 +1171,6 @@
     <t>Nature morte avec bol chinois</t>
   </si>
   <si>
-    <t>Willem van de Velde le Jeune</t>
-  </si>
-  <si>
     <t>Le Canon de salut</t>
   </si>
   <si>
@@ -1261,9 +1240,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/2/27/Galleria_Farnese.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/ae/Portrait_de_Charles_1er%2C_roi_d%27Angleterre%2C_%C3%A0_la_chasse_-_Antoon_van_Dyck_-_Mus%C3%A9e_du_Louvre_Peintures_INV_1236_%3B_MR_666.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/98/Anthonis_van_Dyck_-_Equestrian_Portrait_of_Charles_I_-_National_Gallery%2C_London.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1276,9 +1252,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/GENTILESCHI_Judith.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/e5/Self-portrait_as_the_Allegory_of_Painting_by_Artemisia_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/04/Susanna_and_the_Elders_%281610%29%2C_Artemisia_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1306,27 +1279,15 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/a/ae/BuenPastorMurillo1660.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/50/Bernardo_Strozzi_-_The_Cook_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b8/Bernardo_Strozzi_-_St_Cecilia_-_WGA21904.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Musée d’art Nelson-Atkins,Kansas City</t>
   </si>
   <si>
     <t>1620-1625</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/7e/Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Musée Pouchkine, Moscou</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/52/Accademia_-_Convito_in_casa_di_Simeone_by_Bernardo_Strozzi_cat777.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Gelerie de l'Académie, Venise</t>
   </si>
   <si>
@@ -1336,9 +1297,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/7/77/0_%27La_Vocation_de_saint_Matthieu%27_de_Le_Caravage_-_fr2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/78/Death_of_the_Virgin-Caravaggio_%281606%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/1/1e/Bacchus_%28by_Michelangelo_Merisi_da_Caravaggio%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -1348,39 +1306,18 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/5/5b/Carel_Fabritius_-_The_Goldfinch_-_605_-_Mauritshuis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d9/FabritiusViewOfDelft.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/07/Carel_Fabritius_-_Self-Portrait_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d5/Schwerin_Schlo%C3%9FAusstellung_Torwache_20240702_Carel-Fabritius_1654_6000px-301dpi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/e/e8/Charles_Le_Brun_-_Les_reines_de_Perse_aux_pieds_d%27Alexandre_dit_aussi_la_tente_de_Darius_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Charles_Le_Brun_-_Pierre_S%C3%A9guier%2C_chancelier_de_France_%281655-1661%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d5/Les_peintures_de_la_galerie_des_Glaces_du_ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/9a/Charles_Le_Brun_-_Louis_XIV_Visiting_the_Gobelins_Factory_-_WGA12552.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/81/Claude_Lorrain_008.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/65/Landscape_with_Narcissus_and_Echo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/0a/David_Teniers_%28II%29_-_Smoker_Leaning_his_Elbow_on_a_Table_-_WGA22080.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -1396,27 +1333,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/3/37/David_Teniers_the_Younger_-_The_Card_Players_1645_Louvre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b1/Las_Meninas%2C_by_Diego_Vel%C3%A1zquez%2C_from_Prado_in_Google_EarthFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/8e/Velazquez-The_Surrender_of_Breda.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/80/Diego_Vel%C3%A1zquez_-_Rokeby_Venus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/7f/Retrato_del_Papa_Inocencio_X._Roma%2C_by_Diego_Vel%C3%A1zquez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/e/e6/Domenichino_-_La_caccia_di_Diana_%28Galleria_Borghese%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/0d/LastCommunion.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/Category:Martyrdom_of_Saint_Agnes_of_Rome_by_Domenichino_(Pinacoteca_Nazionale,_Bologna)#/media/File:Domenico_Zampieri_detto_il_Domenichino,_Martirio_di_Sant'Agnese_(1621-1625)_01.jpg/2</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/8/84/Domenichino_-_The_Cumaean_Sibyl_-_WGA06405.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1444,9 +1366,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/e/ed/Francisco_de_Zurbar%C3%A1n_053.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/File:Chen_Hongshou,_An_Elegant_Gathering.jpg#/media/File:Elegant_Gathering._by_Chen_Hongshou.jpg</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/7/75/Chen_hongshou_selfportrait%2C1635_-_crop.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -1456,18 +1375,6 @@
     <t>1600-1650</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/97/Cavalier_soldier_Hals-1624x.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/63/Frans_Hals_-_Malle_Babbe_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/5d/Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/78/Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/f/f6/Frans_Snyders_-_Fish_Stall_-_WGA21521FXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -1507,27 +1414,12 @@
     <t>Le Marchand de volaille</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/91/La_Tour_Le_Tricheur_Louvre_RF1972-8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/97/0_La_Madeleine_%C3%A0_la_veilleuse_-_Georges_de_La_Tour_-_Louvre_RF_1949-11_%281%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/1f/%22Le_Nouveau-n%C3%A9%22_de_Georges_de_la_Tour_%28Mus%C3%A9e_Jacquemard_Andr%C3%A9%2C_Paris%29_-_Flickr_-_dalbera.png?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/25/Georges_de_La_Tour._St._Joseph%2C_the_Carpenter.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/9f/Gerard_Dou_-_The_Dropsical_Woman_-_WGA06647.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/04/Gerrit_Dou_-_%27The_Young_Mother%27_-_32_-_Mauritshuis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/f/f8/Dou%2C_Gerard_-_Astronomer_by_Candlelight_-_late_1650.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/e/ea/Gerard_Dou_-_Self-Portrait_-_WGA06660FXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -1540,9 +1432,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Gerrit_van_Honthorst_-_Het_Concert.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/95/Adoration_of_the_shepherds%2C_by_Gerard_van_Honthorst.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Musée Wallraf-Richartz, Cologne</t>
   </si>
   <si>
@@ -1567,21 +1456,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/a/a2/Guido_Reni%2C_Atalanta_e_Ippomene%2C_Museo_Capodimonte%2C_Napoli.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/af/Avercamp%2C_Hendrick_-_Winterlandschap_met_schaatsers_-_SK-A-1718.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/14/Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/54/Hendrick_Avercamp_-_The_Pleasures_of_Winter.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/8/81/Hishikawa_Moronobu_-_Beauty_Looking_Back_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/8c/Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Musée des Beaux Arts, Boston</t>
   </si>
   <si>
@@ -1597,12 +1474,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/f/fe/Full_portrait_of_Marie_Anne_de_Bourbon_%281666-1739%29%2C_Dowager_Princess_of_Conti_as_depicted_by_Riguad_in_1706.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/8f/Jordaens_King_Drinks_1638-40.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/As_the_Old_Sing%2C_So_the_Young_Pipe%2C_by_Jacob_Jordaens.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Musée des Beaux-Arts, Valenciennes</t>
   </si>
   <si>
@@ -1636,15 +1507,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/8/81/Steen_Doctor_and_His_Patient.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/01/Goyen_1651_View_of_Dordrecht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Musée de Dordrecht</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/File:Goyen_1636_Village_at_the_River.jpg#/media/File:Goyen_1636_Village_at_the_River.jpg/2</t>
-  </si>
-  <si>
     <t>Village au bord de la rivière</t>
   </si>
   <si>
@@ -1657,9 +1522,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/5/5a/Johannes_Vermeer_-_De_melkmeid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/c/c5/Johannes_Vermeer_-_View_of_Delft_-_92_-_Mauritshuis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/5/5e/Jan_Vermeer_-_The_Art_of_Painting_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -1672,12 +1534,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d7/Mujer_barbuda_ribera.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/76/Judith_Leyster_The_Proposition.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg/1920px-Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1720,12 +1576,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/5/52/Mattia_Preti_-_Concert_-_WGA18386.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/62/Meindert_Hobbema_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/af/Meindert_Hobbema_-_The_Water_Mill_-_WGA11437.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/c/c2/The_idle_servant.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1735,9 +1585,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/2/21/Oude_vrouw_in_gebed%2C_bekend_als_%E2%80%98Het_gebed_zonder_end%E2%80%99_Rijksmuseum_SK-C-535.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/L%27Enl%C3%A8vement_des_Sabines_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7290_%3B_MR_2335.jpg/1280px-L%27Enl%C3%A8vement_des_Sabines_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7290_%3B_MR_2335.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1747,18 +1594,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d9/Nicolas_Poussin_078.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/12/Judith_et_sa_servante%2C_par_Orazio_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/2e/Orazio_Gentileschi_-_Dana%C3%AB_-_WGA08578.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/83/Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/1e/Hampton_Court_Palace_Duchess_of_Cumberland_Peter_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Barbara Villiers, duchesse de Cleveland (Les Beautés de Windsor)</t>
   </si>
   <si>
@@ -1774,18 +1609,6 @@
     <t>Portrait de deux dames de la famille Lake</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a4/Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d9/El_Jard%C3%ADn_del_Amor_%28Rubens%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/9c/Rubens%2C_Peter_Paul_-_The_Three_Graces.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/8/82/Le_v%C5%93u_de_Louis_XIII.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1822,9 +1645,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/a/a2/Pieter_de_Hooch_-_At_the_Linen_Closet.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/6e/Ceiling_of_Palazzo_Barberini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d8/Cortona_Rape_of_the_Sabine_Women_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1834,9 +1654,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/The_Nightwatch_by_Rembrandt_-_Rijksmuseum.jpg/3840px-The_Nightwatch_by_Rembrandt_-_Rijksmuseum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/Rembrandt_-_The_Anatomy_Lesson_of_Dr_Nicolaes_Tulp.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/99/Rembrandt_Self-portrait_%28Kenwood%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1876,24 +1693,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/f/fd/Vouet%2C_Simon_-_Father_Time_Overcome_by_Love%2C_Hope_and_Beauty_-_1627.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/e8/Still_Life_with_Gilt_Goblet_1635_Willem_Claesz_Heda.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/4/4a/Heda_hermitage.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Petit-déjeuner avec un crabe</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/4/4a/Heda%2C_Willem_Claeszoon_-_Breakfast_Table_with_Blackberry_Pie_-_WGA.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Table du petit-déjeuner avec tarte aux mûres</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/c/ce/Still_Life_with_Chinese_Bowl_and_Nautilus_1662_Willem_Kalf.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1933,16 +1738,211 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/0/0f/Willem_van_de_Velde_II_-_A_Dutch_Vessel_in_a_Strong_Breeze.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Caravaggio ou Caravage</t>
-  </si>
-  <si>
-    <t>Annibale Carracci ou Carrache</t>
-  </si>
-  <si>
-    <t>Guercino ou Guerchin</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/6e/Van_Dyck_Charles_I_1635.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Self-Portrait_as_the_Allegory_of_Painting_%28La_Pittura%29_-_Artemisia_Gentileschi.jpg/960px-Self-Portrait_as_the_Allegory_of_Painting_%28La_Pittura%29_-_Artemisia_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/87/Bernardo_Strozzi_-_The_Cook_-_WGA21913.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/b8/Bernardo_Strozzi_-_St_Cecilia_-_WGA21904.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg/960px-Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Bernardo_Strozzi_-_Banquet_at_the_House_of_Simon_%28detail%29_-_WGA21902.jpg/1280px-Bernardo_Strozzi_-_Banquet_at_the_House_of_Simon_%28detail%29_-_WGA21902.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/78/Death_of_the_Virgin-Caravaggio_%281606%29.jpg/1920px-Death_of_the_Virgin-Caravaggio_%281606%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d9/FabritiusViewOfDelft.jpg/1280px-FabritiusViewOfDelft.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/07/Carel_Fabritius_-_Self-Portrait_-_Google_Art_Project.jpg/960px-Carel_Fabritius_-_Self-Portrait_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>La Sentinelle</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/2/25/Carel_Fabritius_-_De_poort_bewaker_%281654%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg/1280px-Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg/1280px-Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/53/Elegant_Gathering._by_Chen_Hongshou.jpg/960px-Elegant_Gathering._by_Chen_Hongshou.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/Chateau_Versailles_Galerie_des_Glaces.jpg/1280px-Chateau_Versailles_Galerie_des_Glaces.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/69/Analyasis_of_Las_Meninas.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg/1280px-Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/80/Diego_Vel%C3%A1zquez_-_Rokeby_Venus.jpg/1280px-Diego_Vel%C3%A1zquez_-_Rokeby_Venus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/Diego_Vel%C3%A1zquez%2C_Portrait_du_pape_Innocent_X%2C_1650%2C_huile_sur_toile%2C_140_%C3%97_120_cm%2C_Rome%2C_Galleria_Doria_Pamphilj_%28inv._237%29.jpg/960px-Diego_Vel%C3%A1zquez%2C_Portrait_du_pape_Innocent_X%2C_1650%2C_huile_sur_toile%2C_140_%C3%97_120_cm%2C_Rome%2C_Galleria_Doria_Pamphilj_%28inv._237%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Domenico_Zampieri_detto_il_Domenichino%2C_Martirio_di_Sant%27Agnese_%281621-1625%29_01.jpg/960px-Domenico_Zampieri_detto_il_Domenichino%2C_Martirio_di_Sant%27Agnese_%281621-1625%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Frans_Hals_%E2%80%93_The_Laughing_Cavalier.jpg/960px-Frans_Hals_%E2%80%93_The_Laughing_Cavalier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Malle_Babbe_-_Gem%C3%A4ldegalerie_Berlin_-_5245583.jpg/960px-Malle_Babbe_-_Gem%C3%A4ldegalerie_Berlin_-_5245583.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5d/Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg/1280px-Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/78/Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg/1280px-Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cc/Georges_de_La_Tour_007.jpg/960px-Georges_de_La_Tour_007.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg/1280px-Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3b/Saint_Joseph_Charpentier.jpg/960px-Saint_Joseph_Charpentier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f8/Dou%2C_Gerard_-_Astronomer_by_Candlelight_-_late_1650.jpg/960px-Dou%2C_Gerard_-_Astronomer_by_Candlelight_-_late_1650.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Gerard_van_Honthorst_001.jpg/1280px-Gerard_van_Honthorst_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1f/Hendrick_Avercamp_-_Winterlandschap_met_ijsvermaak.jpg/1280px-Hendrick_Avercamp_-_Winterlandschap_met_ijsvermaak.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg/1280px-Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/54/Hendrick_Avercamp_-_The_Pleasures_of_Winter.jpg/1280px-Hendrick_Avercamp_-_The_Pleasures_of_Winter.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg/1280px-Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/As_the_Old_Sing%2C_So_the_Young_Pipe%2C_by_Jacob_Jordaens.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/bc/Jacob_Jordaens_-_The_Bean_King_%28Louvre%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Goyen_1651_View_of_Dordrecht.jpg/1280px-Goyen_1651_View_of_Dordrecht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/e4/Goyen_1636_Village_at_the_River.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c5/Johannes_Vermeer_-_View_of_Delft_-_92_-_Mauritshuis.jpg/1280px-Johannes_Vermeer_-_View_of_Delft_-_92_-_Mauritshuis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg/1920px-Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/76/Judith_Leyster_The_Proposition.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/Meindert_Hobbema_001.jpg/1280px-Meindert_Hobbema_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg/1280px-Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Judith_et_sa_servante%2C_par_Orazio_Gentileschi.jpg/960px-Judith_et_sa_servante%2C_par_Orazio_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2e/Orazio_Gentileschi_-_Dana%C3%AB_-_WGA08578.jpg/1280px-Orazio_Gentileschi_-_Dana%C3%AB_-_WGA08578.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg/1280px-Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg/960px-Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg/1280px-Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d9/El_Jard%C3%ADn_del_Amor_%28Rubens%29.jpg/1280px-El_Jard%C3%ADn_del_Amor_%28Rubens%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9c/Rubens%2C_Peter_Paul_-_The_Three_Graces.jpg/960px-Rubens%2C_Peter_Paul_-_The_Three_Graces.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6e/Ceiling_of_Palazzo_Barberini.jpg/960px-Ceiling_of_Palazzo_Barberini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Rembrandt_-_The_Anatomy_Lesson_of_Dr_Nicolaes_Tulp.jpg/1280px-Rembrandt_-_The_Anatomy_Lesson_of_Dr_Nicolaes_Tulp.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/26/Stilleven_met_vergulde_bokaal_Rijksmuseum_SK-A-4830.jpeg/1280px-Stilleven_met_vergulde_bokaal_Rijksmuseum_SK-A-4830.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Heda_hermitage.jpg/1280px-Heda_hermitage.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg/1280px-Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png/1280px-Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Antoine van DYCK</t>
+  </si>
+  <si>
+    <t>Annibale CARRACI ou CARRACHE</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO ou CARAVAGE</t>
+  </si>
+  <si>
+    <t>Charles LE BRUN</t>
+  </si>
+  <si>
+    <t>David TENIERS LE JEUNE</t>
+  </si>
+  <si>
+    <t>Eustache LE SUEUR</t>
+  </si>
+  <si>
+    <t>Willem van de VELDE LE JEUNE</t>
+  </si>
+  <si>
+    <t>Willem CLAESZOON HEDA</t>
+  </si>
+  <si>
+    <t>GUERCINO ou GUERCHIN</t>
   </si>
 </sst>
 </file>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>17</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>17</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>17</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -2479,15 +2479,15 @@
         <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -2499,12 +2499,12 @@
         <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>27</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>33</v>
@@ -2530,7 +2530,7 @@
         <v>1650</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>35</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>33</v>
@@ -2564,7 +2564,7 @@
         <v>37</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>38</v>
@@ -2572,10 +2572,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>40</v>
@@ -2589,10 +2589,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>43</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>45</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>48</v>
@@ -2640,622 +2640,622 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>413</v>
+        <v>573</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>632</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>632</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>632</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>418</v>
+        <v>574</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C27" s="4">
         <v>1691</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>428</v>
+        <v>575</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>429</v>
+        <v>576</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>432</v>
+        <v>577</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>434</v>
+        <v>578</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>438</v>
+        <v>579</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="E39" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>442</v>
+        <v>580</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>443</v>
+        <v>581</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="D42" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>444</v>
+        <v>583</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>114</v>
+        <v>582</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>115</v>
+        <v>635</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>447</v>
+        <v>588</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>115</v>
+        <v>635</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>115</v>
+        <v>635</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
-        <v>474</v>
+        <v>587</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C49" s="4">
         <v>1635</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>449</v>
+        <v>584</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>450</v>
+        <v>585</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>452</v>
+        <v>586</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>136</v>
+        <v>636</v>
       </c>
       <c r="C54" s="4">
         <v>1643</v>
@@ -3264,49 +3264,49 @@
         <v>19</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>136</v>
+        <v>636</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>136</v>
+        <v>636</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>39</v>
@@ -3315,66 +3315,66 @@
         <v>19</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>458</v>
+        <v>589</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>459</v>
+        <v>590</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>460</v>
+        <v>591</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>461</v>
+        <v>592</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>28</v>
@@ -3383,134 +3383,134 @@
         <v>41</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="3" t="s">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="D63" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
-        <v>464</v>
+        <v>593</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="3" t="s">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>163</v>
+        <v>637</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="3" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>163</v>
+        <v>637</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
-        <v>467</v>
+        <v>441</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="3" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>163</v>
+        <v>637</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>28</v>
@@ -3519,15 +3519,15 @@
         <v>19</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="3" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>6</v>
@@ -3536,15 +3536,15 @@
         <v>34</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="3" t="s">
-        <v>472</v>
+        <v>446</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>28</v>
@@ -3553,236 +3553,236 @@
         <v>34</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="3" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="3" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
-        <v>478</v>
+        <v>594</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="3" t="s">
-        <v>479</v>
+        <v>595</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="E75" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
-        <v>480</v>
+        <v>596</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="3" t="s">
-        <v>481</v>
+        <v>597</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="3" t="s">
-        <v>482</v>
+        <v>451</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="3" t="s">
-        <v>483</v>
+        <v>452</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>484</v>
+        <v>453</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="3" t="s">
-        <v>485</v>
+        <v>454</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="3" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>487</v>
+        <v>456</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="3" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="3" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="3" t="s">
-        <v>491</v>
+        <v>460</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>492</v>
+        <v>461</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="3" t="s">
-        <v>493</v>
+        <v>462</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C85" s="6">
         <v>1662</v>
@@ -3791,15 +3791,15 @@
         <v>7</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>494</v>
+        <v>463</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="3" t="s">
-        <v>495</v>
+        <v>598</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>12</v>
@@ -3808,66 +3808,66 @@
         <v>19</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="3" t="s">
-        <v>496</v>
+        <v>599</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="3" t="s">
-        <v>497</v>
+        <v>600</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="3" t="s">
-        <v>498</v>
+        <v>601</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="3" t="s">
-        <v>499</v>
+        <v>464</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>20</v>
@@ -3876,457 +3876,457 @@
         <v>19</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="3" t="s">
-        <v>500</v>
+        <v>465</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="3" t="s">
-        <v>501</v>
+        <v>602</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="E92" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="3" t="s">
-        <v>502</v>
+        <v>466</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="3" t="s">
-        <v>503</v>
+        <v>467</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="3" t="s">
-        <v>504</v>
+        <v>468</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="3" t="s">
-        <v>505</v>
+        <v>469</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="3" t="s">
-        <v>506</v>
+        <v>603</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C97" s="2">
+        <v>209</v>
+      </c>
+      <c r="C97" s="4">
         <v>1622</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>507</v>
+        <v>470</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="3" t="s">
-        <v>508</v>
+        <v>471</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="3" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="3" t="s">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="3" t="s">
-        <v>511</v>
+        <v>474</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="3" t="s">
-        <v>512</v>
+        <v>475</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="3" t="s">
-        <v>514</v>
+        <v>477</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="D104" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="3" t="s">
-        <v>515</v>
+        <v>604</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="3" t="s">
-        <v>516</v>
+        <v>605</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="3" t="s">
-        <v>517</v>
+        <v>606</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="3" t="s">
-        <v>518</v>
+        <v>478</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="3" t="s">
-        <v>519</v>
+        <v>607</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>521</v>
+        <v>480</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>520</v>
+        <v>479</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="3" t="s">
-        <v>522</v>
+        <v>481</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="3" t="s">
-        <v>523</v>
+        <v>482</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="3" t="s">
-        <v>524</v>
+        <v>483</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="3" t="s">
-        <v>525</v>
+        <v>609</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="3" t="s">
-        <v>526</v>
+        <v>608</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>527</v>
+        <v>484</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="3" t="s">
-        <v>528</v>
+        <v>485</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="E115" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="3" t="s">
-        <v>529</v>
+        <v>486</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="3" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>30</v>
@@ -4335,49 +4335,49 @@
         <v>7</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="3" t="s">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="3" t="s">
-        <v>532</v>
+        <v>489</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="3" t="s">
-        <v>533</v>
+        <v>490</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C120" s="2">
         <v>1630</v>
@@ -4386,83 +4386,83 @@
         <v>23</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>534</v>
+        <v>491</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="3" t="s">
-        <v>535</v>
+        <v>492</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="3" t="s">
-        <v>536</v>
+        <v>493</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="3" t="s">
-        <v>537</v>
+        <v>494</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="3" t="s">
-        <v>538</v>
+        <v>610</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C124" s="4">
         <v>1651</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>539</v>
+        <v>495</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="3" t="s">
-        <v>540</v>
+        <v>611</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C125" s="4">
         <v>1636</v>
@@ -4471,168 +4471,168 @@
         <v>16</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>541</v>
+        <v>496</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="3" t="s">
-        <v>542</v>
+        <v>497</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C126" s="4">
         <v>1650</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="3" t="s">
-        <v>543</v>
+        <v>498</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="3" t="s">
-        <v>544</v>
+        <v>499</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="3" t="s">
-        <v>545</v>
+        <v>612</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="3" t="s">
-        <v>546</v>
+        <v>500</v>
       </c>
       <c r="B130" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E130" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="3" t="s">
-        <v>547</v>
+        <v>501</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="3" t="s">
-        <v>548</v>
+        <v>502</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="3" t="s">
-        <v>549</v>
+        <v>503</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E133" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="3" t="s">
-        <v>550</v>
+        <v>614</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="3" t="s">
-        <v>551</v>
+        <v>613</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>15</v>
@@ -4641,219 +4641,219 @@
         <v>29</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="3" t="s">
-        <v>552</v>
+        <v>504</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="3" t="s">
-        <v>640</v>
+        <v>572</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C137" s="4">
         <v>1634</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>553</v>
+        <v>505</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="3" t="s">
-        <v>554</v>
+        <v>506</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="3" t="s">
-        <v>555</v>
+        <v>507</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="3" t="s">
-        <v>556</v>
+        <v>508</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="3" t="s">
-        <v>557</v>
+        <v>509</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="3" t="s">
-        <v>558</v>
+        <v>510</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C142" s="4">
         <v>1663</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>559</v>
+        <v>511</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>560</v>
+        <v>512</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="3" t="s">
-        <v>561</v>
+        <v>513</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>562</v>
+        <v>514</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>563</v>
+        <v>515</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="3" t="s">
-        <v>564</v>
+        <v>516</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="3" t="s">
-        <v>565</v>
+        <v>517</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="3" t="s">
-        <v>566</v>
+        <v>615</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="3" t="s">
-        <v>567</v>
+        <v>616</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="3" t="s">
-        <v>568</v>
+        <v>518</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>30</v>
@@ -4862,100 +4862,100 @@
         <v>31</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="3" t="s">
-        <v>569</v>
+        <v>519</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="3" t="s">
-        <v>570</v>
+        <v>520</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="3" t="s">
-        <v>571</v>
+        <v>617</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="3" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="3" t="s">
-        <v>573</v>
+        <v>522</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="3" t="s">
-        <v>574</v>
+        <v>523</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>28</v>
@@ -4964,168 +4964,168 @@
         <v>19</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="3" t="s">
-        <v>575</v>
+        <v>618</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="3" t="s">
-        <v>576</v>
+        <v>619</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="3" t="s">
-        <v>577</v>
+        <v>620</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="3" t="s">
-        <v>578</v>
+        <v>621</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>579</v>
+        <v>524</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="3" t="s">
-        <v>580</v>
+        <v>525</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="3" t="s">
-        <v>581</v>
+        <v>526</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C160" s="4">
         <v>1650</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>582</v>
+        <v>527</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>583</v>
+        <v>528</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="3" t="s">
-        <v>584</v>
+        <v>622</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="3" t="s">
-        <v>585</v>
+        <v>623</v>
       </c>
       <c r="B162" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E162" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="3" t="s">
-        <v>586</v>
+        <v>624</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="3" t="s">
-        <v>587</v>
+        <v>625</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>6</v>
@@ -5134,32 +5134,32 @@
         <v>34</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="3" t="s">
-        <v>588</v>
+        <v>529</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="3" t="s">
-        <v>589</v>
+        <v>530</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>22</v>
@@ -5168,134 +5168,134 @@
         <v>19</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="3" t="s">
-        <v>590</v>
+        <v>531</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="3" t="s">
-        <v>591</v>
+        <v>532</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="3" t="s">
-        <v>592</v>
+        <v>533</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>593</v>
+        <v>534</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="3" t="s">
-        <v>594</v>
+        <v>535</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>595</v>
+        <v>536</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="3" t="s">
-        <v>596</v>
+        <v>537</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="3" t="s">
-        <v>597</v>
+        <v>538</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="3" t="s">
-        <v>598</v>
+        <v>539</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="3" t="s">
-        <v>599</v>
+        <v>540</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>20</v>
@@ -5304,168 +5304,168 @@
         <v>23</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="3" t="s">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="3" t="s">
-        <v>601</v>
+        <v>541</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="3" t="s">
-        <v>602</v>
+        <v>542</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E177" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="3" t="s">
-        <v>603</v>
+        <v>543</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="3" t="s">
-        <v>604</v>
+        <v>627</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="3" t="s">
-        <v>605</v>
+        <v>544</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E180" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="E180" s="2" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="3" t="s">
-        <v>628</v>
+        <v>563</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>629</v>
+        <v>564</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>630</v>
+        <v>565</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="3" t="s">
-        <v>606</v>
+        <v>545</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="3" t="s">
-        <v>626</v>
+        <v>561</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C183" s="2">
+        <v>360</v>
+      </c>
+      <c r="C183" s="4">
         <v>1632</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>627</v>
+        <v>562</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="3" t="s">
-        <v>608</v>
+        <v>547</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C184" s="4">
         <v>1649</v>
@@ -5474,15 +5474,15 @@
         <v>23</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>607</v>
+        <v>546</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="3" t="s">
-        <v>609</v>
+        <v>548</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C185" s="4">
         <v>1650</v>
@@ -5491,83 +5491,83 @@
         <v>19</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>610</v>
+        <v>549</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="3" t="s">
-        <v>611</v>
+        <v>550</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="3" t="s">
-        <v>612</v>
+        <v>551</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="3" t="s">
-        <v>613</v>
+        <v>552</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="3" t="s">
-        <v>614</v>
+        <v>553</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="3" t="s">
-        <v>615</v>
+        <v>554</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>6</v>
@@ -5576,100 +5576,100 @@
         <v>19</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="3" t="s">
-        <v>616</v>
+        <v>555</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="3" t="s">
-        <v>617</v>
+        <v>556</v>
       </c>
       <c r="B192" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C192" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="3" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>384</v>
+        <v>639</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="3" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>384</v>
+        <v>639</v>
       </c>
       <c r="C194" s="4">
         <v>1648</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>620</v>
+        <v>557</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="3" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>384</v>
+        <v>639</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>622</v>
+        <v>558</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="3" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>18</v>
@@ -5678,66 +5678,66 @@
         <v>31</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="3" t="s">
-        <v>624</v>
+        <v>559</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>625</v>
+        <v>560</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="3" t="s">
-        <v>631</v>
+        <v>566</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>389</v>
+        <v>638</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="3" t="s">
-        <v>632</v>
+        <v>567</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>389</v>
+        <v>638</v>
       </c>
       <c r="C199" s="4">
         <v>1655</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>633</v>
+        <v>568</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="3" t="s">
-        <v>634</v>
+        <v>569</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>389</v>
+        <v>638</v>
       </c>
       <c r="C200" s="4">
         <v>1665</v>
@@ -5746,24 +5746,24 @@
         <v>23</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>635</v>
+        <v>570</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="3" t="s">
-        <v>636</v>
+        <v>571</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>389</v>
+        <v>638</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -5784,189 +5784,189 @@
     <hyperlink ref="A15" r:id="rId14" xr:uid="{1A7C0D1A-8696-4142-A459-3A501936D346}"/>
     <hyperlink ref="A16" r:id="rId15" xr:uid="{63A3F731-DF38-41D0-9B74-838F54D7AB05}"/>
     <hyperlink ref="A17" r:id="rId16" xr:uid="{423FD3DE-0113-461A-97E4-49C4E0612BFD}"/>
-    <hyperlink ref="A18" r:id="rId17" display="https://upload.wikimedia.org/wikipedia/commons/a/ae/Portrait_de_Charles_1er%2C_roi_d%27Angleterre%2C_%C3%A0_la_chasse_-_Antoon_van_Dyck_-_Mus%C3%A9e_du_Louvre_Peintures_INV_1236_%3B_MR_666.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original" xr:uid="{B1DA1517-CFBD-43D9-993F-6C9F657DECB4}"/>
-    <hyperlink ref="A19" r:id="rId18" xr:uid="{A9F291AE-CE9E-473E-9CE6-C39E797E2926}"/>
-    <hyperlink ref="A20" r:id="rId19" xr:uid="{82F72AF5-4CC0-4860-BDB2-3730895CB4A2}"/>
-    <hyperlink ref="A21" r:id="rId20" xr:uid="{96ABEC9C-4002-4C16-9491-E90FB150403C}"/>
-    <hyperlink ref="A22" r:id="rId21" xr:uid="{7E0DEBF1-9967-4A4C-8099-60B9DEB5D6A8}"/>
-    <hyperlink ref="A23" r:id="rId22" xr:uid="{3AB7A3E9-12AA-4664-89B7-C6AB610687D5}"/>
-    <hyperlink ref="A24" r:id="rId23" xr:uid="{546CD3A0-4594-432F-814F-E62DAAAC6D34}"/>
-    <hyperlink ref="A25" r:id="rId24" xr:uid="{5AF69EB2-2583-48EE-A7AB-3BD2D4DB8B58}"/>
-    <hyperlink ref="A26" r:id="rId25" xr:uid="{443377B4-B04D-403D-A824-DB13768731AF}"/>
-    <hyperlink ref="A27" r:id="rId26" xr:uid="{D9FD282A-4352-4FF4-AD57-33E255170BD4}"/>
-    <hyperlink ref="A28" r:id="rId27" xr:uid="{96AEEB4F-086F-426E-B93A-2DA57DE54BFE}"/>
-    <hyperlink ref="A29" r:id="rId28" xr:uid="{B1D18D5B-F033-4CBC-8258-80D80B3D6B1A}"/>
-    <hyperlink ref="A30" r:id="rId29" xr:uid="{02BEF0CC-E5B2-4149-A90C-618525707993}"/>
-    <hyperlink ref="A31" r:id="rId30" xr:uid="{083B8D7F-6587-4FB0-9734-1147CCF679AB}"/>
-    <hyperlink ref="A32" r:id="rId31" xr:uid="{2C71B471-4CE8-429D-B25A-38AAD873211F}"/>
-    <hyperlink ref="A33" r:id="rId32" xr:uid="{5AEE1EF7-080A-47B7-9FCE-3553BD3BCF65}"/>
-    <hyperlink ref="A34" r:id="rId33" xr:uid="{4C22E169-BD71-4F09-9B1C-9F051AA14141}"/>
-    <hyperlink ref="A35" r:id="rId34" xr:uid="{356CD76A-2084-47D9-893F-D82E028B3EC4}"/>
-    <hyperlink ref="A36" r:id="rId35" xr:uid="{72C00A77-DE47-4350-ABDF-53A01568DB8C}"/>
-    <hyperlink ref="A37" r:id="rId36" xr:uid="{5AF98135-DD77-4625-8F13-879BBF038995}"/>
-    <hyperlink ref="A38" r:id="rId37" xr:uid="{8D66B7E5-4F81-473E-BAC6-3A133A8BF0A1}"/>
-    <hyperlink ref="A39" r:id="rId38" xr:uid="{5A5B1E69-6425-4E72-AB90-3ACA37CE9C16}"/>
-    <hyperlink ref="A40" r:id="rId39" xr:uid="{410B345F-73DD-447C-9423-97EB3B76E6DA}"/>
-    <hyperlink ref="A41" r:id="rId40" xr:uid="{250EFD8F-8E6C-48A3-80C2-4DA26FED43F5}"/>
-    <hyperlink ref="A42" r:id="rId41" xr:uid="{9287664B-6C7D-4BAD-9E07-1FD23F25EAD2}"/>
-    <hyperlink ref="A43" r:id="rId42" xr:uid="{2DDEADD1-1E13-47DB-90BB-E14E146F7D98}"/>
-    <hyperlink ref="A44" r:id="rId43" xr:uid="{D0A7CACE-A9DB-4898-88D4-4742CDAAC4E9}"/>
-    <hyperlink ref="A45" r:id="rId44" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
-    <hyperlink ref="A46" r:id="rId45" xr:uid="{9EC41CFB-6431-4458-9FB6-22282256C21C}"/>
-    <hyperlink ref="A47" r:id="rId46" xr:uid="{CBE9F467-FD86-4B4E-8B2C-A0DF71E3A3F7}"/>
-    <hyperlink ref="A50" r:id="rId47" display="https://upload.wikimedia.org/wikipedia/commons/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{EF1DEDB6-C815-4BDA-9879-3384057FFBDB}"/>
-    <hyperlink ref="A51" r:id="rId48" xr:uid="{1E42B7B4-9FE3-4396-AAAE-F17E96D91C2F}"/>
-    <hyperlink ref="A53" r:id="rId49" xr:uid="{13BB11A7-8B20-43FA-947B-6BB2E06251B8}"/>
-    <hyperlink ref="A52" r:id="rId50" xr:uid="{DF0AE9F4-B328-43BE-980A-041FF11FCDE5}"/>
-    <hyperlink ref="A54" r:id="rId51" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
-    <hyperlink ref="A55" r:id="rId52" xr:uid="{6036570F-FE5D-4357-98FB-FB0599A85710}"/>
-    <hyperlink ref="A56" r:id="rId53" xr:uid="{C0B1A606-83CA-4C03-83D2-E5F3AF629E02}"/>
-    <hyperlink ref="A57" r:id="rId54" xr:uid="{BA75ACE4-BC4D-49C9-B96A-E5BAE7B87F58}"/>
-    <hyperlink ref="A58" r:id="rId55" xr:uid="{E295B8A2-C5BB-45D7-9AA7-E002F85E21B1}"/>
-    <hyperlink ref="A59" r:id="rId56" xr:uid="{2FB12C4A-C046-4F6A-9A28-6F41C8634666}"/>
-    <hyperlink ref="A60" r:id="rId57" xr:uid="{CC04E872-F305-4047-8084-F7B987C08A04}"/>
-    <hyperlink ref="A61" r:id="rId58" xr:uid="{E4A75F7B-D88F-486B-A53C-DCC7D5520580}"/>
-    <hyperlink ref="A62" r:id="rId59" xr:uid="{05771483-93F6-4474-B4B2-32295BDD81BC}"/>
-    <hyperlink ref="A63" r:id="rId60" xr:uid="{8D289CD3-5A64-44EF-9B11-57A8D86F52B2}"/>
-    <hyperlink ref="A64" r:id="rId61" location="/media/File:Domenico_Zampieri_detto_il_Domenichino,_Martirio_di_Sant'Agnese_(1621-1625)_01.jpg/2" xr:uid="{2C84482D-586A-4589-880B-CED67E69B949}"/>
-    <hyperlink ref="A65" r:id="rId62" xr:uid="{3D29F5EB-74D0-4F8C-873C-CF8696F82267}"/>
-    <hyperlink ref="A66" r:id="rId63" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
-    <hyperlink ref="A68" r:id="rId64" xr:uid="{F12CA809-887E-4065-8BCF-672DEEE659D9}"/>
-    <hyperlink ref="A67" r:id="rId65" xr:uid="{AEA087D1-239A-45A8-B8E2-097CE49E0FA2}"/>
-    <hyperlink ref="A69" r:id="rId66" xr:uid="{E14EDC9B-A66C-4E7F-8F51-FC4AFBB6A5B6}"/>
-    <hyperlink ref="A70" r:id="rId67" xr:uid="{40958558-46AF-4CE2-B242-1552F7202DDD}"/>
-    <hyperlink ref="A72" r:id="rId68" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
-    <hyperlink ref="A71" r:id="rId69" xr:uid="{418161AA-1108-438A-A40F-FEEBCEEA59A7}"/>
-    <hyperlink ref="A73" r:id="rId70" xr:uid="{41401B15-DF59-4BCD-B69D-632B9BC768D9}"/>
-    <hyperlink ref="A48" r:id="rId71" location="/media/File:Elegant_Gathering._by_Chen_Hongshou.jpg" xr:uid="{5407551E-6A5B-4A57-A006-871F99CE6C8C}"/>
-    <hyperlink ref="A49" r:id="rId72" xr:uid="{410386BC-CF6D-4493-8184-0403996A2394}"/>
-    <hyperlink ref="A74" r:id="rId73" xr:uid="{5B67177B-3566-448C-82E8-B3E47FC7E769}"/>
-    <hyperlink ref="A75" r:id="rId74" xr:uid="{55CF4348-C10A-485D-83F8-C0C64E997A50}"/>
-    <hyperlink ref="A76" r:id="rId75" xr:uid="{DC8DBFA5-20A8-4931-B503-11332AC1CB27}"/>
-    <hyperlink ref="A77" r:id="rId76" xr:uid="{222BFEB5-F162-497C-B31A-A629B7124A08}"/>
-    <hyperlink ref="A78" r:id="rId77" xr:uid="{08DD652B-0E47-4AEF-AE3B-843EED3B5D37}"/>
-    <hyperlink ref="A79" r:id="rId78" xr:uid="{9A750BC8-C762-4EDF-93CC-4032B3907B5D}"/>
-    <hyperlink ref="A80" r:id="rId79" xr:uid="{A30474FF-37E1-44F6-A97C-56E497ADD848}"/>
-    <hyperlink ref="A81" r:id="rId80" xr:uid="{F49E3730-867C-4DB9-985B-3F8975A1C09A}"/>
-    <hyperlink ref="A82" r:id="rId81" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
-    <hyperlink ref="A83" r:id="rId82" xr:uid="{08D60088-499F-44EC-99C8-8B92DAABE16C}"/>
-    <hyperlink ref="A84" r:id="rId83" xr:uid="{4CFFE30B-35C8-4D31-9C98-C457D41CA94F}"/>
-    <hyperlink ref="A85" r:id="rId84" xr:uid="{78669114-120E-45A5-BE51-0591720645D5}"/>
-    <hyperlink ref="A86" r:id="rId85" xr:uid="{8D4F9315-2578-4A82-A162-B6F8D1439BCA}"/>
-    <hyperlink ref="A87" r:id="rId86" xr:uid="{3F1F21A3-1BED-4E8C-A970-5495C5CDC35D}"/>
-    <hyperlink ref="A88" r:id="rId87" xr:uid="{57E19A71-5180-4667-83CC-D00FA996D44A}"/>
-    <hyperlink ref="A89" r:id="rId88" xr:uid="{B6F98EFB-3DDC-4C19-8014-DE9258DDD55F}"/>
-    <hyperlink ref="A90" r:id="rId89" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
-    <hyperlink ref="A91" r:id="rId90" xr:uid="{3411B753-8C89-4443-907B-D69B16883A6C}"/>
-    <hyperlink ref="A92" r:id="rId91" xr:uid="{44E93E43-AAEC-45E4-9B52-16F66EC4C75A}"/>
-    <hyperlink ref="A93" r:id="rId92" xr:uid="{F985F01B-0DAF-4F36-913E-468DDCCF0CAE}"/>
-    <hyperlink ref="A94" r:id="rId93" xr:uid="{74A7EC9A-D21C-4ECC-949D-FCC02E532D40}"/>
-    <hyperlink ref="A95" r:id="rId94" xr:uid="{4D57808A-EF9C-4AA9-BA44-1512D9D61C6C}"/>
-    <hyperlink ref="A96" r:id="rId95" xr:uid="{15EB3C0C-34FA-4F74-85F1-9B11B80679A1}"/>
-    <hyperlink ref="A97" r:id="rId96" xr:uid="{3A6769A7-F323-4DD3-8C2D-087715115AFF}"/>
-    <hyperlink ref="A98" r:id="rId97" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
-    <hyperlink ref="A99" r:id="rId98" xr:uid="{C494AD1B-E0CA-4F10-84B5-455B27655F83}"/>
-    <hyperlink ref="A100" r:id="rId99" xr:uid="{63F9BC15-635D-4D78-8C4C-A018738BAD9F}"/>
-    <hyperlink ref="A101" r:id="rId100" xr:uid="{7CA35FBE-ACB3-446B-B5C5-CAB02BA12633}"/>
-    <hyperlink ref="A102" r:id="rId101" xr:uid="{7E575697-1670-41B2-BC75-9872FD034F04}"/>
-    <hyperlink ref="A103" r:id="rId102" xr:uid="{AEE3E4E0-6220-49B0-BC8E-1FBD267EA3F0}"/>
-    <hyperlink ref="A104" r:id="rId103" xr:uid="{81770296-8553-4FA3-9953-4DF2380B6A02}"/>
-    <hyperlink ref="A105" r:id="rId104" xr:uid="{C56A21A7-BA62-4ADB-A8E1-875A3978D465}"/>
-    <hyperlink ref="A106" r:id="rId105" xr:uid="{2918E51F-E0FF-4A78-BCD9-DAB0B11DF8F3}"/>
-    <hyperlink ref="A107" r:id="rId106" xr:uid="{1C18FD23-B116-474C-9DE8-8369BCCEA128}"/>
-    <hyperlink ref="A108" r:id="rId107" xr:uid="{E9D4827D-694A-41D2-9587-D78CF34633D6}"/>
-    <hyperlink ref="A109" r:id="rId108" xr:uid="{EEC08419-F100-4CE1-89FA-85F419FD4289}"/>
-    <hyperlink ref="A110" r:id="rId109" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
-    <hyperlink ref="A111" r:id="rId110" xr:uid="{74963DD6-10C1-4409-BE27-A8DE50EA1647}"/>
-    <hyperlink ref="A112" r:id="rId111" xr:uid="{EDFC0569-A0F2-4981-8582-AC4EA5959270}"/>
-    <hyperlink ref="A113" r:id="rId112" xr:uid="{39A0F762-D90E-4572-9DEC-9EA918318ACF}"/>
-    <hyperlink ref="A114" r:id="rId113" xr:uid="{2B644338-E4B1-44CF-BEB3-A13E62B9DDA8}"/>
-    <hyperlink ref="A115" r:id="rId114" xr:uid="{257F90C9-10B4-47A9-AD8D-DA20E8A51DF1}"/>
-    <hyperlink ref="A116" r:id="rId115" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
-    <hyperlink ref="A117" r:id="rId116" xr:uid="{C170162D-4ABB-46ED-8E71-615D33E57AF5}"/>
-    <hyperlink ref="A118" r:id="rId117" xr:uid="{DC0BB354-B413-4027-8A80-8DCA353DFAAB}"/>
-    <hyperlink ref="A119" r:id="rId118" xr:uid="{F55798B2-2CE8-4A25-815E-90D86322A818}"/>
-    <hyperlink ref="A120" r:id="rId119" xr:uid="{1D5BD7CB-5D55-40D2-8180-0DC2168D4975}"/>
-    <hyperlink ref="A121" r:id="rId120" xr:uid="{F95E6437-8FC2-4E97-BB2A-3A078AEE787C}"/>
-    <hyperlink ref="A122" r:id="rId121" xr:uid="{75E3C088-0BD1-4C69-9E56-F32A00846E6D}"/>
-    <hyperlink ref="A123" r:id="rId122" xr:uid="{D8022634-90FC-40D5-B726-72063260437B}"/>
-    <hyperlink ref="A124" r:id="rId123" xr:uid="{360DE5AA-3E6B-4B70-92A1-E33A17D256DC}"/>
-    <hyperlink ref="A125" r:id="rId124" location="/media/File:Goyen_1636_Village_at_the_River.jpg/2" xr:uid="{90320534-E6B0-47FA-8517-C5996A4DD903}"/>
-    <hyperlink ref="A126" r:id="rId125" xr:uid="{1CA26EC6-4D0B-478A-AB7C-73C492B901B7}"/>
-    <hyperlink ref="A127" r:id="rId126" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
-    <hyperlink ref="A128" r:id="rId127" xr:uid="{FDEB65E8-E3C9-4173-A3A5-699B556167FB}"/>
-    <hyperlink ref="A129" r:id="rId128" xr:uid="{10D51050-49FA-4334-891C-7BB191F9AAC3}"/>
-    <hyperlink ref="A130" r:id="rId129" xr:uid="{E9FF7778-8F2C-473D-94E5-F797AA522FF4}"/>
-    <hyperlink ref="A131" r:id="rId130" xr:uid="{3BE0486C-7F43-481A-86BD-951F21E28A4C}"/>
-    <hyperlink ref="A132" r:id="rId131" xr:uid="{652988B1-F9B3-4052-9579-F36110769952}"/>
-    <hyperlink ref="A133" r:id="rId132" xr:uid="{9EDF33BD-D7E0-466D-992C-D9A55F7FCB22}"/>
-    <hyperlink ref="A134" r:id="rId133" xr:uid="{61962E7C-EF1D-40BD-ACA7-CA6F3B609C6F}"/>
-    <hyperlink ref="A135" r:id="rId134" xr:uid="{8B20EDCD-1325-45F5-8F5D-A7C167C88195}"/>
-    <hyperlink ref="A136" r:id="rId135" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg/1920px-Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{20D16125-BA3E-4740-8460-267B893FB822}"/>
-    <hyperlink ref="A138" r:id="rId136" xr:uid="{C2924DD1-C68C-444A-A0E3-59C8E373AD89}"/>
-    <hyperlink ref="A139" r:id="rId137" xr:uid="{65345FEB-0D91-4161-877B-BA82E8036012}"/>
-    <hyperlink ref="A140" r:id="rId138" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a5/%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg/1920px-%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F15F6E3C-73ED-4C57-8C55-43394AFB2AB2}"/>
-    <hyperlink ref="A141" r:id="rId139" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/La_Famille_heureuse_-_Fr%C3%A8res_Le_Nain_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1941_20.jpg/1280px-La_Famille_heureuse_-_Fr%C3%A8res_Le_Nain_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1941_20.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6FB76A19-EF26-402C-A597-C32FFFCC17C8}"/>
-    <hyperlink ref="A142" r:id="rId140" xr:uid="{75B759AD-4F67-448E-B557-AEA72EFC75A5}"/>
-    <hyperlink ref="A143" r:id="rId141" display="https://upload.wikimedia.org/wikipedia/commons/thumb/d/d2/Firenze_Palazzo_Medici_Riccardi_Interno_Galleria_Soffitto_01.jpg/1280px-Firenze_Palazzo_Medici_Riccardi_Interno_Galleria_Soffitto_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{444BA55E-6438-4CFB-9303-997E4FF662A1}"/>
-    <hyperlink ref="A144" r:id="rId142" xr:uid="{CD9775EB-2654-4C75-971C-D0D4D92F6FFA}"/>
-    <hyperlink ref="A145" r:id="rId143" xr:uid="{7DC05548-CDE3-4C34-86E0-3F27F8867EB5}"/>
-    <hyperlink ref="A146" r:id="rId144" xr:uid="{2BF6D38A-2C06-4EB1-83D9-ADA687CE29F2}"/>
-    <hyperlink ref="A147" r:id="rId145" xr:uid="{C46D2EAA-7267-4320-B38D-412AC06D44BE}"/>
-    <hyperlink ref="A148" r:id="rId146" xr:uid="{5EB8FE73-1B38-4EE8-9F5D-408471533360}"/>
-    <hyperlink ref="A149" r:id="rId147" xr:uid="{CBEC5A31-19D9-4333-8626-A71B2B34FD4A}"/>
-    <hyperlink ref="A150" r:id="rId148" xr:uid="{D252EB3F-6F51-4F15-B589-73117EA8D496}"/>
-    <hyperlink ref="A151" r:id="rId149" xr:uid="{8AB4CB1D-C2C6-41EA-890E-ABACF970DD91}"/>
-    <hyperlink ref="A152" r:id="rId150" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/L%27Enl%C3%A8vement_des_Sabines_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7290_%3B_MR_2335.jpg/1280px-L%27Enl%C3%A8vement_des_Sabines_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7290_%3B_MR_2335.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A19357B7-751B-4941-BF08-3534E28A3DF6}"/>
-    <hyperlink ref="A153" r:id="rId151" xr:uid="{B4520E14-8C23-4E76-8E14-1E3E1A19B85A}"/>
-    <hyperlink ref="A154" r:id="rId152" xr:uid="{7D7AB562-1695-44D3-9302-EB9B70CAA7E3}"/>
-    <hyperlink ref="A155" r:id="rId153" xr:uid="{FB460A1A-07EA-48A8-9D24-E0EB432A0123}"/>
-    <hyperlink ref="A156" r:id="rId154" xr:uid="{973F6B18-7396-4966-92DF-6E5006CB6F3A}"/>
-    <hyperlink ref="A157" r:id="rId155" xr:uid="{C0B358EE-4F82-4CCC-B168-7058D1059E76}"/>
-    <hyperlink ref="A158" r:id="rId156" xr:uid="{5BB0097B-55F4-42A3-92F7-B32B91E9112E}"/>
-    <hyperlink ref="A159" r:id="rId157" xr:uid="{0E932A87-BF91-4D10-9E97-3A276D068D8E}"/>
-    <hyperlink ref="A160" r:id="rId158" xr:uid="{91B168A5-36C9-42BE-9EAB-E976F78F8C7E}"/>
-    <hyperlink ref="A161" r:id="rId159" xr:uid="{01EA9FE3-3B2A-42AC-A1F3-B75B9ACC1DFF}"/>
-    <hyperlink ref="A162" r:id="rId160" xr:uid="{E9733671-1FE2-403D-8095-2BB075D81AA2}"/>
-    <hyperlink ref="A163" r:id="rId161" xr:uid="{6D0A82AE-FDDF-4057-B19A-9BDFDDDF31C2}"/>
-    <hyperlink ref="A164" r:id="rId162" xr:uid="{21971C3D-CABC-46DE-85AD-6B57AB9BD862}"/>
-    <hyperlink ref="A165" r:id="rId163" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
-    <hyperlink ref="A166" r:id="rId164" xr:uid="{D4971BCF-D378-4CCD-80B1-9BCD850F3F00}"/>
-    <hyperlink ref="A167" r:id="rId165" xr:uid="{DEDAFC51-2102-44FE-845E-028590F63B54}"/>
-    <hyperlink ref="A168" r:id="rId166" xr:uid="{D8984F0D-FF89-40E3-AAC2-A91916DF4A3A}"/>
-    <hyperlink ref="A169" r:id="rId167" xr:uid="{148877A9-A1F7-456C-A81C-37672CB63775}"/>
-    <hyperlink ref="A170" r:id="rId168" xr:uid="{336390E0-177C-4949-A051-CB2980A81A7E}"/>
-    <hyperlink ref="A171" r:id="rId169" xr:uid="{DF73CDA4-CEF8-4638-BBC0-C361102BEE04}"/>
-    <hyperlink ref="A172" r:id="rId170" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
-    <hyperlink ref="A173" r:id="rId171" xr:uid="{CBB82F3B-75DE-4B07-BB90-D0FA63126A81}"/>
-    <hyperlink ref="A174" r:id="rId172" xr:uid="{183A9005-718E-4023-B10F-2589B3446C71}"/>
-    <hyperlink ref="A175" r:id="rId173" xr:uid="{E70300CA-0777-4952-90C0-98EF3B6AD5F8}"/>
-    <hyperlink ref="A176" r:id="rId174" xr:uid="{118EEA92-6B38-446A-B361-3D3EC12529C2}"/>
-    <hyperlink ref="A177" r:id="rId175" xr:uid="{0E580CC5-5962-4510-B23D-5DFEA390BBDF}"/>
-    <hyperlink ref="A178" r:id="rId176" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
-    <hyperlink ref="A179" r:id="rId177" xr:uid="{3CACB936-9C90-4545-AEDB-02617B9E40F2}"/>
-    <hyperlink ref="A180" r:id="rId178" xr:uid="{66D1456D-CC97-46B1-88D5-50974D80DFD7}"/>
-    <hyperlink ref="A182" r:id="rId179" xr:uid="{DC7B95D3-2C37-40E4-B9E2-5EDC59BFA338}"/>
-    <hyperlink ref="A184" r:id="rId180" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
-    <hyperlink ref="A185" r:id="rId181" xr:uid="{465F45A3-ED2E-4491-BC71-18B9F45F2764}"/>
-    <hyperlink ref="A186" r:id="rId182" xr:uid="{15CF0BF0-994A-4A35-9671-66A095B35CD8}"/>
-    <hyperlink ref="A187" r:id="rId183" xr:uid="{2C4AA8F5-D564-4836-B8DB-CC33D50B9F4C}"/>
-    <hyperlink ref="A188" r:id="rId184" xr:uid="{B9E7ABC5-B793-4A1A-B2B9-8DE84F6E3979}"/>
-    <hyperlink ref="A189" r:id="rId185" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
-    <hyperlink ref="A190" r:id="rId186" xr:uid="{91E75685-F1D8-4C6B-826E-E52CBE4A3B62}"/>
-    <hyperlink ref="A191" r:id="rId187" xr:uid="{9A72E3BA-EF99-42A4-820F-8F04F17B25E5}"/>
-    <hyperlink ref="A192" r:id="rId188" xr:uid="{D2384007-1315-48D6-A7F8-DF584E5A77D6}"/>
-    <hyperlink ref="A193" r:id="rId189" xr:uid="{272E99F1-3024-4F10-BE75-D7BBEDD80ACD}"/>
-    <hyperlink ref="A194" r:id="rId190" xr:uid="{C89F33BB-64FD-4253-B43C-5790AF81136F}"/>
-    <hyperlink ref="A195" r:id="rId191" xr:uid="{139BB9CE-E7F2-4FDD-9903-1415B2B366A1}"/>
-    <hyperlink ref="A196" r:id="rId192" xr:uid="{869EEE74-EC55-442B-878C-AA7159427BE6}"/>
-    <hyperlink ref="A197" r:id="rId193" xr:uid="{E24536B2-D94D-4265-92FB-5240863341CF}"/>
-    <hyperlink ref="A183" r:id="rId194" xr:uid="{6DD0EC74-3A66-4DDC-B41B-EFFADB8DFD35}"/>
-    <hyperlink ref="A181" r:id="rId195" xr:uid="{70262521-5303-465D-8B9D-47AE4E0F2D2A}"/>
-    <hyperlink ref="A199" r:id="rId196" xr:uid="{A14CE758-CBAB-4381-8BBB-15948337FAD9}"/>
-    <hyperlink ref="A200" r:id="rId197" xr:uid="{19AA5435-A462-4C11-8578-83786F967017}"/>
-    <hyperlink ref="A201" r:id="rId198" xr:uid="{578B1F4E-5D73-4740-AB71-68CB241AAB4D}"/>
-    <hyperlink ref="A137" r:id="rId199" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C4847D49-3E1B-4371-9BC3-FE1B7A707E3C}"/>
+    <hyperlink ref="A19" r:id="rId17" xr:uid="{A9F291AE-CE9E-473E-9CE6-C39E797E2926}"/>
+    <hyperlink ref="A20" r:id="rId18" xr:uid="{82F72AF5-4CC0-4860-BDB2-3730895CB4A2}"/>
+    <hyperlink ref="A21" r:id="rId19" xr:uid="{96ABEC9C-4002-4C16-9491-E90FB150403C}"/>
+    <hyperlink ref="A22" r:id="rId20" xr:uid="{7E0DEBF1-9967-4A4C-8099-60B9DEB5D6A8}"/>
+    <hyperlink ref="A24" r:id="rId21" xr:uid="{546CD3A0-4594-432F-814F-E62DAAAC6D34}"/>
+    <hyperlink ref="A25" r:id="rId22" xr:uid="{5AF69EB2-2583-48EE-A7AB-3BD2D4DB8B58}"/>
+    <hyperlink ref="A26" r:id="rId23" xr:uid="{443377B4-B04D-403D-A824-DB13768731AF}"/>
+    <hyperlink ref="A27" r:id="rId24" xr:uid="{D9FD282A-4352-4FF4-AD57-33E255170BD4}"/>
+    <hyperlink ref="A28" r:id="rId25" xr:uid="{96AEEB4F-086F-426E-B93A-2DA57DE54BFE}"/>
+    <hyperlink ref="A29" r:id="rId26" xr:uid="{B1D18D5B-F033-4CBC-8258-80D80B3D6B1A}"/>
+    <hyperlink ref="A30" r:id="rId27" xr:uid="{02BEF0CC-E5B2-4149-A90C-618525707993}"/>
+    <hyperlink ref="A31" r:id="rId28" xr:uid="{083B8D7F-6587-4FB0-9734-1147CCF679AB}"/>
+    <hyperlink ref="A36" r:id="rId29" xr:uid="{72C00A77-DE47-4350-ABDF-53A01568DB8C}"/>
+    <hyperlink ref="A38" r:id="rId30" xr:uid="{8D66B7E5-4F81-473E-BAC6-3A133A8BF0A1}"/>
+    <hyperlink ref="A39" r:id="rId31" xr:uid="{5A5B1E69-6425-4E72-AB90-3ACA37CE9C16}"/>
+    <hyperlink ref="A44" r:id="rId32" xr:uid="{D0A7CACE-A9DB-4898-88D4-4742CDAAC4E9}"/>
+    <hyperlink ref="A45" r:id="rId33" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
+    <hyperlink ref="A47" r:id="rId34" xr:uid="{CBE9F467-FD86-4B4E-8B2C-A0DF71E3A3F7}"/>
+    <hyperlink ref="A53" r:id="rId35" xr:uid="{13BB11A7-8B20-43FA-947B-6BB2E06251B8}"/>
+    <hyperlink ref="A54" r:id="rId36" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
+    <hyperlink ref="A55" r:id="rId37" xr:uid="{6036570F-FE5D-4357-98FB-FB0599A85710}"/>
+    <hyperlink ref="A56" r:id="rId38" xr:uid="{C0B1A606-83CA-4C03-83D2-E5F3AF629E02}"/>
+    <hyperlink ref="A57" r:id="rId39" xr:uid="{BA75ACE4-BC4D-49C9-B96A-E5BAE7B87F58}"/>
+    <hyperlink ref="A62" r:id="rId40" xr:uid="{05771483-93F6-4474-B4B2-32295BDD81BC}"/>
+    <hyperlink ref="A63" r:id="rId41" xr:uid="{8D289CD3-5A64-44EF-9B11-57A8D86F52B2}"/>
+    <hyperlink ref="A65" r:id="rId42" xr:uid="{3D29F5EB-74D0-4F8C-873C-CF8696F82267}"/>
+    <hyperlink ref="A66" r:id="rId43" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
+    <hyperlink ref="A68" r:id="rId44" xr:uid="{F12CA809-887E-4065-8BCF-672DEEE659D9}"/>
+    <hyperlink ref="A67" r:id="rId45" xr:uid="{AEA087D1-239A-45A8-B8E2-097CE49E0FA2}"/>
+    <hyperlink ref="A69" r:id="rId46" xr:uid="{E14EDC9B-A66C-4E7F-8F51-FC4AFBB6A5B6}"/>
+    <hyperlink ref="A70" r:id="rId47" xr:uid="{40958558-46AF-4CE2-B242-1552F7202DDD}"/>
+    <hyperlink ref="A72" r:id="rId48" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
+    <hyperlink ref="A71" r:id="rId49" xr:uid="{418161AA-1108-438A-A40F-FEEBCEEA59A7}"/>
+    <hyperlink ref="A73" r:id="rId50" xr:uid="{41401B15-DF59-4BCD-B69D-632B9BC768D9}"/>
+    <hyperlink ref="A49" r:id="rId51" xr:uid="{410386BC-CF6D-4493-8184-0403996A2394}"/>
+    <hyperlink ref="A78" r:id="rId52" xr:uid="{08DD652B-0E47-4AEF-AE3B-843EED3B5D37}"/>
+    <hyperlink ref="A79" r:id="rId53" xr:uid="{9A750BC8-C762-4EDF-93CC-4032B3907B5D}"/>
+    <hyperlink ref="A80" r:id="rId54" xr:uid="{A30474FF-37E1-44F6-A97C-56E497ADD848}"/>
+    <hyperlink ref="A81" r:id="rId55" xr:uid="{F49E3730-867C-4DB9-985B-3F8975A1C09A}"/>
+    <hyperlink ref="A82" r:id="rId56" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
+    <hyperlink ref="A83" r:id="rId57" xr:uid="{08D60088-499F-44EC-99C8-8B92DAABE16C}"/>
+    <hyperlink ref="A84" r:id="rId58" xr:uid="{4CFFE30B-35C8-4D31-9C98-C457D41CA94F}"/>
+    <hyperlink ref="A85" r:id="rId59" xr:uid="{78669114-120E-45A5-BE51-0591720645D5}"/>
+    <hyperlink ref="A90" r:id="rId60" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
+    <hyperlink ref="A91" r:id="rId61" xr:uid="{3411B753-8C89-4443-907B-D69B16883A6C}"/>
+    <hyperlink ref="A93" r:id="rId62" xr:uid="{F985F01B-0DAF-4F36-913E-468DDCCF0CAE}"/>
+    <hyperlink ref="A94" r:id="rId63" xr:uid="{74A7EC9A-D21C-4ECC-949D-FCC02E532D40}"/>
+    <hyperlink ref="A95" r:id="rId64" xr:uid="{4D57808A-EF9C-4AA9-BA44-1512D9D61C6C}"/>
+    <hyperlink ref="A96" r:id="rId65" xr:uid="{15EB3C0C-34FA-4F74-85F1-9B11B80679A1}"/>
+    <hyperlink ref="A98" r:id="rId66" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
+    <hyperlink ref="A99" r:id="rId67" xr:uid="{C494AD1B-E0CA-4F10-84B5-455B27655F83}"/>
+    <hyperlink ref="A100" r:id="rId68" xr:uid="{63F9BC15-635D-4D78-8C4C-A018738BAD9F}"/>
+    <hyperlink ref="A101" r:id="rId69" xr:uid="{7CA35FBE-ACB3-446B-B5C5-CAB02BA12633}"/>
+    <hyperlink ref="A102" r:id="rId70" xr:uid="{7E575697-1670-41B2-BC75-9872FD034F04}"/>
+    <hyperlink ref="A103" r:id="rId71" xr:uid="{AEE3E4E0-6220-49B0-BC8E-1FBD267EA3F0}"/>
+    <hyperlink ref="A104" r:id="rId72" xr:uid="{81770296-8553-4FA3-9953-4DF2380B6A02}"/>
+    <hyperlink ref="A108" r:id="rId73" xr:uid="{E9D4827D-694A-41D2-9587-D78CF34633D6}"/>
+    <hyperlink ref="A110" r:id="rId74" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
+    <hyperlink ref="A111" r:id="rId75" xr:uid="{74963DD6-10C1-4409-BE27-A8DE50EA1647}"/>
+    <hyperlink ref="A112" r:id="rId76" xr:uid="{EDFC0569-A0F2-4981-8582-AC4EA5959270}"/>
+    <hyperlink ref="A115" r:id="rId77" xr:uid="{257F90C9-10B4-47A9-AD8D-DA20E8A51DF1}"/>
+    <hyperlink ref="A116" r:id="rId78" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
+    <hyperlink ref="A117" r:id="rId79" xr:uid="{C170162D-4ABB-46ED-8E71-615D33E57AF5}"/>
+    <hyperlink ref="A118" r:id="rId80" xr:uid="{DC0BB354-B413-4027-8A80-8DCA353DFAAB}"/>
+    <hyperlink ref="A119" r:id="rId81" xr:uid="{F55798B2-2CE8-4A25-815E-90D86322A818}"/>
+    <hyperlink ref="A120" r:id="rId82" xr:uid="{1D5BD7CB-5D55-40D2-8180-0DC2168D4975}"/>
+    <hyperlink ref="A121" r:id="rId83" xr:uid="{F95E6437-8FC2-4E97-BB2A-3A078AEE787C}"/>
+    <hyperlink ref="A122" r:id="rId84" xr:uid="{75E3C088-0BD1-4C69-9E56-F32A00846E6D}"/>
+    <hyperlink ref="A123" r:id="rId85" xr:uid="{D8022634-90FC-40D5-B726-72063260437B}"/>
+    <hyperlink ref="A126" r:id="rId86" xr:uid="{1CA26EC6-4D0B-478A-AB7C-73C492B901B7}"/>
+    <hyperlink ref="A127" r:id="rId87" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
+    <hyperlink ref="A128" r:id="rId88" xr:uid="{FDEB65E8-E3C9-4173-A3A5-699B556167FB}"/>
+    <hyperlink ref="A130" r:id="rId89" xr:uid="{E9FF7778-8F2C-473D-94E5-F797AA522FF4}"/>
+    <hyperlink ref="A131" r:id="rId90" xr:uid="{3BE0486C-7F43-481A-86BD-951F21E28A4C}"/>
+    <hyperlink ref="A132" r:id="rId91" xr:uid="{652988B1-F9B3-4052-9579-F36110769952}"/>
+    <hyperlink ref="A133" r:id="rId92" xr:uid="{9EDF33BD-D7E0-466D-992C-D9A55F7FCB22}"/>
+    <hyperlink ref="A138" r:id="rId93" xr:uid="{C2924DD1-C68C-444A-A0E3-59C8E373AD89}"/>
+    <hyperlink ref="A139" r:id="rId94" xr:uid="{65345FEB-0D91-4161-877B-BA82E8036012}"/>
+    <hyperlink ref="A140" r:id="rId95" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a5/%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg/1920px-%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F15F6E3C-73ED-4C57-8C55-43394AFB2AB2}"/>
+    <hyperlink ref="A141" r:id="rId96" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/La_Famille_heureuse_-_Fr%C3%A8res_Le_Nain_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1941_20.jpg/1280px-La_Famille_heureuse_-_Fr%C3%A8res_Le_Nain_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1941_20.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6FB76A19-EF26-402C-A597-C32FFFCC17C8}"/>
+    <hyperlink ref="A142" r:id="rId97" xr:uid="{75B759AD-4F67-448E-B557-AEA72EFC75A5}"/>
+    <hyperlink ref="A143" r:id="rId98" display="https://upload.wikimedia.org/wikipedia/commons/thumb/d/d2/Firenze_Palazzo_Medici_Riccardi_Interno_Galleria_Soffitto_01.jpg/1280px-Firenze_Palazzo_Medici_Riccardi_Interno_Galleria_Soffitto_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{444BA55E-6438-4CFB-9303-997E4FF662A1}"/>
+    <hyperlink ref="A144" r:id="rId99" xr:uid="{CD9775EB-2654-4C75-971C-D0D4D92F6FFA}"/>
+    <hyperlink ref="A145" r:id="rId100" xr:uid="{7DC05548-CDE3-4C34-86E0-3F27F8867EB5}"/>
+    <hyperlink ref="A148" r:id="rId101" xr:uid="{5EB8FE73-1B38-4EE8-9F5D-408471533360}"/>
+    <hyperlink ref="A149" r:id="rId102" xr:uid="{CBEC5A31-19D9-4333-8626-A71B2B34FD4A}"/>
+    <hyperlink ref="A150" r:id="rId103" xr:uid="{D252EB3F-6F51-4F15-B589-73117EA8D496}"/>
+    <hyperlink ref="A152" r:id="rId104" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/L%27Enl%C3%A8vement_des_Sabines_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7290_%3B_MR_2335.jpg/1280px-L%27Enl%C3%A8vement_des_Sabines_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7290_%3B_MR_2335.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A19357B7-751B-4941-BF08-3534E28A3DF6}"/>
+    <hyperlink ref="A153" r:id="rId105" xr:uid="{B4520E14-8C23-4E76-8E14-1E3E1A19B85A}"/>
+    <hyperlink ref="A154" r:id="rId106" xr:uid="{7D7AB562-1695-44D3-9302-EB9B70CAA7E3}"/>
+    <hyperlink ref="A159" r:id="rId107" xr:uid="{0E932A87-BF91-4D10-9E97-3A276D068D8E}"/>
+    <hyperlink ref="A160" r:id="rId108" xr:uid="{91B168A5-36C9-42BE-9EAB-E976F78F8C7E}"/>
+    <hyperlink ref="A165" r:id="rId109" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
+    <hyperlink ref="A166" r:id="rId110" xr:uid="{D4971BCF-D378-4CCD-80B1-9BCD850F3F00}"/>
+    <hyperlink ref="A167" r:id="rId111" xr:uid="{DEDAFC51-2102-44FE-845E-028590F63B54}"/>
+    <hyperlink ref="A168" r:id="rId112" xr:uid="{D8984F0D-FF89-40E3-AAC2-A91916DF4A3A}"/>
+    <hyperlink ref="A169" r:id="rId113" xr:uid="{148877A9-A1F7-456C-A81C-37672CB63775}"/>
+    <hyperlink ref="A170" r:id="rId114" xr:uid="{336390E0-177C-4949-A051-CB2980A81A7E}"/>
+    <hyperlink ref="A171" r:id="rId115" xr:uid="{DF73CDA4-CEF8-4638-BBC0-C361102BEE04}"/>
+    <hyperlink ref="A172" r:id="rId116" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
+    <hyperlink ref="A173" r:id="rId117" xr:uid="{CBB82F3B-75DE-4B07-BB90-D0FA63126A81}"/>
+    <hyperlink ref="A174" r:id="rId118" xr:uid="{183A9005-718E-4023-B10F-2589B3446C71}"/>
+    <hyperlink ref="A176" r:id="rId119" xr:uid="{118EEA92-6B38-446A-B361-3D3EC12529C2}"/>
+    <hyperlink ref="A177" r:id="rId120" xr:uid="{0E580CC5-5962-4510-B23D-5DFEA390BBDF}"/>
+    <hyperlink ref="A178" r:id="rId121" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
+    <hyperlink ref="A180" r:id="rId122" xr:uid="{66D1456D-CC97-46B1-88D5-50974D80DFD7}"/>
+    <hyperlink ref="A182" r:id="rId123" xr:uid="{DC7B95D3-2C37-40E4-B9E2-5EDC59BFA338}"/>
+    <hyperlink ref="A184" r:id="rId124" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
+    <hyperlink ref="A185" r:id="rId125" xr:uid="{465F45A3-ED2E-4491-BC71-18B9F45F2764}"/>
+    <hyperlink ref="A186" r:id="rId126" xr:uid="{15CF0BF0-994A-4A35-9671-66A095B35CD8}"/>
+    <hyperlink ref="A187" r:id="rId127" xr:uid="{2C4AA8F5-D564-4836-B8DB-CC33D50B9F4C}"/>
+    <hyperlink ref="A188" r:id="rId128" xr:uid="{B9E7ABC5-B793-4A1A-B2B9-8DE84F6E3979}"/>
+    <hyperlink ref="A189" r:id="rId129" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
+    <hyperlink ref="A190" r:id="rId130" xr:uid="{91E75685-F1D8-4C6B-826E-E52CBE4A3B62}"/>
+    <hyperlink ref="A191" r:id="rId131" xr:uid="{9A72E3BA-EF99-42A4-820F-8F04F17B25E5}"/>
+    <hyperlink ref="A192" r:id="rId132" xr:uid="{D2384007-1315-48D6-A7F8-DF584E5A77D6}"/>
+    <hyperlink ref="A197" r:id="rId133" xr:uid="{E24536B2-D94D-4265-92FB-5240863341CF}"/>
+    <hyperlink ref="A183" r:id="rId134" xr:uid="{6DD0EC74-3A66-4DDC-B41B-EFFADB8DFD35}"/>
+    <hyperlink ref="A181" r:id="rId135" xr:uid="{70262521-5303-465D-8B9D-47AE4E0F2D2A}"/>
+    <hyperlink ref="A199" r:id="rId136" xr:uid="{A14CE758-CBAB-4381-8BBB-15948337FAD9}"/>
+    <hyperlink ref="A200" r:id="rId137" xr:uid="{19AA5435-A462-4C11-8578-83786F967017}"/>
+    <hyperlink ref="A201" r:id="rId138" xr:uid="{578B1F4E-5D73-4740-AB71-68CB241AAB4D}"/>
+    <hyperlink ref="A137" r:id="rId139" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C4847D49-3E1B-4371-9BC3-FE1B7A707E3C}"/>
+    <hyperlink ref="A18" r:id="rId140" xr:uid="{945251CC-E6AD-4661-9571-02B7C81C2515}"/>
+    <hyperlink ref="A23" r:id="rId141" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Self-Portrait_as_the_Allegory_of_Painting_%28La_Pittura%29_-_Artemisia_Gentileschi.jpg/960px-Self-Portrait_as_the_Allegory_of_Painting_%28La_Pittura%29_-_Artemisia_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{450912E8-6C20-4F26-8538-8282F02EDAD8}"/>
+    <hyperlink ref="A32" r:id="rId142" xr:uid="{AE09BF63-612F-4029-93B7-0FFC6478EC80}"/>
+    <hyperlink ref="A33" r:id="rId143" xr:uid="{6AD1CDA5-519C-44A7-AB4B-917CF44D65A8}"/>
+    <hyperlink ref="A34" r:id="rId144" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg/960px-Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C2850ED-78A6-4C59-BCF7-C65C3396179F}"/>
+    <hyperlink ref="A35" r:id="rId145" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Bernardo_Strozzi_-_Banquet_at_the_House_of_Simon_%28detail%29_-_WGA21902.jpg/1280px-Bernardo_Strozzi_-_Banquet_at_the_House_of_Simon_%28detail%29_-_WGA21902.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0D8B2BF6-D494-4AD9-80B6-152EDA1BE1C7}"/>
+    <hyperlink ref="A37" r:id="rId146" xr:uid="{1ED06375-42E6-4B79-A731-BA5599550BCB}"/>
+    <hyperlink ref="A40" r:id="rId147" xr:uid="{A4E016D8-8E8B-4277-888D-5A265E16A6CA}"/>
+    <hyperlink ref="A41" r:id="rId148" xr:uid="{413F4FD9-A1E7-43F4-8861-E70D31398644}"/>
+    <hyperlink ref="A42" r:id="rId149" xr:uid="{1009E53D-045D-4F7C-9946-780F3CE87428}"/>
+    <hyperlink ref="A43" r:id="rId150" xr:uid="{7EA200AC-EB1E-4D87-9C6E-2F83CFE486B9}"/>
+    <hyperlink ref="A50" r:id="rId151" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{596E240E-7D53-4A32-9D33-569DA93A4937}"/>
+    <hyperlink ref="A51" r:id="rId152" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg/1280px-Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EBCA20AC-1D38-4222-AB4E-BF68B3C90D3C}"/>
+    <hyperlink ref="A52" r:id="rId153" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg/1280px-Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06244E1C-7B67-4593-BB56-4DEE3423A1BB}"/>
+    <hyperlink ref="A48" r:id="rId154" xr:uid="{92BA32AF-8EC9-4665-A5CC-676E19F93BB1}"/>
+    <hyperlink ref="A46" r:id="rId155" xr:uid="{4C18F5D5-E2D3-4F40-B1CB-F3145EB601CB}"/>
+    <hyperlink ref="A58" r:id="rId156" xr:uid="{EF15C00B-27CF-44B6-8670-F310C1BB94A2}"/>
+    <hyperlink ref="A59" r:id="rId157" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg/1280px-Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57BDA7C2-2097-4285-8501-5706AF6C54CB}"/>
+    <hyperlink ref="A60" r:id="rId158" xr:uid="{96F3CC4F-FB51-40C8-88EA-2F121A7073B1}"/>
+    <hyperlink ref="A61" r:id="rId159" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/Diego_Vel%C3%A1zquez%2C_Portrait_du_pape_Innocent_X%2C_1650%2C_huile_sur_toile%2C_140_%C3%97_120_cm%2C_Rome%2C_Galleria_Doria_Pamphilj_%28inv._237%29.jpg/960px-Diego_Vel%C3%A1zquez%2C_Portrait_du_pape_Innocent_X%2C_1650%2C_huile_sur_toile%2C_140_%C3%97_120_cm%2C_Rome%2C_Galleria_Doria_Pamphilj_%28inv._237%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D87623A4-196A-43C4-9B3B-F42FDF54C823}"/>
+    <hyperlink ref="A64" r:id="rId160" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Domenico_Zampieri_detto_il_Domenichino%2C_Martirio_di_Sant%27Agnese_%281621-1625%29_01.jpg/960px-Domenico_Zampieri_detto_il_Domenichino%2C_Martirio_di_Sant%27Agnese_%281621-1625%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C8B9AC2D-28FD-4FDE-B0A2-F9C7118A3B16}"/>
+    <hyperlink ref="A74" r:id="rId161" xr:uid="{59CEEA06-FA81-4ACE-8191-838FE9BA1BF7}"/>
+    <hyperlink ref="A75" r:id="rId162" xr:uid="{E503067F-9D64-47B3-A4A0-CEB2FFACDB43}"/>
+    <hyperlink ref="A76" r:id="rId163" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5d/Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg/1280px-Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{136AAD34-4CD7-44CB-A4E6-E14EBBA741CE}"/>
+    <hyperlink ref="A77" r:id="rId164" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/78/Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg/1280px-Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{81540B48-5B00-42DD-9EF5-412A04667459}"/>
+    <hyperlink ref="A86" r:id="rId165" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{78A42547-C969-4BBC-BDEF-3E15484B20A9}"/>
+    <hyperlink ref="A87" r:id="rId166" xr:uid="{4B07A603-5273-44D0-B268-760021F85005}"/>
+    <hyperlink ref="A88" r:id="rId167" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg/1280px-Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{10E006E8-2443-4060-9149-E3123D594459}"/>
+    <hyperlink ref="A89" r:id="rId168" xr:uid="{143D80C2-5A99-482A-8173-C372796357EC}"/>
+    <hyperlink ref="A92" r:id="rId169" xr:uid="{302BFBD5-CCBC-44D9-B9D7-53DC45FF1E20}"/>
+    <hyperlink ref="A97" r:id="rId170" xr:uid="{D3C667FB-F60A-40F5-835F-58D418AEEBF0}"/>
+    <hyperlink ref="A105" r:id="rId171" xr:uid="{3028B9B6-1977-4385-A1C6-3FAEC26A346D}"/>
+    <hyperlink ref="A106" r:id="rId172" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg/1280px-Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21DB9486-01EC-4E16-BB8D-ECC0905220A1}"/>
+    <hyperlink ref="A107" r:id="rId173" xr:uid="{61A0E5BE-362D-4770-80F3-3DD9B7FF9694}"/>
+    <hyperlink ref="A109" r:id="rId174" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg/1280px-Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D04BBB03-3D9D-453F-8CD9-245E66F3AD32}"/>
+    <hyperlink ref="A114" r:id="rId175" xr:uid="{2A8DF019-5FC0-46BB-8113-2075AEF0CCED}"/>
+    <hyperlink ref="A113" r:id="rId176" xr:uid="{975264BA-C514-413E-99EA-DD14D58AB288}"/>
+    <hyperlink ref="A124" r:id="rId177" xr:uid="{86A34B4C-C537-4D76-A3EA-321DD50D8CB1}"/>
+    <hyperlink ref="A125" r:id="rId178" xr:uid="{90266FA6-15A2-46AC-8C7B-FCBCC44F01FA}"/>
+    <hyperlink ref="A129" r:id="rId179" xr:uid="{072FFDC6-2747-4BB4-BC37-0C70594E6F4D}"/>
+    <hyperlink ref="A135" r:id="rId180" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg/1920px-Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8BC641E9-9E78-406C-9A28-319E9127B01C}"/>
+    <hyperlink ref="A134" r:id="rId181" xr:uid="{C594B535-2481-40E5-9C7D-7ED4B45F7645}"/>
+    <hyperlink ref="A136" r:id="rId182" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg/1920px-Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DB908BC3-2D48-410E-BEFE-4CCB04FD6CB4}"/>
+    <hyperlink ref="A146" r:id="rId183" xr:uid="{97D61BE1-3395-44FA-A95B-2E1DF5026D4F}"/>
+    <hyperlink ref="A147" r:id="rId184" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg/1280px-Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9552E73C-3D36-4755-AB33-97007CDF5358}"/>
+    <hyperlink ref="A151" r:id="rId185" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06C35A77-A512-486F-96AF-3B12DCA46F8F}"/>
+    <hyperlink ref="A155" r:id="rId186" xr:uid="{42CCE4FE-9359-4905-8FA6-E951073D0EBF}"/>
+    <hyperlink ref="A156" r:id="rId187" xr:uid="{FE18FAC0-7CE1-4001-986D-644A0C94D4EE}"/>
+    <hyperlink ref="A157" r:id="rId188" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg/1280px-Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{717F9D1A-B3AE-4DEC-AE52-C308AAEBC665}"/>
+    <hyperlink ref="A158" r:id="rId189" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg/960px-Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6D642F82-38C2-4D7F-BE14-5866750B76EA}"/>
+    <hyperlink ref="A161" r:id="rId190" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{0DEC1873-EA8A-4837-A600-314F517B37B3}"/>
+    <hyperlink ref="A162" r:id="rId191" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg/1280px-Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{975F1E1C-791A-4C4E-BECF-5701732F6721}"/>
+    <hyperlink ref="A163" r:id="rId192" xr:uid="{AC4529FF-6236-4187-A38E-F96F4FA87989}"/>
+    <hyperlink ref="A164" r:id="rId193" xr:uid="{6F236C01-0CD5-413D-AAF1-D13121442DC4}"/>
+    <hyperlink ref="A175" r:id="rId194" xr:uid="{5FE70125-FB71-4033-91A5-592708E66E93}"/>
+    <hyperlink ref="A179" r:id="rId195" xr:uid="{1C87A638-94E8-40B9-A0F1-C41FE40A0E7B}"/>
+    <hyperlink ref="A193" r:id="rId196" xr:uid="{66F5C3AC-AC1A-4F70-99C0-35B4342E87D9}"/>
+    <hyperlink ref="A194" r:id="rId197" xr:uid="{DBF9950D-25AB-4896-9E4E-6E334EF854EB}"/>
+    <hyperlink ref="A195" r:id="rId198" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg/1280px-Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0E287FD2-4B38-4DE9-96FA-D2FE3EE0C624}"/>
+    <hyperlink ref="A196" r:id="rId199" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png/1280px-Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A8A2E502-8764-42A6-825B-73739FCA7F0A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-17e-niveau3.xlsx
+++ b/quizzes/peinture-17e-niveau3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371C2F2F-C433-4B80-8558-56AA96A1E421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3A52F6-AAC7-4D91-8A2C-D080DAC1D289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="639">
   <si>
     <t>image</t>
   </si>
@@ -307,9 +307,6 @@
     <t>Le Concert</t>
   </si>
   <si>
-    <t>1599-1600</t>
-  </si>
-  <si>
     <t>Église Saint-Louis-des-Français, Rome</t>
   </si>
   <si>
@@ -322,15 +319,6 @@
     <t>La Mort de la Vierge</t>
   </si>
   <si>
-    <t>1596-1597</t>
-  </si>
-  <si>
-    <t>Bacchus</t>
-  </si>
-  <si>
-    <t>1599</t>
-  </si>
-  <si>
     <t>Galleria Nazionale d'Arte Antica, Rome</t>
   </si>
   <si>
@@ -1297,12 +1285,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/7/77/0_%27La_Vocation_de_saint_Matthieu%27_de_Le_Caravage_-_fr2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/1e/Bacchus_%28by_Michelangelo_Merisi_da_Caravaggio%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/78/Judith_Beheading_Holofernes_-_Caravaggio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/5/5b/Carel_Fabritius_-_The_Goldfinch_-_605_-_Mauritshuis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -1943,6 +1925,18 @@
   </si>
   <si>
     <t>GUERCINO ou GUERCHIN</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f6/David_with_the_Head_of_Goliath-Caravaggio_%281610%29.jpg/960px-David_with_the_Head_of_Goliath-Caravaggio_%281610%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>David avec la tête de Goliath</t>
+  </si>
+  <si>
+    <t>Le Souper à Emmaüs</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c0/Supper_at_Emmaus-Caravaggio_%281601%29.jpg/1280px-Supper_at_Emmaus-Caravaggio_%281601%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -1976,7 +1970,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1993,8 +1987,14 @@
         <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2017,12 +2017,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2031,11 +2053,17 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2368,7 +2396,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -2385,7 +2413,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -2402,7 +2430,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2419,7 +2447,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>17</v>
@@ -2436,7 +2464,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>17</v>
@@ -2453,7 +2481,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>17</v>
@@ -2470,7 +2498,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -2479,15 +2507,15 @@
         <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -2499,12 +2527,12 @@
         <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>27</v>
@@ -2521,7 +2549,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>33</v>
@@ -2530,7 +2558,7 @@
         <v>1650</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>35</v>
@@ -2538,7 +2566,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
@@ -2555,7 +2583,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>33</v>
@@ -2564,7 +2592,7 @@
         <v>37</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>38</v>
@@ -2572,10 +2600,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>40</v>
@@ -2589,10 +2617,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>43</v>
@@ -2606,10 +2634,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>45</v>
@@ -2623,10 +2651,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>48</v>
@@ -2639,28 +2667,28 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="A18" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="7" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>53</v>
@@ -2674,10 +2702,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>55</v>
@@ -2691,10 +2719,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>58</v>
@@ -2708,7 +2736,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>61</v>
@@ -2723,26 +2751,26 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="1:5" s="8" customFormat="1">
+      <c r="A23" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>61</v>
@@ -2759,7 +2787,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>61</v>
@@ -2776,7 +2804,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>73</v>
@@ -2793,7 +2821,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>73</v>
@@ -2802,7 +2830,7 @@
         <v>1691</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>78</v>
@@ -2810,7 +2838,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>79</v>
@@ -2827,7 +2855,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>79</v>
@@ -2844,7 +2872,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>79</v>
@@ -2861,7 +2889,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>79</v>
@@ -2876,386 +2904,386 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="1:5" s="8" customFormat="1">
+      <c r="A32" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="1:5" s="8" customFormat="1">
+      <c r="A33" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D33" s="5" t="s">
+      <c r="C33" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="8" customFormat="1">
+      <c r="A34" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="8" customFormat="1">
+      <c r="A35" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>419</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="C36" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1600</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E36" s="2" t="s">
+    </row>
+    <row r="37" spans="1:5" s="8" customFormat="1">
+      <c r="A37" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>425</v>
+        <v>635</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>100</v>
+        <v>628</v>
+      </c>
+      <c r="C38" s="4">
+        <v>1610</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>101</v>
+        <v>636</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>426</v>
+        <v>638</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="C39" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1601</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" s="8" customFormat="1">
+      <c r="A40" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E40" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="B40" s="2" t="s">
+    </row>
+    <row r="41" spans="1:5" s="8" customFormat="1">
+      <c r="A41" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D41" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D40" s="2" t="s">
+    </row>
+    <row r="42" spans="1:5" s="8" customFormat="1">
+      <c r="A42" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E42" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C41" s="2" t="s">
+    <row r="43" spans="1:5" s="8" customFormat="1">
+      <c r="A43" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>582</v>
+      <c r="E43" s="7" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E45" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" s="12" customFormat="1">
+      <c r="A46" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" s="11" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C46" s="2" t="s">
+    <row r="48" spans="1:5" s="8" customFormat="1">
+      <c r="A48" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E46" s="2" t="s">
+      <c r="C48" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E48" s="7" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C49" s="4">
         <v>1635</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="B50" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="8" customFormat="1">
+      <c r="A50" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" s="8" customFormat="1">
+      <c r="A51" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C50" s="2" t="s">
+    </row>
+    <row r="52" spans="1:5" s="8" customFormat="1">
+      <c r="A52" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D52" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E52" s="7" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C51" s="2" t="s">
+    <row r="53" spans="1:5" s="8" customFormat="1">
+      <c r="A53" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D53" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E53" s="7" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C54" s="4">
         <v>1643</v>
@@ -3264,49 +3292,49 @@
         <v>19</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>39</v>
@@ -3315,202 +3343,202 @@
         <v>19</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" s="8" customFormat="1">
+      <c r="A58" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" s="8" customFormat="1">
+      <c r="A59" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="B58" s="2" t="s">
+      <c r="D59" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E59" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C58" s="2" t="s">
+    </row>
+    <row r="60" spans="1:5" s="8" customFormat="1">
+      <c r="A60" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="D60" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C59" s="2" t="s">
+    <row r="61" spans="1:5" s="8" customFormat="1">
+      <c r="A61" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="3" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="D63" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="3" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="3" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="3" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>28</v>
@@ -3519,15 +3547,15 @@
         <v>19</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="3" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>6</v>
@@ -3536,15 +3564,15 @@
         <v>34</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="3" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>28</v>
@@ -3553,253 +3581,253 @@
         <v>34</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="3" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="3" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="3" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="D75" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="3" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>457</v>
-      </c>
       <c r="D78" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="3" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="3" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="3" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="3" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="3" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="3" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="3" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C85" s="6">
+        <v>185</v>
+      </c>
+      <c r="C85" s="5">
         <v>1662</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="3" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>12</v>
@@ -3808,66 +3836,66 @@
         <v>19</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="3" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="3" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="E88" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="3" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="3" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>20</v>
@@ -3876,103 +3904,103 @@
         <v>19</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="3" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="3" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="D92" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="3" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="3" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>19</v>
@@ -3983,64 +4011,64 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="3" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C97" s="4">
         <v>1622</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="3" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>34</v>
@@ -4051,282 +4079,282 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="3" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="3" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="3" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="3" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="3" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="3" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="3" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="3" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="D111" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="3" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="3" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="3" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="3" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="3" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>30</v>
@@ -4335,49 +4363,49 @@
         <v>7</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="3" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="3" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C120" s="2">
         <v>1630</v>
@@ -4386,49 +4414,49 @@
         <v>23</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="3" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="3" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B122" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="3" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>86</v>
@@ -4437,32 +4465,32 @@
         <v>23</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="3" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C124" s="4">
         <v>1651</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="3" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C125" s="4">
         <v>1636</v>
@@ -4471,168 +4499,168 @@
         <v>16</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="3" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C126" s="4">
         <v>1650</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="3" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="3" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="3" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="3" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B130" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>283</v>
-      </c>
       <c r="D130" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="3" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="3" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D133" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>289</v>
-      </c>
       <c r="E133" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="3" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="3" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>15</v>
@@ -4641,171 +4669,171 @@
         <v>29</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="3" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="3" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C137" s="4">
         <v>1634</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="3" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="3" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="3" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="3" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="3" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C142" s="4">
         <v>1663</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="3" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="3" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>31</v>
@@ -4816,44 +4844,44 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="3" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="3" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>30</v>
@@ -4862,66 +4890,66 @@
         <v>31</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="3" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="B149" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="3" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="3" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="3" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>53</v>
@@ -4930,32 +4958,32 @@
         <v>10</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="3" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="3" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>28</v>
@@ -4964,21 +4992,21 @@
         <v>19</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="3" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>72</v>
@@ -4986,61 +5014,61 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="3" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>75</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="3" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>325</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="3" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="3" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>28</v>
@@ -5049,83 +5077,83 @@
         <v>56</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="3" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C160" s="4">
         <v>1650</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="3" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="3" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B162" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C162" s="2" t="s">
-        <v>335</v>
-      </c>
       <c r="D162" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="3" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="3" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>6</v>
@@ -5134,32 +5162,32 @@
         <v>34</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="3" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>22</v>
@@ -5168,15 +5196,15 @@
         <v>19</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="3" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>58</v>
@@ -5185,117 +5213,117 @@
         <v>31</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="3" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="3" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="3" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="3" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="3" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="3" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="3" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>20</v>
@@ -5304,151 +5332,151 @@
         <v>23</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="3" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="3" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="3" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="3" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="3" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="3" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D180" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="C180" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>364</v>
-      </c>
       <c r="E180" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="3" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="3" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="3" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C183" s="4">
         <v>1632</v>
@@ -5457,15 +5485,15 @@
         <v>19</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="3" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C184" s="4">
         <v>1649</v>
@@ -5474,15 +5502,15 @@
         <v>23</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="3" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C185" s="4">
         <v>1650</v>
@@ -5491,83 +5519,83 @@
         <v>19</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="3" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="3" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="3" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="3" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="3" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>6</v>
@@ -5576,49 +5604,49 @@
         <v>19</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B191" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E191" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="3" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="3" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>51</v>
@@ -5627,32 +5655,32 @@
         <v>23</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="3" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C194" s="4">
         <v>1648</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="3" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>51</v>
@@ -5661,15 +5689,15 @@
         <v>7</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="3" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>18</v>
@@ -5678,66 +5706,66 @@
         <v>31</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="3" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="3" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="3" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C199" s="4">
         <v>1655</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="3" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C200" s="4">
         <v>1665</v>
@@ -5746,15 +5774,15 @@
         <v>23</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="3" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>86</v>
@@ -5763,7 +5791,7 @@
         <v>31</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -5797,176 +5825,176 @@
     <hyperlink ref="A30" r:id="rId27" xr:uid="{02BEF0CC-E5B2-4149-A90C-618525707993}"/>
     <hyperlink ref="A31" r:id="rId28" xr:uid="{083B8D7F-6587-4FB0-9734-1147CCF679AB}"/>
     <hyperlink ref="A36" r:id="rId29" xr:uid="{72C00A77-DE47-4350-ABDF-53A01568DB8C}"/>
-    <hyperlink ref="A38" r:id="rId30" xr:uid="{8D66B7E5-4F81-473E-BAC6-3A133A8BF0A1}"/>
-    <hyperlink ref="A39" r:id="rId31" xr:uid="{5A5B1E69-6425-4E72-AB90-3ACA37CE9C16}"/>
-    <hyperlink ref="A44" r:id="rId32" xr:uid="{D0A7CACE-A9DB-4898-88D4-4742CDAAC4E9}"/>
-    <hyperlink ref="A45" r:id="rId33" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
-    <hyperlink ref="A47" r:id="rId34" xr:uid="{CBE9F467-FD86-4B4E-8B2C-A0DF71E3A3F7}"/>
-    <hyperlink ref="A53" r:id="rId35" xr:uid="{13BB11A7-8B20-43FA-947B-6BB2E06251B8}"/>
-    <hyperlink ref="A54" r:id="rId36" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
-    <hyperlink ref="A55" r:id="rId37" xr:uid="{6036570F-FE5D-4357-98FB-FB0599A85710}"/>
-    <hyperlink ref="A56" r:id="rId38" xr:uid="{C0B1A606-83CA-4C03-83D2-E5F3AF629E02}"/>
-    <hyperlink ref="A57" r:id="rId39" xr:uid="{BA75ACE4-BC4D-49C9-B96A-E5BAE7B87F58}"/>
-    <hyperlink ref="A62" r:id="rId40" xr:uid="{05771483-93F6-4474-B4B2-32295BDD81BC}"/>
-    <hyperlink ref="A63" r:id="rId41" xr:uid="{8D289CD3-5A64-44EF-9B11-57A8D86F52B2}"/>
-    <hyperlink ref="A65" r:id="rId42" xr:uid="{3D29F5EB-74D0-4F8C-873C-CF8696F82267}"/>
-    <hyperlink ref="A66" r:id="rId43" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
-    <hyperlink ref="A68" r:id="rId44" xr:uid="{F12CA809-887E-4065-8BCF-672DEEE659D9}"/>
-    <hyperlink ref="A67" r:id="rId45" xr:uid="{AEA087D1-239A-45A8-B8E2-097CE49E0FA2}"/>
-    <hyperlink ref="A69" r:id="rId46" xr:uid="{E14EDC9B-A66C-4E7F-8F51-FC4AFBB6A5B6}"/>
-    <hyperlink ref="A70" r:id="rId47" xr:uid="{40958558-46AF-4CE2-B242-1552F7202DDD}"/>
-    <hyperlink ref="A72" r:id="rId48" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
-    <hyperlink ref="A71" r:id="rId49" xr:uid="{418161AA-1108-438A-A40F-FEEBCEEA59A7}"/>
-    <hyperlink ref="A73" r:id="rId50" xr:uid="{41401B15-DF59-4BCD-B69D-632B9BC768D9}"/>
-    <hyperlink ref="A49" r:id="rId51" xr:uid="{410386BC-CF6D-4493-8184-0403996A2394}"/>
-    <hyperlink ref="A78" r:id="rId52" xr:uid="{08DD652B-0E47-4AEF-AE3B-843EED3B5D37}"/>
-    <hyperlink ref="A79" r:id="rId53" xr:uid="{9A750BC8-C762-4EDF-93CC-4032B3907B5D}"/>
-    <hyperlink ref="A80" r:id="rId54" xr:uid="{A30474FF-37E1-44F6-A97C-56E497ADD848}"/>
-    <hyperlink ref="A81" r:id="rId55" xr:uid="{F49E3730-867C-4DB9-985B-3F8975A1C09A}"/>
-    <hyperlink ref="A82" r:id="rId56" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
-    <hyperlink ref="A83" r:id="rId57" xr:uid="{08D60088-499F-44EC-99C8-8B92DAABE16C}"/>
-    <hyperlink ref="A84" r:id="rId58" xr:uid="{4CFFE30B-35C8-4D31-9C98-C457D41CA94F}"/>
-    <hyperlink ref="A85" r:id="rId59" xr:uid="{78669114-120E-45A5-BE51-0591720645D5}"/>
-    <hyperlink ref="A90" r:id="rId60" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
-    <hyperlink ref="A91" r:id="rId61" xr:uid="{3411B753-8C89-4443-907B-D69B16883A6C}"/>
-    <hyperlink ref="A93" r:id="rId62" xr:uid="{F985F01B-0DAF-4F36-913E-468DDCCF0CAE}"/>
-    <hyperlink ref="A94" r:id="rId63" xr:uid="{74A7EC9A-D21C-4ECC-949D-FCC02E532D40}"/>
-    <hyperlink ref="A95" r:id="rId64" xr:uid="{4D57808A-EF9C-4AA9-BA44-1512D9D61C6C}"/>
-    <hyperlink ref="A96" r:id="rId65" xr:uid="{15EB3C0C-34FA-4F74-85F1-9B11B80679A1}"/>
-    <hyperlink ref="A98" r:id="rId66" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
-    <hyperlink ref="A99" r:id="rId67" xr:uid="{C494AD1B-E0CA-4F10-84B5-455B27655F83}"/>
-    <hyperlink ref="A100" r:id="rId68" xr:uid="{63F9BC15-635D-4D78-8C4C-A018738BAD9F}"/>
-    <hyperlink ref="A101" r:id="rId69" xr:uid="{7CA35FBE-ACB3-446B-B5C5-CAB02BA12633}"/>
-    <hyperlink ref="A102" r:id="rId70" xr:uid="{7E575697-1670-41B2-BC75-9872FD034F04}"/>
-    <hyperlink ref="A103" r:id="rId71" xr:uid="{AEE3E4E0-6220-49B0-BC8E-1FBD267EA3F0}"/>
-    <hyperlink ref="A104" r:id="rId72" xr:uid="{81770296-8553-4FA3-9953-4DF2380B6A02}"/>
-    <hyperlink ref="A108" r:id="rId73" xr:uid="{E9D4827D-694A-41D2-9587-D78CF34633D6}"/>
-    <hyperlink ref="A110" r:id="rId74" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
-    <hyperlink ref="A111" r:id="rId75" xr:uid="{74963DD6-10C1-4409-BE27-A8DE50EA1647}"/>
-    <hyperlink ref="A112" r:id="rId76" xr:uid="{EDFC0569-A0F2-4981-8582-AC4EA5959270}"/>
-    <hyperlink ref="A115" r:id="rId77" xr:uid="{257F90C9-10B4-47A9-AD8D-DA20E8A51DF1}"/>
-    <hyperlink ref="A116" r:id="rId78" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
-    <hyperlink ref="A117" r:id="rId79" xr:uid="{C170162D-4ABB-46ED-8E71-615D33E57AF5}"/>
-    <hyperlink ref="A118" r:id="rId80" xr:uid="{DC0BB354-B413-4027-8A80-8DCA353DFAAB}"/>
-    <hyperlink ref="A119" r:id="rId81" xr:uid="{F55798B2-2CE8-4A25-815E-90D86322A818}"/>
-    <hyperlink ref="A120" r:id="rId82" xr:uid="{1D5BD7CB-5D55-40D2-8180-0DC2168D4975}"/>
-    <hyperlink ref="A121" r:id="rId83" xr:uid="{F95E6437-8FC2-4E97-BB2A-3A078AEE787C}"/>
-    <hyperlink ref="A122" r:id="rId84" xr:uid="{75E3C088-0BD1-4C69-9E56-F32A00846E6D}"/>
-    <hyperlink ref="A123" r:id="rId85" xr:uid="{D8022634-90FC-40D5-B726-72063260437B}"/>
-    <hyperlink ref="A126" r:id="rId86" xr:uid="{1CA26EC6-4D0B-478A-AB7C-73C492B901B7}"/>
-    <hyperlink ref="A127" r:id="rId87" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
-    <hyperlink ref="A128" r:id="rId88" xr:uid="{FDEB65E8-E3C9-4173-A3A5-699B556167FB}"/>
-    <hyperlink ref="A130" r:id="rId89" xr:uid="{E9FF7778-8F2C-473D-94E5-F797AA522FF4}"/>
-    <hyperlink ref="A131" r:id="rId90" xr:uid="{3BE0486C-7F43-481A-86BD-951F21E28A4C}"/>
-    <hyperlink ref="A132" r:id="rId91" xr:uid="{652988B1-F9B3-4052-9579-F36110769952}"/>
-    <hyperlink ref="A133" r:id="rId92" xr:uid="{9EDF33BD-D7E0-466D-992C-D9A55F7FCB22}"/>
-    <hyperlink ref="A138" r:id="rId93" xr:uid="{C2924DD1-C68C-444A-A0E3-59C8E373AD89}"/>
-    <hyperlink ref="A139" r:id="rId94" xr:uid="{65345FEB-0D91-4161-877B-BA82E8036012}"/>
-    <hyperlink ref="A140" r:id="rId95" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a5/%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg/1920px-%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F15F6E3C-73ED-4C57-8C55-43394AFB2AB2}"/>
-    <hyperlink ref="A141" r:id="rId96" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/La_Famille_heureuse_-_Fr%C3%A8res_Le_Nain_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1941_20.jpg/1280px-La_Famille_heureuse_-_Fr%C3%A8res_Le_Nain_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1941_20.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6FB76A19-EF26-402C-A597-C32FFFCC17C8}"/>
-    <hyperlink ref="A142" r:id="rId97" xr:uid="{75B759AD-4F67-448E-B557-AEA72EFC75A5}"/>
-    <hyperlink ref="A143" r:id="rId98" display="https://upload.wikimedia.org/wikipedia/commons/thumb/d/d2/Firenze_Palazzo_Medici_Riccardi_Interno_Galleria_Soffitto_01.jpg/1280px-Firenze_Palazzo_Medici_Riccardi_Interno_Galleria_Soffitto_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{444BA55E-6438-4CFB-9303-997E4FF662A1}"/>
-    <hyperlink ref="A144" r:id="rId99" xr:uid="{CD9775EB-2654-4C75-971C-D0D4D92F6FFA}"/>
-    <hyperlink ref="A145" r:id="rId100" xr:uid="{7DC05548-CDE3-4C34-86E0-3F27F8867EB5}"/>
-    <hyperlink ref="A148" r:id="rId101" xr:uid="{5EB8FE73-1B38-4EE8-9F5D-408471533360}"/>
-    <hyperlink ref="A149" r:id="rId102" xr:uid="{CBEC5A31-19D9-4333-8626-A71B2B34FD4A}"/>
-    <hyperlink ref="A150" r:id="rId103" xr:uid="{D252EB3F-6F51-4F15-B589-73117EA8D496}"/>
-    <hyperlink ref="A152" r:id="rId104" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/L%27Enl%C3%A8vement_des_Sabines_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7290_%3B_MR_2335.jpg/1280px-L%27Enl%C3%A8vement_des_Sabines_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7290_%3B_MR_2335.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A19357B7-751B-4941-BF08-3534E28A3DF6}"/>
-    <hyperlink ref="A153" r:id="rId105" xr:uid="{B4520E14-8C23-4E76-8E14-1E3E1A19B85A}"/>
-    <hyperlink ref="A154" r:id="rId106" xr:uid="{7D7AB562-1695-44D3-9302-EB9B70CAA7E3}"/>
-    <hyperlink ref="A159" r:id="rId107" xr:uid="{0E932A87-BF91-4D10-9E97-3A276D068D8E}"/>
-    <hyperlink ref="A160" r:id="rId108" xr:uid="{91B168A5-36C9-42BE-9EAB-E976F78F8C7E}"/>
-    <hyperlink ref="A165" r:id="rId109" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
-    <hyperlink ref="A166" r:id="rId110" xr:uid="{D4971BCF-D378-4CCD-80B1-9BCD850F3F00}"/>
-    <hyperlink ref="A167" r:id="rId111" xr:uid="{DEDAFC51-2102-44FE-845E-028590F63B54}"/>
-    <hyperlink ref="A168" r:id="rId112" xr:uid="{D8984F0D-FF89-40E3-AAC2-A91916DF4A3A}"/>
-    <hyperlink ref="A169" r:id="rId113" xr:uid="{148877A9-A1F7-456C-A81C-37672CB63775}"/>
-    <hyperlink ref="A170" r:id="rId114" xr:uid="{336390E0-177C-4949-A051-CB2980A81A7E}"/>
-    <hyperlink ref="A171" r:id="rId115" xr:uid="{DF73CDA4-CEF8-4638-BBC0-C361102BEE04}"/>
-    <hyperlink ref="A172" r:id="rId116" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
-    <hyperlink ref="A173" r:id="rId117" xr:uid="{CBB82F3B-75DE-4B07-BB90-D0FA63126A81}"/>
-    <hyperlink ref="A174" r:id="rId118" xr:uid="{183A9005-718E-4023-B10F-2589B3446C71}"/>
-    <hyperlink ref="A176" r:id="rId119" xr:uid="{118EEA92-6B38-446A-B361-3D3EC12529C2}"/>
-    <hyperlink ref="A177" r:id="rId120" xr:uid="{0E580CC5-5962-4510-B23D-5DFEA390BBDF}"/>
-    <hyperlink ref="A178" r:id="rId121" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
-    <hyperlink ref="A180" r:id="rId122" xr:uid="{66D1456D-CC97-46B1-88D5-50974D80DFD7}"/>
-    <hyperlink ref="A182" r:id="rId123" xr:uid="{DC7B95D3-2C37-40E4-B9E2-5EDC59BFA338}"/>
-    <hyperlink ref="A184" r:id="rId124" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
-    <hyperlink ref="A185" r:id="rId125" xr:uid="{465F45A3-ED2E-4491-BC71-18B9F45F2764}"/>
-    <hyperlink ref="A186" r:id="rId126" xr:uid="{15CF0BF0-994A-4A35-9671-66A095B35CD8}"/>
-    <hyperlink ref="A187" r:id="rId127" xr:uid="{2C4AA8F5-D564-4836-B8DB-CC33D50B9F4C}"/>
-    <hyperlink ref="A188" r:id="rId128" xr:uid="{B9E7ABC5-B793-4A1A-B2B9-8DE84F6E3979}"/>
-    <hyperlink ref="A189" r:id="rId129" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
-    <hyperlink ref="A190" r:id="rId130" xr:uid="{91E75685-F1D8-4C6B-826E-E52CBE4A3B62}"/>
-    <hyperlink ref="A191" r:id="rId131" xr:uid="{9A72E3BA-EF99-42A4-820F-8F04F17B25E5}"/>
-    <hyperlink ref="A192" r:id="rId132" xr:uid="{D2384007-1315-48D6-A7F8-DF584E5A77D6}"/>
-    <hyperlink ref="A197" r:id="rId133" xr:uid="{E24536B2-D94D-4265-92FB-5240863341CF}"/>
-    <hyperlink ref="A183" r:id="rId134" xr:uid="{6DD0EC74-3A66-4DDC-B41B-EFFADB8DFD35}"/>
-    <hyperlink ref="A181" r:id="rId135" xr:uid="{70262521-5303-465D-8B9D-47AE4E0F2D2A}"/>
-    <hyperlink ref="A199" r:id="rId136" xr:uid="{A14CE758-CBAB-4381-8BBB-15948337FAD9}"/>
-    <hyperlink ref="A200" r:id="rId137" xr:uid="{19AA5435-A462-4C11-8578-83786F967017}"/>
-    <hyperlink ref="A201" r:id="rId138" xr:uid="{578B1F4E-5D73-4740-AB71-68CB241AAB4D}"/>
-    <hyperlink ref="A137" r:id="rId139" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C4847D49-3E1B-4371-9BC3-FE1B7A707E3C}"/>
-    <hyperlink ref="A18" r:id="rId140" xr:uid="{945251CC-E6AD-4661-9571-02B7C81C2515}"/>
-    <hyperlink ref="A23" r:id="rId141" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Self-Portrait_as_the_Allegory_of_Painting_%28La_Pittura%29_-_Artemisia_Gentileschi.jpg/960px-Self-Portrait_as_the_Allegory_of_Painting_%28La_Pittura%29_-_Artemisia_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{450912E8-6C20-4F26-8538-8282F02EDAD8}"/>
-    <hyperlink ref="A32" r:id="rId142" xr:uid="{AE09BF63-612F-4029-93B7-0FFC6478EC80}"/>
-    <hyperlink ref="A33" r:id="rId143" xr:uid="{6AD1CDA5-519C-44A7-AB4B-917CF44D65A8}"/>
-    <hyperlink ref="A34" r:id="rId144" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg/960px-Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C2850ED-78A6-4C59-BCF7-C65C3396179F}"/>
-    <hyperlink ref="A35" r:id="rId145" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Bernardo_Strozzi_-_Banquet_at_the_House_of_Simon_%28detail%29_-_WGA21902.jpg/1280px-Bernardo_Strozzi_-_Banquet_at_the_House_of_Simon_%28detail%29_-_WGA21902.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0D8B2BF6-D494-4AD9-80B6-152EDA1BE1C7}"/>
-    <hyperlink ref="A37" r:id="rId146" xr:uid="{1ED06375-42E6-4B79-A731-BA5599550BCB}"/>
-    <hyperlink ref="A40" r:id="rId147" xr:uid="{A4E016D8-8E8B-4277-888D-5A265E16A6CA}"/>
-    <hyperlink ref="A41" r:id="rId148" xr:uid="{413F4FD9-A1E7-43F4-8861-E70D31398644}"/>
-    <hyperlink ref="A42" r:id="rId149" xr:uid="{1009E53D-045D-4F7C-9946-780F3CE87428}"/>
-    <hyperlink ref="A43" r:id="rId150" xr:uid="{7EA200AC-EB1E-4D87-9C6E-2F83CFE486B9}"/>
-    <hyperlink ref="A50" r:id="rId151" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{596E240E-7D53-4A32-9D33-569DA93A4937}"/>
-    <hyperlink ref="A51" r:id="rId152" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg/1280px-Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EBCA20AC-1D38-4222-AB4E-BF68B3C90D3C}"/>
-    <hyperlink ref="A52" r:id="rId153" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg/1280px-Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06244E1C-7B67-4593-BB56-4DEE3423A1BB}"/>
-    <hyperlink ref="A48" r:id="rId154" xr:uid="{92BA32AF-8EC9-4665-A5CC-676E19F93BB1}"/>
-    <hyperlink ref="A46" r:id="rId155" xr:uid="{4C18F5D5-E2D3-4F40-B1CB-F3145EB601CB}"/>
-    <hyperlink ref="A58" r:id="rId156" xr:uid="{EF15C00B-27CF-44B6-8670-F310C1BB94A2}"/>
-    <hyperlink ref="A59" r:id="rId157" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg/1280px-Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57BDA7C2-2097-4285-8501-5706AF6C54CB}"/>
-    <hyperlink ref="A60" r:id="rId158" xr:uid="{96F3CC4F-FB51-40C8-88EA-2F121A7073B1}"/>
-    <hyperlink ref="A61" r:id="rId159" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/Diego_Vel%C3%A1zquez%2C_Portrait_du_pape_Innocent_X%2C_1650%2C_huile_sur_toile%2C_140_%C3%97_120_cm%2C_Rome%2C_Galleria_Doria_Pamphilj_%28inv._237%29.jpg/960px-Diego_Vel%C3%A1zquez%2C_Portrait_du_pape_Innocent_X%2C_1650%2C_huile_sur_toile%2C_140_%C3%97_120_cm%2C_Rome%2C_Galleria_Doria_Pamphilj_%28inv._237%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D87623A4-196A-43C4-9B3B-F42FDF54C823}"/>
-    <hyperlink ref="A64" r:id="rId160" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Domenico_Zampieri_detto_il_Domenichino%2C_Martirio_di_Sant%27Agnese_%281621-1625%29_01.jpg/960px-Domenico_Zampieri_detto_il_Domenichino%2C_Martirio_di_Sant%27Agnese_%281621-1625%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C8B9AC2D-28FD-4FDE-B0A2-F9C7118A3B16}"/>
-    <hyperlink ref="A74" r:id="rId161" xr:uid="{59CEEA06-FA81-4ACE-8191-838FE9BA1BF7}"/>
-    <hyperlink ref="A75" r:id="rId162" xr:uid="{E503067F-9D64-47B3-A4A0-CEB2FFACDB43}"/>
-    <hyperlink ref="A76" r:id="rId163" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5d/Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg/1280px-Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{136AAD34-4CD7-44CB-A4E6-E14EBBA741CE}"/>
-    <hyperlink ref="A77" r:id="rId164" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/78/Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg/1280px-Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{81540B48-5B00-42DD-9EF5-412A04667459}"/>
-    <hyperlink ref="A86" r:id="rId165" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{78A42547-C969-4BBC-BDEF-3E15484B20A9}"/>
-    <hyperlink ref="A87" r:id="rId166" xr:uid="{4B07A603-5273-44D0-B268-760021F85005}"/>
-    <hyperlink ref="A88" r:id="rId167" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg/1280px-Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{10E006E8-2443-4060-9149-E3123D594459}"/>
-    <hyperlink ref="A89" r:id="rId168" xr:uid="{143D80C2-5A99-482A-8173-C372796357EC}"/>
-    <hyperlink ref="A92" r:id="rId169" xr:uid="{302BFBD5-CCBC-44D9-B9D7-53DC45FF1E20}"/>
-    <hyperlink ref="A97" r:id="rId170" xr:uid="{D3C667FB-F60A-40F5-835F-58D418AEEBF0}"/>
-    <hyperlink ref="A105" r:id="rId171" xr:uid="{3028B9B6-1977-4385-A1C6-3FAEC26A346D}"/>
-    <hyperlink ref="A106" r:id="rId172" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg/1280px-Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21DB9486-01EC-4E16-BB8D-ECC0905220A1}"/>
-    <hyperlink ref="A107" r:id="rId173" xr:uid="{61A0E5BE-362D-4770-80F3-3DD9B7FF9694}"/>
-    <hyperlink ref="A109" r:id="rId174" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg/1280px-Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D04BBB03-3D9D-453F-8CD9-245E66F3AD32}"/>
-    <hyperlink ref="A114" r:id="rId175" xr:uid="{2A8DF019-5FC0-46BB-8113-2075AEF0CCED}"/>
-    <hyperlink ref="A113" r:id="rId176" xr:uid="{975264BA-C514-413E-99EA-DD14D58AB288}"/>
-    <hyperlink ref="A124" r:id="rId177" xr:uid="{86A34B4C-C537-4D76-A3EA-321DD50D8CB1}"/>
-    <hyperlink ref="A125" r:id="rId178" xr:uid="{90266FA6-15A2-46AC-8C7B-FCBCC44F01FA}"/>
-    <hyperlink ref="A129" r:id="rId179" xr:uid="{072FFDC6-2747-4BB4-BC37-0C70594E6F4D}"/>
-    <hyperlink ref="A135" r:id="rId180" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg/1920px-Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8BC641E9-9E78-406C-9A28-319E9127B01C}"/>
-    <hyperlink ref="A134" r:id="rId181" xr:uid="{C594B535-2481-40E5-9C7D-7ED4B45F7645}"/>
-    <hyperlink ref="A136" r:id="rId182" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg/1920px-Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DB908BC3-2D48-410E-BEFE-4CCB04FD6CB4}"/>
-    <hyperlink ref="A146" r:id="rId183" xr:uid="{97D61BE1-3395-44FA-A95B-2E1DF5026D4F}"/>
-    <hyperlink ref="A147" r:id="rId184" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg/1280px-Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9552E73C-3D36-4755-AB33-97007CDF5358}"/>
-    <hyperlink ref="A151" r:id="rId185" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06C35A77-A512-486F-96AF-3B12DCA46F8F}"/>
-    <hyperlink ref="A155" r:id="rId186" xr:uid="{42CCE4FE-9359-4905-8FA6-E951073D0EBF}"/>
-    <hyperlink ref="A156" r:id="rId187" xr:uid="{FE18FAC0-7CE1-4001-986D-644A0C94D4EE}"/>
-    <hyperlink ref="A157" r:id="rId188" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg/1280px-Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{717F9D1A-B3AE-4DEC-AE52-C308AAEBC665}"/>
-    <hyperlink ref="A158" r:id="rId189" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg/960px-Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6D642F82-38C2-4D7F-BE14-5866750B76EA}"/>
-    <hyperlink ref="A161" r:id="rId190" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{0DEC1873-EA8A-4837-A600-314F517B37B3}"/>
-    <hyperlink ref="A162" r:id="rId191" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg/1280px-Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{975F1E1C-791A-4C4E-BECF-5701732F6721}"/>
-    <hyperlink ref="A163" r:id="rId192" xr:uid="{AC4529FF-6236-4187-A38E-F96F4FA87989}"/>
-    <hyperlink ref="A164" r:id="rId193" xr:uid="{6F236C01-0CD5-413D-AAF1-D13121442DC4}"/>
-    <hyperlink ref="A175" r:id="rId194" xr:uid="{5FE70125-FB71-4033-91A5-592708E66E93}"/>
-    <hyperlink ref="A179" r:id="rId195" xr:uid="{1C87A638-94E8-40B9-A0F1-C41FE40A0E7B}"/>
-    <hyperlink ref="A193" r:id="rId196" xr:uid="{66F5C3AC-AC1A-4F70-99C0-35B4342E87D9}"/>
-    <hyperlink ref="A194" r:id="rId197" xr:uid="{DBF9950D-25AB-4896-9E4E-6E334EF854EB}"/>
-    <hyperlink ref="A195" r:id="rId198" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg/1280px-Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0E287FD2-4B38-4DE9-96FA-D2FE3EE0C624}"/>
-    <hyperlink ref="A196" r:id="rId199" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png/1280px-Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A8A2E502-8764-42A6-825B-73739FCA7F0A}"/>
+    <hyperlink ref="A44" r:id="rId30" xr:uid="{D0A7CACE-A9DB-4898-88D4-4742CDAAC4E9}"/>
+    <hyperlink ref="A45" r:id="rId31" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
+    <hyperlink ref="A47" r:id="rId32" xr:uid="{CBE9F467-FD86-4B4E-8B2C-A0DF71E3A3F7}"/>
+    <hyperlink ref="A53" r:id="rId33" xr:uid="{13BB11A7-8B20-43FA-947B-6BB2E06251B8}"/>
+    <hyperlink ref="A54" r:id="rId34" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
+    <hyperlink ref="A55" r:id="rId35" xr:uid="{6036570F-FE5D-4357-98FB-FB0599A85710}"/>
+    <hyperlink ref="A56" r:id="rId36" xr:uid="{C0B1A606-83CA-4C03-83D2-E5F3AF629E02}"/>
+    <hyperlink ref="A57" r:id="rId37" xr:uid="{BA75ACE4-BC4D-49C9-B96A-E5BAE7B87F58}"/>
+    <hyperlink ref="A62" r:id="rId38" xr:uid="{05771483-93F6-4474-B4B2-32295BDD81BC}"/>
+    <hyperlink ref="A63" r:id="rId39" xr:uid="{8D289CD3-5A64-44EF-9B11-57A8D86F52B2}"/>
+    <hyperlink ref="A65" r:id="rId40" xr:uid="{3D29F5EB-74D0-4F8C-873C-CF8696F82267}"/>
+    <hyperlink ref="A66" r:id="rId41" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
+    <hyperlink ref="A68" r:id="rId42" xr:uid="{F12CA809-887E-4065-8BCF-672DEEE659D9}"/>
+    <hyperlink ref="A67" r:id="rId43" xr:uid="{AEA087D1-239A-45A8-B8E2-097CE49E0FA2}"/>
+    <hyperlink ref="A69" r:id="rId44" xr:uid="{E14EDC9B-A66C-4E7F-8F51-FC4AFBB6A5B6}"/>
+    <hyperlink ref="A70" r:id="rId45" xr:uid="{40958558-46AF-4CE2-B242-1552F7202DDD}"/>
+    <hyperlink ref="A72" r:id="rId46" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
+    <hyperlink ref="A71" r:id="rId47" xr:uid="{418161AA-1108-438A-A40F-FEEBCEEA59A7}"/>
+    <hyperlink ref="A73" r:id="rId48" xr:uid="{41401B15-DF59-4BCD-B69D-632B9BC768D9}"/>
+    <hyperlink ref="A49" r:id="rId49" xr:uid="{410386BC-CF6D-4493-8184-0403996A2394}"/>
+    <hyperlink ref="A78" r:id="rId50" xr:uid="{08DD652B-0E47-4AEF-AE3B-843EED3B5D37}"/>
+    <hyperlink ref="A79" r:id="rId51" xr:uid="{9A750BC8-C762-4EDF-93CC-4032B3907B5D}"/>
+    <hyperlink ref="A80" r:id="rId52" xr:uid="{A30474FF-37E1-44F6-A97C-56E497ADD848}"/>
+    <hyperlink ref="A81" r:id="rId53" xr:uid="{F49E3730-867C-4DB9-985B-3F8975A1C09A}"/>
+    <hyperlink ref="A82" r:id="rId54" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
+    <hyperlink ref="A83" r:id="rId55" xr:uid="{08D60088-499F-44EC-99C8-8B92DAABE16C}"/>
+    <hyperlink ref="A84" r:id="rId56" xr:uid="{4CFFE30B-35C8-4D31-9C98-C457D41CA94F}"/>
+    <hyperlink ref="A85" r:id="rId57" xr:uid="{78669114-120E-45A5-BE51-0591720645D5}"/>
+    <hyperlink ref="A90" r:id="rId58" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
+    <hyperlink ref="A91" r:id="rId59" xr:uid="{3411B753-8C89-4443-907B-D69B16883A6C}"/>
+    <hyperlink ref="A93" r:id="rId60" xr:uid="{F985F01B-0DAF-4F36-913E-468DDCCF0CAE}"/>
+    <hyperlink ref="A94" r:id="rId61" xr:uid="{74A7EC9A-D21C-4ECC-949D-FCC02E532D40}"/>
+    <hyperlink ref="A95" r:id="rId62" xr:uid="{4D57808A-EF9C-4AA9-BA44-1512D9D61C6C}"/>
+    <hyperlink ref="A96" r:id="rId63" xr:uid="{15EB3C0C-34FA-4F74-85F1-9B11B80679A1}"/>
+    <hyperlink ref="A98" r:id="rId64" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
+    <hyperlink ref="A99" r:id="rId65" xr:uid="{C494AD1B-E0CA-4F10-84B5-455B27655F83}"/>
+    <hyperlink ref="A100" r:id="rId66" xr:uid="{63F9BC15-635D-4D78-8C4C-A018738BAD9F}"/>
+    <hyperlink ref="A101" r:id="rId67" xr:uid="{7CA35FBE-ACB3-446B-B5C5-CAB02BA12633}"/>
+    <hyperlink ref="A102" r:id="rId68" xr:uid="{7E575697-1670-41B2-BC75-9872FD034F04}"/>
+    <hyperlink ref="A103" r:id="rId69" xr:uid="{AEE3E4E0-6220-49B0-BC8E-1FBD267EA3F0}"/>
+    <hyperlink ref="A104" r:id="rId70" xr:uid="{81770296-8553-4FA3-9953-4DF2380B6A02}"/>
+    <hyperlink ref="A108" r:id="rId71" xr:uid="{E9D4827D-694A-41D2-9587-D78CF34633D6}"/>
+    <hyperlink ref="A110" r:id="rId72" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
+    <hyperlink ref="A111" r:id="rId73" xr:uid="{74963DD6-10C1-4409-BE27-A8DE50EA1647}"/>
+    <hyperlink ref="A112" r:id="rId74" xr:uid="{EDFC0569-A0F2-4981-8582-AC4EA5959270}"/>
+    <hyperlink ref="A115" r:id="rId75" xr:uid="{257F90C9-10B4-47A9-AD8D-DA20E8A51DF1}"/>
+    <hyperlink ref="A116" r:id="rId76" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
+    <hyperlink ref="A117" r:id="rId77" xr:uid="{C170162D-4ABB-46ED-8E71-615D33E57AF5}"/>
+    <hyperlink ref="A118" r:id="rId78" xr:uid="{DC0BB354-B413-4027-8A80-8DCA353DFAAB}"/>
+    <hyperlink ref="A119" r:id="rId79" xr:uid="{F55798B2-2CE8-4A25-815E-90D86322A818}"/>
+    <hyperlink ref="A120" r:id="rId80" xr:uid="{1D5BD7CB-5D55-40D2-8180-0DC2168D4975}"/>
+    <hyperlink ref="A121" r:id="rId81" xr:uid="{F95E6437-8FC2-4E97-BB2A-3A078AEE787C}"/>
+    <hyperlink ref="A122" r:id="rId82" xr:uid="{75E3C088-0BD1-4C69-9E56-F32A00846E6D}"/>
+    <hyperlink ref="A123" r:id="rId83" xr:uid="{D8022634-90FC-40D5-B726-72063260437B}"/>
+    <hyperlink ref="A126" r:id="rId84" xr:uid="{1CA26EC6-4D0B-478A-AB7C-73C492B901B7}"/>
+    <hyperlink ref="A127" r:id="rId85" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
+    <hyperlink ref="A128" r:id="rId86" xr:uid="{FDEB65E8-E3C9-4173-A3A5-699B556167FB}"/>
+    <hyperlink ref="A130" r:id="rId87" xr:uid="{E9FF7778-8F2C-473D-94E5-F797AA522FF4}"/>
+    <hyperlink ref="A131" r:id="rId88" xr:uid="{3BE0486C-7F43-481A-86BD-951F21E28A4C}"/>
+    <hyperlink ref="A132" r:id="rId89" xr:uid="{652988B1-F9B3-4052-9579-F36110769952}"/>
+    <hyperlink ref="A133" r:id="rId90" xr:uid="{9EDF33BD-D7E0-466D-992C-D9A55F7FCB22}"/>
+    <hyperlink ref="A138" r:id="rId91" xr:uid="{C2924DD1-C68C-444A-A0E3-59C8E373AD89}"/>
+    <hyperlink ref="A139" r:id="rId92" xr:uid="{65345FEB-0D91-4161-877B-BA82E8036012}"/>
+    <hyperlink ref="A140" r:id="rId93" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a5/%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg/1920px-%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F15F6E3C-73ED-4C57-8C55-43394AFB2AB2}"/>
+    <hyperlink ref="A141" r:id="rId94" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/La_Famille_heureuse_-_Fr%C3%A8res_Le_Nain_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1941_20.jpg/1280px-La_Famille_heureuse_-_Fr%C3%A8res_Le_Nain_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1941_20.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6FB76A19-EF26-402C-A597-C32FFFCC17C8}"/>
+    <hyperlink ref="A142" r:id="rId95" xr:uid="{75B759AD-4F67-448E-B557-AEA72EFC75A5}"/>
+    <hyperlink ref="A143" r:id="rId96" display="https://upload.wikimedia.org/wikipedia/commons/thumb/d/d2/Firenze_Palazzo_Medici_Riccardi_Interno_Galleria_Soffitto_01.jpg/1280px-Firenze_Palazzo_Medici_Riccardi_Interno_Galleria_Soffitto_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{444BA55E-6438-4CFB-9303-997E4FF662A1}"/>
+    <hyperlink ref="A144" r:id="rId97" xr:uid="{CD9775EB-2654-4C75-971C-D0D4D92F6FFA}"/>
+    <hyperlink ref="A145" r:id="rId98" xr:uid="{7DC05548-CDE3-4C34-86E0-3F27F8867EB5}"/>
+    <hyperlink ref="A148" r:id="rId99" xr:uid="{5EB8FE73-1B38-4EE8-9F5D-408471533360}"/>
+    <hyperlink ref="A149" r:id="rId100" xr:uid="{CBEC5A31-19D9-4333-8626-A71B2B34FD4A}"/>
+    <hyperlink ref="A150" r:id="rId101" xr:uid="{D252EB3F-6F51-4F15-B589-73117EA8D496}"/>
+    <hyperlink ref="A152" r:id="rId102" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/L%27Enl%C3%A8vement_des_Sabines_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7290_%3B_MR_2335.jpg/1280px-L%27Enl%C3%A8vement_des_Sabines_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7290_%3B_MR_2335.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A19357B7-751B-4941-BF08-3534E28A3DF6}"/>
+    <hyperlink ref="A153" r:id="rId103" xr:uid="{B4520E14-8C23-4E76-8E14-1E3E1A19B85A}"/>
+    <hyperlink ref="A154" r:id="rId104" xr:uid="{7D7AB562-1695-44D3-9302-EB9B70CAA7E3}"/>
+    <hyperlink ref="A159" r:id="rId105" xr:uid="{0E932A87-BF91-4D10-9E97-3A276D068D8E}"/>
+    <hyperlink ref="A160" r:id="rId106" xr:uid="{91B168A5-36C9-42BE-9EAB-E976F78F8C7E}"/>
+    <hyperlink ref="A165" r:id="rId107" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
+    <hyperlink ref="A166" r:id="rId108" xr:uid="{D4971BCF-D378-4CCD-80B1-9BCD850F3F00}"/>
+    <hyperlink ref="A167" r:id="rId109" xr:uid="{DEDAFC51-2102-44FE-845E-028590F63B54}"/>
+    <hyperlink ref="A168" r:id="rId110" xr:uid="{D8984F0D-FF89-40E3-AAC2-A91916DF4A3A}"/>
+    <hyperlink ref="A169" r:id="rId111" xr:uid="{148877A9-A1F7-456C-A81C-37672CB63775}"/>
+    <hyperlink ref="A170" r:id="rId112" xr:uid="{336390E0-177C-4949-A051-CB2980A81A7E}"/>
+    <hyperlink ref="A171" r:id="rId113" xr:uid="{DF73CDA4-CEF8-4638-BBC0-C361102BEE04}"/>
+    <hyperlink ref="A172" r:id="rId114" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
+    <hyperlink ref="A173" r:id="rId115" xr:uid="{CBB82F3B-75DE-4B07-BB90-D0FA63126A81}"/>
+    <hyperlink ref="A174" r:id="rId116" xr:uid="{183A9005-718E-4023-B10F-2589B3446C71}"/>
+    <hyperlink ref="A176" r:id="rId117" xr:uid="{118EEA92-6B38-446A-B361-3D3EC12529C2}"/>
+    <hyperlink ref="A177" r:id="rId118" xr:uid="{0E580CC5-5962-4510-B23D-5DFEA390BBDF}"/>
+    <hyperlink ref="A178" r:id="rId119" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
+    <hyperlink ref="A180" r:id="rId120" xr:uid="{66D1456D-CC97-46B1-88D5-50974D80DFD7}"/>
+    <hyperlink ref="A182" r:id="rId121" xr:uid="{DC7B95D3-2C37-40E4-B9E2-5EDC59BFA338}"/>
+    <hyperlink ref="A184" r:id="rId122" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
+    <hyperlink ref="A185" r:id="rId123" xr:uid="{465F45A3-ED2E-4491-BC71-18B9F45F2764}"/>
+    <hyperlink ref="A186" r:id="rId124" xr:uid="{15CF0BF0-994A-4A35-9671-66A095B35CD8}"/>
+    <hyperlink ref="A187" r:id="rId125" xr:uid="{2C4AA8F5-D564-4836-B8DB-CC33D50B9F4C}"/>
+    <hyperlink ref="A188" r:id="rId126" xr:uid="{B9E7ABC5-B793-4A1A-B2B9-8DE84F6E3979}"/>
+    <hyperlink ref="A189" r:id="rId127" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
+    <hyperlink ref="A190" r:id="rId128" xr:uid="{91E75685-F1D8-4C6B-826E-E52CBE4A3B62}"/>
+    <hyperlink ref="A191" r:id="rId129" xr:uid="{9A72E3BA-EF99-42A4-820F-8F04F17B25E5}"/>
+    <hyperlink ref="A192" r:id="rId130" xr:uid="{D2384007-1315-48D6-A7F8-DF584E5A77D6}"/>
+    <hyperlink ref="A197" r:id="rId131" xr:uid="{E24536B2-D94D-4265-92FB-5240863341CF}"/>
+    <hyperlink ref="A183" r:id="rId132" xr:uid="{6DD0EC74-3A66-4DDC-B41B-EFFADB8DFD35}"/>
+    <hyperlink ref="A181" r:id="rId133" xr:uid="{70262521-5303-465D-8B9D-47AE4E0F2D2A}"/>
+    <hyperlink ref="A199" r:id="rId134" xr:uid="{A14CE758-CBAB-4381-8BBB-15948337FAD9}"/>
+    <hyperlink ref="A200" r:id="rId135" xr:uid="{19AA5435-A462-4C11-8578-83786F967017}"/>
+    <hyperlink ref="A201" r:id="rId136" xr:uid="{578B1F4E-5D73-4740-AB71-68CB241AAB4D}"/>
+    <hyperlink ref="A137" r:id="rId137" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C4847D49-3E1B-4371-9BC3-FE1B7A707E3C}"/>
+    <hyperlink ref="A18" r:id="rId138" xr:uid="{945251CC-E6AD-4661-9571-02B7C81C2515}"/>
+    <hyperlink ref="A23" r:id="rId139" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Self-Portrait_as_the_Allegory_of_Painting_%28La_Pittura%29_-_Artemisia_Gentileschi.jpg/960px-Self-Portrait_as_the_Allegory_of_Painting_%28La_Pittura%29_-_Artemisia_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{450912E8-6C20-4F26-8538-8282F02EDAD8}"/>
+    <hyperlink ref="A32" r:id="rId140" xr:uid="{AE09BF63-612F-4029-93B7-0FFC6478EC80}"/>
+    <hyperlink ref="A33" r:id="rId141" xr:uid="{6AD1CDA5-519C-44A7-AB4B-917CF44D65A8}"/>
+    <hyperlink ref="A34" r:id="rId142" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg/960px-Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C2850ED-78A6-4C59-BCF7-C65C3396179F}"/>
+    <hyperlink ref="A35" r:id="rId143" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Bernardo_Strozzi_-_Banquet_at_the_House_of_Simon_%28detail%29_-_WGA21902.jpg/1280px-Bernardo_Strozzi_-_Banquet_at_the_House_of_Simon_%28detail%29_-_WGA21902.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0D8B2BF6-D494-4AD9-80B6-152EDA1BE1C7}"/>
+    <hyperlink ref="A37" r:id="rId144" xr:uid="{1ED06375-42E6-4B79-A731-BA5599550BCB}"/>
+    <hyperlink ref="A40" r:id="rId145" xr:uid="{A4E016D8-8E8B-4277-888D-5A265E16A6CA}"/>
+    <hyperlink ref="A41" r:id="rId146" xr:uid="{413F4FD9-A1E7-43F4-8861-E70D31398644}"/>
+    <hyperlink ref="A42" r:id="rId147" xr:uid="{1009E53D-045D-4F7C-9946-780F3CE87428}"/>
+    <hyperlink ref="A43" r:id="rId148" xr:uid="{7EA200AC-EB1E-4D87-9C6E-2F83CFE486B9}"/>
+    <hyperlink ref="A50" r:id="rId149" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{596E240E-7D53-4A32-9D33-569DA93A4937}"/>
+    <hyperlink ref="A51" r:id="rId150" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg/1280px-Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EBCA20AC-1D38-4222-AB4E-BF68B3C90D3C}"/>
+    <hyperlink ref="A52" r:id="rId151" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg/1280px-Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06244E1C-7B67-4593-BB56-4DEE3423A1BB}"/>
+    <hyperlink ref="A48" r:id="rId152" xr:uid="{92BA32AF-8EC9-4665-A5CC-676E19F93BB1}"/>
+    <hyperlink ref="A46" r:id="rId153" xr:uid="{4C18F5D5-E2D3-4F40-B1CB-F3145EB601CB}"/>
+    <hyperlink ref="A58" r:id="rId154" xr:uid="{EF15C00B-27CF-44B6-8670-F310C1BB94A2}"/>
+    <hyperlink ref="A59" r:id="rId155" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg/1280px-Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57BDA7C2-2097-4285-8501-5706AF6C54CB}"/>
+    <hyperlink ref="A60" r:id="rId156" xr:uid="{96F3CC4F-FB51-40C8-88EA-2F121A7073B1}"/>
+    <hyperlink ref="A61" r:id="rId157" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/Diego_Vel%C3%A1zquez%2C_Portrait_du_pape_Innocent_X%2C_1650%2C_huile_sur_toile%2C_140_%C3%97_120_cm%2C_Rome%2C_Galleria_Doria_Pamphilj_%28inv._237%29.jpg/960px-Diego_Vel%C3%A1zquez%2C_Portrait_du_pape_Innocent_X%2C_1650%2C_huile_sur_toile%2C_140_%C3%97_120_cm%2C_Rome%2C_Galleria_Doria_Pamphilj_%28inv._237%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D87623A4-196A-43C4-9B3B-F42FDF54C823}"/>
+    <hyperlink ref="A64" r:id="rId158" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Domenico_Zampieri_detto_il_Domenichino%2C_Martirio_di_Sant%27Agnese_%281621-1625%29_01.jpg/960px-Domenico_Zampieri_detto_il_Domenichino%2C_Martirio_di_Sant%27Agnese_%281621-1625%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C8B9AC2D-28FD-4FDE-B0A2-F9C7118A3B16}"/>
+    <hyperlink ref="A74" r:id="rId159" xr:uid="{59CEEA06-FA81-4ACE-8191-838FE9BA1BF7}"/>
+    <hyperlink ref="A75" r:id="rId160" xr:uid="{E503067F-9D64-47B3-A4A0-CEB2FFACDB43}"/>
+    <hyperlink ref="A76" r:id="rId161" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5d/Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg/1280px-Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{136AAD34-4CD7-44CB-A4E6-E14EBBA741CE}"/>
+    <hyperlink ref="A77" r:id="rId162" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/78/Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg/1280px-Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{81540B48-5B00-42DD-9EF5-412A04667459}"/>
+    <hyperlink ref="A86" r:id="rId163" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{78A42547-C969-4BBC-BDEF-3E15484B20A9}"/>
+    <hyperlink ref="A87" r:id="rId164" xr:uid="{4B07A603-5273-44D0-B268-760021F85005}"/>
+    <hyperlink ref="A88" r:id="rId165" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg/1280px-Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{10E006E8-2443-4060-9149-E3123D594459}"/>
+    <hyperlink ref="A89" r:id="rId166" xr:uid="{143D80C2-5A99-482A-8173-C372796357EC}"/>
+    <hyperlink ref="A92" r:id="rId167" xr:uid="{302BFBD5-CCBC-44D9-B9D7-53DC45FF1E20}"/>
+    <hyperlink ref="A97" r:id="rId168" xr:uid="{D3C667FB-F60A-40F5-835F-58D418AEEBF0}"/>
+    <hyperlink ref="A105" r:id="rId169" xr:uid="{3028B9B6-1977-4385-A1C6-3FAEC26A346D}"/>
+    <hyperlink ref="A106" r:id="rId170" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg/1280px-Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21DB9486-01EC-4E16-BB8D-ECC0905220A1}"/>
+    <hyperlink ref="A107" r:id="rId171" xr:uid="{61A0E5BE-362D-4770-80F3-3DD9B7FF9694}"/>
+    <hyperlink ref="A109" r:id="rId172" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg/1280px-Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D04BBB03-3D9D-453F-8CD9-245E66F3AD32}"/>
+    <hyperlink ref="A114" r:id="rId173" xr:uid="{2A8DF019-5FC0-46BB-8113-2075AEF0CCED}"/>
+    <hyperlink ref="A113" r:id="rId174" xr:uid="{975264BA-C514-413E-99EA-DD14D58AB288}"/>
+    <hyperlink ref="A124" r:id="rId175" xr:uid="{86A34B4C-C537-4D76-A3EA-321DD50D8CB1}"/>
+    <hyperlink ref="A125" r:id="rId176" xr:uid="{90266FA6-15A2-46AC-8C7B-FCBCC44F01FA}"/>
+    <hyperlink ref="A129" r:id="rId177" xr:uid="{072FFDC6-2747-4BB4-BC37-0C70594E6F4D}"/>
+    <hyperlink ref="A135" r:id="rId178" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg/1920px-Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8BC641E9-9E78-406C-9A28-319E9127B01C}"/>
+    <hyperlink ref="A134" r:id="rId179" xr:uid="{C594B535-2481-40E5-9C7D-7ED4B45F7645}"/>
+    <hyperlink ref="A136" r:id="rId180" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg/1920px-Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DB908BC3-2D48-410E-BEFE-4CCB04FD6CB4}"/>
+    <hyperlink ref="A146" r:id="rId181" xr:uid="{97D61BE1-3395-44FA-A95B-2E1DF5026D4F}"/>
+    <hyperlink ref="A147" r:id="rId182" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg/1280px-Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9552E73C-3D36-4755-AB33-97007CDF5358}"/>
+    <hyperlink ref="A151" r:id="rId183" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06C35A77-A512-486F-96AF-3B12DCA46F8F}"/>
+    <hyperlink ref="A155" r:id="rId184" xr:uid="{42CCE4FE-9359-4905-8FA6-E951073D0EBF}"/>
+    <hyperlink ref="A156" r:id="rId185" xr:uid="{FE18FAC0-7CE1-4001-986D-644A0C94D4EE}"/>
+    <hyperlink ref="A157" r:id="rId186" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg/1280px-Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{717F9D1A-B3AE-4DEC-AE52-C308AAEBC665}"/>
+    <hyperlink ref="A158" r:id="rId187" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg/960px-Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6D642F82-38C2-4D7F-BE14-5866750B76EA}"/>
+    <hyperlink ref="A161" r:id="rId188" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{0DEC1873-EA8A-4837-A600-314F517B37B3}"/>
+    <hyperlink ref="A162" r:id="rId189" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg/1280px-Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{975F1E1C-791A-4C4E-BECF-5701732F6721}"/>
+    <hyperlink ref="A163" r:id="rId190" xr:uid="{AC4529FF-6236-4187-A38E-F96F4FA87989}"/>
+    <hyperlink ref="A164" r:id="rId191" xr:uid="{6F236C01-0CD5-413D-AAF1-D13121442DC4}"/>
+    <hyperlink ref="A175" r:id="rId192" xr:uid="{5FE70125-FB71-4033-91A5-592708E66E93}"/>
+    <hyperlink ref="A179" r:id="rId193" xr:uid="{1C87A638-94E8-40B9-A0F1-C41FE40A0E7B}"/>
+    <hyperlink ref="A193" r:id="rId194" xr:uid="{66F5C3AC-AC1A-4F70-99C0-35B4342E87D9}"/>
+    <hyperlink ref="A194" r:id="rId195" xr:uid="{DBF9950D-25AB-4896-9E4E-6E334EF854EB}"/>
+    <hyperlink ref="A195" r:id="rId196" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg/1280px-Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0E287FD2-4B38-4DE9-96FA-D2FE3EE0C624}"/>
+    <hyperlink ref="A196" r:id="rId197" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png/1280px-Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A8A2E502-8764-42A6-825B-73739FCA7F0A}"/>
+    <hyperlink ref="A38" r:id="rId198" xr:uid="{2E22A58C-17B1-4A26-A346-B2B74239110E}"/>
+    <hyperlink ref="A39" r:id="rId199" xr:uid="{313F2464-066F-4F8B-B7A6-8668093EF425}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-17e-niveau3.xlsx
+++ b/quizzes/peinture-17e-niveau3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3A52F6-AAC7-4D91-8A2C-D080DAC1D289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFDC261-C9FA-4C16-A14A-EAB92ED58CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="641">
   <si>
     <t>image</t>
   </si>
@@ -1675,9 +1675,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/f/fd/Vouet%2C_Simon_-_Father_Time_Overcome_by_Love%2C_Hope_and_Beauty_-_1627.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Petit-déjeuner avec un crabe</t>
-  </si>
-  <si>
     <t>Table du petit-déjeuner avec tarte aux mûres</t>
   </si>
   <si>
@@ -1711,12 +1708,6 @@
     <t>Bateaux de pêche sous voile</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/4/4e/Willem_van_de_Velde_II_-_Dutch_men-o%27-war_and_other_shipping_in_a_calm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Navires néerlandais en mer Modifier cela sur Wikidata calme</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/0f/Willem_van_de_Velde_II_-_A_Dutch_Vessel_in_a_Strong_Breeze.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1891,9 +1882,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/26/Stilleven_met_vergulde_bokaal_Rijksmuseum_SK-A-4830.jpeg/1280px-Stilleven_met_vergulde_bokaal_Rijksmuseum_SK-A-4830.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Heda_hermitage.jpg/1280px-Heda_hermitage.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg/1280px-Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1937,6 +1925,24 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c0/Supper_at_Emmaus-Caravaggio_%281601%29.jpg/1280px-Supper_at_Emmaus-Caravaggio_%281601%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/8a/Valentin_de_Boulogne%2C_Judgment_of_Solomon_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Valentin de Boulogne</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/Gian_Lorenzo_Bernini%2C_self-portrait%2C_c1623.jpg/960px-Gian_Lorenzo_Bernini%2C_self-portrait%2C_c1623.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Gian Lorenzo Bernini</t>
+  </si>
+  <si>
+    <t>Galerie Borghese, Rome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autoportrait </t>
   </si>
 </sst>
 </file>
@@ -2603,7 +2609,7 @@
         <v>398</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>40</v>
@@ -2620,7 +2626,7 @@
         <v>399</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>43</v>
@@ -2637,7 +2643,7 @@
         <v>400</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>45</v>
@@ -2654,7 +2660,7 @@
         <v>401</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>48</v>
@@ -2668,10 +2674,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>51</v>
@@ -2688,7 +2694,7 @@
         <v>402</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>53</v>
@@ -2705,7 +2711,7 @@
         <v>403</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>55</v>
@@ -2722,7 +2728,7 @@
         <v>404</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>58</v>
@@ -2753,7 +2759,7 @@
     </row>
     <row r="23" spans="1:5" s="8" customFormat="1">
       <c r="A23" s="6" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>61</v>
@@ -2906,7 +2912,7 @@
     </row>
     <row r="32" spans="1:5" s="8" customFormat="1">
       <c r="A32" s="6" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>88</v>
@@ -2923,7 +2929,7 @@
     </row>
     <row r="33" spans="1:5" s="8" customFormat="1">
       <c r="A33" s="6" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>88</v>
@@ -2940,7 +2946,7 @@
     </row>
     <row r="34" spans="1:5" s="8" customFormat="1">
       <c r="A34" s="6" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>88</v>
@@ -2957,7 +2963,7 @@
     </row>
     <row r="35" spans="1:5" s="8" customFormat="1">
       <c r="A35" s="6" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>88</v>
@@ -2977,7 +2983,7 @@
         <v>420</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C36" s="2">
         <v>1600</v>
@@ -2991,10 +2997,10 @@
     </row>
     <row r="37" spans="1:5" s="8" customFormat="1">
       <c r="A37" s="6" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>97</v>
@@ -3008,10 +3014,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C38" s="4">
         <v>1610</v>
@@ -3020,15 +3026,15 @@
         <v>146</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C39" s="2">
         <v>1601</v>
@@ -3037,7 +3043,7 @@
         <v>31</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="40" spans="1:5" s="8" customFormat="1">
@@ -3059,7 +3065,7 @@
     </row>
     <row r="41" spans="1:5" s="8" customFormat="1">
       <c r="A41" s="6" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>100</v>
@@ -3076,7 +3082,7 @@
     </row>
     <row r="42" spans="1:5" s="8" customFormat="1">
       <c r="A42" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>100</v>
@@ -3093,7 +3099,7 @@
     </row>
     <row r="43" spans="1:5" s="8" customFormat="1">
       <c r="A43" s="6" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>100</v>
@@ -3105,7 +3111,7 @@
         <v>108</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -3113,7 +3119,7 @@
         <v>422</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>109</v>
@@ -3130,7 +3136,7 @@
         <v>423</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>112</v>
@@ -3144,10 +3150,10 @@
     </row>
     <row r="46" spans="1:5" s="12" customFormat="1">
       <c r="A46" s="6" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>114</v>
@@ -3164,7 +3170,7 @@
         <v>424</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C47" s="11" t="s">
         <v>116</v>
@@ -3178,7 +3184,7 @@
     </row>
     <row r="48" spans="1:5" s="8" customFormat="1">
       <c r="A48" s="6" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>118</v>
@@ -3212,7 +3218,7 @@
     </row>
     <row r="50" spans="1:5" s="8" customFormat="1">
       <c r="A50" s="6" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>120</v>
@@ -3229,7 +3235,7 @@
     </row>
     <row r="51" spans="1:5" s="8" customFormat="1">
       <c r="A51" s="6" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>120</v>
@@ -3246,7 +3252,7 @@
     </row>
     <row r="52" spans="1:5" s="8" customFormat="1">
       <c r="A52" s="6" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>120</v>
@@ -3283,7 +3289,7 @@
         <v>426</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C54" s="4">
         <v>1643</v>
@@ -3300,7 +3306,7 @@
         <v>427</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>104</v>
@@ -3317,7 +3323,7 @@
         <v>429</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>132</v>
@@ -3334,7 +3340,7 @@
         <v>430</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>39</v>
@@ -3348,7 +3354,7 @@
     </row>
     <row r="58" spans="1:5" s="8" customFormat="1">
       <c r="A58" s="6" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>136</v>
@@ -3365,7 +3371,7 @@
     </row>
     <row r="59" spans="1:5" s="8" customFormat="1">
       <c r="A59" s="6" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>136</v>
@@ -3382,7 +3388,7 @@
     </row>
     <row r="60" spans="1:5" s="8" customFormat="1">
       <c r="A60" s="6" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>136</v>
@@ -3399,7 +3405,7 @@
     </row>
     <row r="61" spans="1:5" s="8" customFormat="1">
       <c r="A61" s="6" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>136</v>
@@ -3450,7 +3456,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>144</v>
@@ -3487,7 +3493,7 @@
         <v>434</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>155</v>
@@ -3504,7 +3510,7 @@
         <v>436</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>157</v>
@@ -3521,7 +3527,7 @@
         <v>435</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>159</v>
@@ -3538,7 +3544,7 @@
         <v>437</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>28</v>
@@ -3620,7 +3626,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>169</v>
@@ -3637,7 +3643,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="3" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>169</v>
@@ -3654,7 +3660,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>169</v>
@@ -3671,7 +3677,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="3" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>169</v>
@@ -3824,7 +3830,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="3" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>191</v>
@@ -3841,7 +3847,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="3" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>191</v>
@@ -3858,7 +3864,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="3" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>191</v>
@@ -3875,7 +3881,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="3" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>191</v>
@@ -3926,7 +3932,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="3" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>198</v>
@@ -4011,7 +4017,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="3" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>205</v>
@@ -4031,7 +4037,7 @@
         <v>465</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>213</v>
@@ -4048,7 +4054,7 @@
         <v>466</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>215</v>
@@ -4065,7 +4071,7 @@
         <v>467</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>206</v>
@@ -4082,7 +4088,7 @@
         <v>468</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>218</v>
@@ -4147,7 +4153,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="3" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>229</v>
@@ -4164,7 +4170,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="3" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>229</v>
@@ -4181,7 +4187,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="3" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>229</v>
@@ -4215,7 +4221,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>236</v>
@@ -4283,7 +4289,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="3" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>249</v>
@@ -4300,7 +4306,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>249</v>
@@ -4470,7 +4476,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="3" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>270</v>
@@ -4487,7 +4493,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="3" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>270</v>
@@ -4555,7 +4561,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="3" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>275</v>
@@ -4640,7 +4646,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="3" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>287</v>
@@ -4657,7 +4663,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="3" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>287</v>
@@ -4691,7 +4697,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>291</v>
@@ -4844,7 +4850,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="3" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>304</v>
@@ -4861,7 +4867,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="3" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>304</v>
@@ -4929,7 +4935,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="3" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>313</v>
@@ -4997,7 +5003,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="3" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>317</v>
@@ -5014,7 +5020,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="3" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>317</v>
@@ -5031,7 +5037,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="3" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>317</v>
@@ -5048,7 +5054,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="3" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>323</v>
@@ -5099,7 +5105,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="3" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>327</v>
@@ -5116,7 +5122,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="3" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>327</v>
@@ -5133,7 +5139,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="3" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>327</v>
@@ -5150,7 +5156,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="3" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>327</v>
@@ -5337,7 +5343,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="3" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>350</v>
@@ -5405,7 +5411,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="3" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>356</v>
@@ -5439,19 +5445,19 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>356</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>260</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -5473,7 +5479,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>356</v>
@@ -5485,7 +5491,7 @@
         <v>19</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -5643,10 +5649,10 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>51</v>
@@ -5660,16 +5666,16 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="3" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="C194" s="4">
-        <v>1648</v>
+        <v>629</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>260</v>
+        <v>7</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>551</v>
@@ -5677,53 +5683,53 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="3" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>633</v>
+        <v>376</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>552</v>
+        <v>377</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="3" t="s">
-        <v>625</v>
+        <v>552</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>376</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>31</v>
+        <v>553</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="3" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>376</v>
+        <v>628</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>554</v>
+        <v>23</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -5731,67 +5737,67 @@
         <v>560</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>256</v>
+        <v>628</v>
+      </c>
+      <c r="C198" s="4">
+        <v>1655</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>379</v>
+        <v>561</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C199" s="4">
-        <v>1655</v>
+        <v>628</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>171</v>
+        <v>31</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>562</v>
+        <v>380</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="3" t="s">
-        <v>563</v>
+        <v>635</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C200" s="4">
-        <v>1665</v>
+        <v>1625</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>564</v>
+        <v>299</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="3" t="s">
-        <v>565</v>
+        <v>637</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>86</v>
+        <v>638</v>
+      </c>
+      <c r="C201" s="4">
+        <v>1623</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>31</v>
+        <v>639</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>380</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -5926,75 +5932,75 @@
     <hyperlink ref="A190" r:id="rId128" xr:uid="{91E75685-F1D8-4C6B-826E-E52CBE4A3B62}"/>
     <hyperlink ref="A191" r:id="rId129" xr:uid="{9A72E3BA-EF99-42A4-820F-8F04F17B25E5}"/>
     <hyperlink ref="A192" r:id="rId130" xr:uid="{D2384007-1315-48D6-A7F8-DF584E5A77D6}"/>
-    <hyperlink ref="A197" r:id="rId131" xr:uid="{E24536B2-D94D-4265-92FB-5240863341CF}"/>
+    <hyperlink ref="A196" r:id="rId131" xr:uid="{E24536B2-D94D-4265-92FB-5240863341CF}"/>
     <hyperlink ref="A183" r:id="rId132" xr:uid="{6DD0EC74-3A66-4DDC-B41B-EFFADB8DFD35}"/>
     <hyperlink ref="A181" r:id="rId133" xr:uid="{70262521-5303-465D-8B9D-47AE4E0F2D2A}"/>
-    <hyperlink ref="A199" r:id="rId134" xr:uid="{A14CE758-CBAB-4381-8BBB-15948337FAD9}"/>
-    <hyperlink ref="A200" r:id="rId135" xr:uid="{19AA5435-A462-4C11-8578-83786F967017}"/>
-    <hyperlink ref="A201" r:id="rId136" xr:uid="{578B1F4E-5D73-4740-AB71-68CB241AAB4D}"/>
-    <hyperlink ref="A137" r:id="rId137" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C4847D49-3E1B-4371-9BC3-FE1B7A707E3C}"/>
-    <hyperlink ref="A18" r:id="rId138" xr:uid="{945251CC-E6AD-4661-9571-02B7C81C2515}"/>
-    <hyperlink ref="A23" r:id="rId139" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Self-Portrait_as_the_Allegory_of_Painting_%28La_Pittura%29_-_Artemisia_Gentileschi.jpg/960px-Self-Portrait_as_the_Allegory_of_Painting_%28La_Pittura%29_-_Artemisia_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{450912E8-6C20-4F26-8538-8282F02EDAD8}"/>
-    <hyperlink ref="A32" r:id="rId140" xr:uid="{AE09BF63-612F-4029-93B7-0FFC6478EC80}"/>
-    <hyperlink ref="A33" r:id="rId141" xr:uid="{6AD1CDA5-519C-44A7-AB4B-917CF44D65A8}"/>
-    <hyperlink ref="A34" r:id="rId142" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg/960px-Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C2850ED-78A6-4C59-BCF7-C65C3396179F}"/>
-    <hyperlink ref="A35" r:id="rId143" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Bernardo_Strozzi_-_Banquet_at_the_House_of_Simon_%28detail%29_-_WGA21902.jpg/1280px-Bernardo_Strozzi_-_Banquet_at_the_House_of_Simon_%28detail%29_-_WGA21902.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0D8B2BF6-D494-4AD9-80B6-152EDA1BE1C7}"/>
-    <hyperlink ref="A37" r:id="rId144" xr:uid="{1ED06375-42E6-4B79-A731-BA5599550BCB}"/>
-    <hyperlink ref="A40" r:id="rId145" xr:uid="{A4E016D8-8E8B-4277-888D-5A265E16A6CA}"/>
-    <hyperlink ref="A41" r:id="rId146" xr:uid="{413F4FD9-A1E7-43F4-8861-E70D31398644}"/>
-    <hyperlink ref="A42" r:id="rId147" xr:uid="{1009E53D-045D-4F7C-9946-780F3CE87428}"/>
-    <hyperlink ref="A43" r:id="rId148" xr:uid="{7EA200AC-EB1E-4D87-9C6E-2F83CFE486B9}"/>
-    <hyperlink ref="A50" r:id="rId149" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{596E240E-7D53-4A32-9D33-569DA93A4937}"/>
-    <hyperlink ref="A51" r:id="rId150" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg/1280px-Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EBCA20AC-1D38-4222-AB4E-BF68B3C90D3C}"/>
-    <hyperlink ref="A52" r:id="rId151" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg/1280px-Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06244E1C-7B67-4593-BB56-4DEE3423A1BB}"/>
-    <hyperlink ref="A48" r:id="rId152" xr:uid="{92BA32AF-8EC9-4665-A5CC-676E19F93BB1}"/>
-    <hyperlink ref="A46" r:id="rId153" xr:uid="{4C18F5D5-E2D3-4F40-B1CB-F3145EB601CB}"/>
-    <hyperlink ref="A58" r:id="rId154" xr:uid="{EF15C00B-27CF-44B6-8670-F310C1BB94A2}"/>
-    <hyperlink ref="A59" r:id="rId155" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg/1280px-Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57BDA7C2-2097-4285-8501-5706AF6C54CB}"/>
-    <hyperlink ref="A60" r:id="rId156" xr:uid="{96F3CC4F-FB51-40C8-88EA-2F121A7073B1}"/>
-    <hyperlink ref="A61" r:id="rId157" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/Diego_Vel%C3%A1zquez%2C_Portrait_du_pape_Innocent_X%2C_1650%2C_huile_sur_toile%2C_140_%C3%97_120_cm%2C_Rome%2C_Galleria_Doria_Pamphilj_%28inv._237%29.jpg/960px-Diego_Vel%C3%A1zquez%2C_Portrait_du_pape_Innocent_X%2C_1650%2C_huile_sur_toile%2C_140_%C3%97_120_cm%2C_Rome%2C_Galleria_Doria_Pamphilj_%28inv._237%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D87623A4-196A-43C4-9B3B-F42FDF54C823}"/>
-    <hyperlink ref="A64" r:id="rId158" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Domenico_Zampieri_detto_il_Domenichino%2C_Martirio_di_Sant%27Agnese_%281621-1625%29_01.jpg/960px-Domenico_Zampieri_detto_il_Domenichino%2C_Martirio_di_Sant%27Agnese_%281621-1625%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C8B9AC2D-28FD-4FDE-B0A2-F9C7118A3B16}"/>
-    <hyperlink ref="A74" r:id="rId159" xr:uid="{59CEEA06-FA81-4ACE-8191-838FE9BA1BF7}"/>
-    <hyperlink ref="A75" r:id="rId160" xr:uid="{E503067F-9D64-47B3-A4A0-CEB2FFACDB43}"/>
-    <hyperlink ref="A76" r:id="rId161" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5d/Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg/1280px-Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{136AAD34-4CD7-44CB-A4E6-E14EBBA741CE}"/>
-    <hyperlink ref="A77" r:id="rId162" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/78/Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg/1280px-Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{81540B48-5B00-42DD-9EF5-412A04667459}"/>
-    <hyperlink ref="A86" r:id="rId163" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{78A42547-C969-4BBC-BDEF-3E15484B20A9}"/>
-    <hyperlink ref="A87" r:id="rId164" xr:uid="{4B07A603-5273-44D0-B268-760021F85005}"/>
-    <hyperlink ref="A88" r:id="rId165" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg/1280px-Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{10E006E8-2443-4060-9149-E3123D594459}"/>
-    <hyperlink ref="A89" r:id="rId166" xr:uid="{143D80C2-5A99-482A-8173-C372796357EC}"/>
-    <hyperlink ref="A92" r:id="rId167" xr:uid="{302BFBD5-CCBC-44D9-B9D7-53DC45FF1E20}"/>
-    <hyperlink ref="A97" r:id="rId168" xr:uid="{D3C667FB-F60A-40F5-835F-58D418AEEBF0}"/>
-    <hyperlink ref="A105" r:id="rId169" xr:uid="{3028B9B6-1977-4385-A1C6-3FAEC26A346D}"/>
-    <hyperlink ref="A106" r:id="rId170" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg/1280px-Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21DB9486-01EC-4E16-BB8D-ECC0905220A1}"/>
-    <hyperlink ref="A107" r:id="rId171" xr:uid="{61A0E5BE-362D-4770-80F3-3DD9B7FF9694}"/>
-    <hyperlink ref="A109" r:id="rId172" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg/1280px-Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D04BBB03-3D9D-453F-8CD9-245E66F3AD32}"/>
-    <hyperlink ref="A114" r:id="rId173" xr:uid="{2A8DF019-5FC0-46BB-8113-2075AEF0CCED}"/>
-    <hyperlink ref="A113" r:id="rId174" xr:uid="{975264BA-C514-413E-99EA-DD14D58AB288}"/>
-    <hyperlink ref="A124" r:id="rId175" xr:uid="{86A34B4C-C537-4D76-A3EA-321DD50D8CB1}"/>
-    <hyperlink ref="A125" r:id="rId176" xr:uid="{90266FA6-15A2-46AC-8C7B-FCBCC44F01FA}"/>
-    <hyperlink ref="A129" r:id="rId177" xr:uid="{072FFDC6-2747-4BB4-BC37-0C70594E6F4D}"/>
-    <hyperlink ref="A135" r:id="rId178" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg/1920px-Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8BC641E9-9E78-406C-9A28-319E9127B01C}"/>
-    <hyperlink ref="A134" r:id="rId179" xr:uid="{C594B535-2481-40E5-9C7D-7ED4B45F7645}"/>
-    <hyperlink ref="A136" r:id="rId180" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg/1920px-Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DB908BC3-2D48-410E-BEFE-4CCB04FD6CB4}"/>
-    <hyperlink ref="A146" r:id="rId181" xr:uid="{97D61BE1-3395-44FA-A95B-2E1DF5026D4F}"/>
-    <hyperlink ref="A147" r:id="rId182" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg/1280px-Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9552E73C-3D36-4755-AB33-97007CDF5358}"/>
-    <hyperlink ref="A151" r:id="rId183" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06C35A77-A512-486F-96AF-3B12DCA46F8F}"/>
-    <hyperlink ref="A155" r:id="rId184" xr:uid="{42CCE4FE-9359-4905-8FA6-E951073D0EBF}"/>
-    <hyperlink ref="A156" r:id="rId185" xr:uid="{FE18FAC0-7CE1-4001-986D-644A0C94D4EE}"/>
-    <hyperlink ref="A157" r:id="rId186" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg/1280px-Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{717F9D1A-B3AE-4DEC-AE52-C308AAEBC665}"/>
-    <hyperlink ref="A158" r:id="rId187" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg/960px-Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6D642F82-38C2-4D7F-BE14-5866750B76EA}"/>
-    <hyperlink ref="A161" r:id="rId188" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{0DEC1873-EA8A-4837-A600-314F517B37B3}"/>
-    <hyperlink ref="A162" r:id="rId189" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg/1280px-Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{975F1E1C-791A-4C4E-BECF-5701732F6721}"/>
-    <hyperlink ref="A163" r:id="rId190" xr:uid="{AC4529FF-6236-4187-A38E-F96F4FA87989}"/>
-    <hyperlink ref="A164" r:id="rId191" xr:uid="{6F236C01-0CD5-413D-AAF1-D13121442DC4}"/>
-    <hyperlink ref="A175" r:id="rId192" xr:uid="{5FE70125-FB71-4033-91A5-592708E66E93}"/>
-    <hyperlink ref="A179" r:id="rId193" xr:uid="{1C87A638-94E8-40B9-A0F1-C41FE40A0E7B}"/>
-    <hyperlink ref="A193" r:id="rId194" xr:uid="{66F5C3AC-AC1A-4F70-99C0-35B4342E87D9}"/>
-    <hyperlink ref="A194" r:id="rId195" xr:uid="{DBF9950D-25AB-4896-9E4E-6E334EF854EB}"/>
-    <hyperlink ref="A195" r:id="rId196" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg/1280px-Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0E287FD2-4B38-4DE9-96FA-D2FE3EE0C624}"/>
-    <hyperlink ref="A196" r:id="rId197" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png/1280px-Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A8A2E502-8764-42A6-825B-73739FCA7F0A}"/>
-    <hyperlink ref="A38" r:id="rId198" xr:uid="{2E22A58C-17B1-4A26-A346-B2B74239110E}"/>
-    <hyperlink ref="A39" r:id="rId199" xr:uid="{313F2464-066F-4F8B-B7A6-8668093EF425}"/>
+    <hyperlink ref="A198" r:id="rId134" xr:uid="{A14CE758-CBAB-4381-8BBB-15948337FAD9}"/>
+    <hyperlink ref="A199" r:id="rId135" xr:uid="{578B1F4E-5D73-4740-AB71-68CB241AAB4D}"/>
+    <hyperlink ref="A137" r:id="rId136" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C4847D49-3E1B-4371-9BC3-FE1B7A707E3C}"/>
+    <hyperlink ref="A18" r:id="rId137" xr:uid="{945251CC-E6AD-4661-9571-02B7C81C2515}"/>
+    <hyperlink ref="A23" r:id="rId138" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Self-Portrait_as_the_Allegory_of_Painting_%28La_Pittura%29_-_Artemisia_Gentileschi.jpg/960px-Self-Portrait_as_the_Allegory_of_Painting_%28La_Pittura%29_-_Artemisia_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{450912E8-6C20-4F26-8538-8282F02EDAD8}"/>
+    <hyperlink ref="A32" r:id="rId139" xr:uid="{AE09BF63-612F-4029-93B7-0FFC6478EC80}"/>
+    <hyperlink ref="A33" r:id="rId140" xr:uid="{6AD1CDA5-519C-44A7-AB4B-917CF44D65A8}"/>
+    <hyperlink ref="A34" r:id="rId141" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg/960px-Bernardo_Strozzi_-_Vanitas_%28Old_Coquette%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C2850ED-78A6-4C59-BCF7-C65C3396179F}"/>
+    <hyperlink ref="A35" r:id="rId142" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Bernardo_Strozzi_-_Banquet_at_the_House_of_Simon_%28detail%29_-_WGA21902.jpg/1280px-Bernardo_Strozzi_-_Banquet_at_the_House_of_Simon_%28detail%29_-_WGA21902.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0D8B2BF6-D494-4AD9-80B6-152EDA1BE1C7}"/>
+    <hyperlink ref="A37" r:id="rId143" xr:uid="{1ED06375-42E6-4B79-A731-BA5599550BCB}"/>
+    <hyperlink ref="A40" r:id="rId144" xr:uid="{A4E016D8-8E8B-4277-888D-5A265E16A6CA}"/>
+    <hyperlink ref="A41" r:id="rId145" xr:uid="{413F4FD9-A1E7-43F4-8861-E70D31398644}"/>
+    <hyperlink ref="A42" r:id="rId146" xr:uid="{1009E53D-045D-4F7C-9946-780F3CE87428}"/>
+    <hyperlink ref="A43" r:id="rId147" xr:uid="{7EA200AC-EB1E-4D87-9C6E-2F83CFE486B9}"/>
+    <hyperlink ref="A50" r:id="rId148" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{596E240E-7D53-4A32-9D33-569DA93A4937}"/>
+    <hyperlink ref="A51" r:id="rId149" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg/1280px-Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EBCA20AC-1D38-4222-AB4E-BF68B3C90D3C}"/>
+    <hyperlink ref="A52" r:id="rId150" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg/1280px-Port_de_mer_au_soleil_couchant_-_Claude_Gell%C3%A9e_dit_Le_Lorrain_-_Mus%C3%A9e_du_Louvre_Peintures_INV_4715_%3B_MR_1740.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06244E1C-7B67-4593-BB56-4DEE3423A1BB}"/>
+    <hyperlink ref="A48" r:id="rId151" xr:uid="{92BA32AF-8EC9-4665-A5CC-676E19F93BB1}"/>
+    <hyperlink ref="A46" r:id="rId152" xr:uid="{4C18F5D5-E2D3-4F40-B1CB-F3145EB601CB}"/>
+    <hyperlink ref="A58" r:id="rId153" xr:uid="{EF15C00B-27CF-44B6-8670-F310C1BB94A2}"/>
+    <hyperlink ref="A59" r:id="rId154" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg/1280px-Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57BDA7C2-2097-4285-8501-5706AF6C54CB}"/>
+    <hyperlink ref="A60" r:id="rId155" xr:uid="{96F3CC4F-FB51-40C8-88EA-2F121A7073B1}"/>
+    <hyperlink ref="A61" r:id="rId156" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/Diego_Vel%C3%A1zquez%2C_Portrait_du_pape_Innocent_X%2C_1650%2C_huile_sur_toile%2C_140_%C3%97_120_cm%2C_Rome%2C_Galleria_Doria_Pamphilj_%28inv._237%29.jpg/960px-Diego_Vel%C3%A1zquez%2C_Portrait_du_pape_Innocent_X%2C_1650%2C_huile_sur_toile%2C_140_%C3%97_120_cm%2C_Rome%2C_Galleria_Doria_Pamphilj_%28inv._237%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D87623A4-196A-43C4-9B3B-F42FDF54C823}"/>
+    <hyperlink ref="A64" r:id="rId157" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Domenico_Zampieri_detto_il_Domenichino%2C_Martirio_di_Sant%27Agnese_%281621-1625%29_01.jpg/960px-Domenico_Zampieri_detto_il_Domenichino%2C_Martirio_di_Sant%27Agnese_%281621-1625%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C8B9AC2D-28FD-4FDE-B0A2-F9C7118A3B16}"/>
+    <hyperlink ref="A74" r:id="rId158" xr:uid="{59CEEA06-FA81-4ACE-8191-838FE9BA1BF7}"/>
+    <hyperlink ref="A75" r:id="rId159" xr:uid="{E503067F-9D64-47B3-A4A0-CEB2FFACDB43}"/>
+    <hyperlink ref="A76" r:id="rId160" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5d/Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg/1280px-Regents_of_the_Old_Men%27s_Alms_House%2C_by_Frans_Hals.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{136AAD34-4CD7-44CB-A4E6-E14EBBA741CE}"/>
+    <hyperlink ref="A77" r:id="rId161" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/78/Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg/1280px-Frans_Hals_-_Portret_van_een_stel_in_een_landschap_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{81540B48-5B00-42DD-9EF5-412A04667459}"/>
+    <hyperlink ref="A86" r:id="rId162" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{78A42547-C969-4BBC-BDEF-3E15484B20A9}"/>
+    <hyperlink ref="A87" r:id="rId163" xr:uid="{4B07A603-5273-44D0-B268-760021F85005}"/>
+    <hyperlink ref="A88" r:id="rId164" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg/1280px-Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{10E006E8-2443-4060-9149-E3123D594459}"/>
+    <hyperlink ref="A89" r:id="rId165" xr:uid="{143D80C2-5A99-482A-8173-C372796357EC}"/>
+    <hyperlink ref="A92" r:id="rId166" xr:uid="{302BFBD5-CCBC-44D9-B9D7-53DC45FF1E20}"/>
+    <hyperlink ref="A97" r:id="rId167" xr:uid="{D3C667FB-F60A-40F5-835F-58D418AEEBF0}"/>
+    <hyperlink ref="A105" r:id="rId168" xr:uid="{3028B9B6-1977-4385-A1C6-3FAEC26A346D}"/>
+    <hyperlink ref="A106" r:id="rId169" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg/1280px-Hendrick_Avercamp_-_A_Scene_on_the_Ice_near_a_Town_-_WGA1075.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21DB9486-01EC-4E16-BB8D-ECC0905220A1}"/>
+    <hyperlink ref="A107" r:id="rId170" xr:uid="{61A0E5BE-362D-4770-80F3-3DD9B7FF9694}"/>
+    <hyperlink ref="A109" r:id="rId171" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg/1280px-Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D04BBB03-3D9D-453F-8CD9-245E66F3AD32}"/>
+    <hyperlink ref="A114" r:id="rId172" xr:uid="{2A8DF019-5FC0-46BB-8113-2075AEF0CCED}"/>
+    <hyperlink ref="A113" r:id="rId173" xr:uid="{975264BA-C514-413E-99EA-DD14D58AB288}"/>
+    <hyperlink ref="A124" r:id="rId174" xr:uid="{86A34B4C-C537-4D76-A3EA-321DD50D8CB1}"/>
+    <hyperlink ref="A125" r:id="rId175" xr:uid="{90266FA6-15A2-46AC-8C7B-FCBCC44F01FA}"/>
+    <hyperlink ref="A129" r:id="rId176" xr:uid="{072FFDC6-2747-4BB4-BC37-0C70594E6F4D}"/>
+    <hyperlink ref="A135" r:id="rId177" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg/1920px-Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8BC641E9-9E78-406C-9A28-319E9127B01C}"/>
+    <hyperlink ref="A134" r:id="rId178" xr:uid="{C594B535-2481-40E5-9C7D-7ED4B45F7645}"/>
+    <hyperlink ref="A136" r:id="rId179" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg/1920px-Judith_Leyster_-_Boy_playing_the_Flute_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DB908BC3-2D48-410E-BEFE-4CCB04FD6CB4}"/>
+    <hyperlink ref="A146" r:id="rId180" xr:uid="{97D61BE1-3395-44FA-A95B-2E1DF5026D4F}"/>
+    <hyperlink ref="A147" r:id="rId181" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg/1280px-Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9552E73C-3D36-4755-AB33-97007CDF5358}"/>
+    <hyperlink ref="A151" r:id="rId182" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06C35A77-A512-486F-96AF-3B12DCA46F8F}"/>
+    <hyperlink ref="A155" r:id="rId183" xr:uid="{42CCE4FE-9359-4905-8FA6-E951073D0EBF}"/>
+    <hyperlink ref="A156" r:id="rId184" xr:uid="{FE18FAC0-7CE1-4001-986D-644A0C94D4EE}"/>
+    <hyperlink ref="A157" r:id="rId185" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg/1280px-Le_repos_pendant_la_fuite_en_%C3%89gypte_par_Orazio_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{717F9D1A-B3AE-4DEC-AE52-C308AAEBC665}"/>
+    <hyperlink ref="A158" r:id="rId186" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg/960px-Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6D642F82-38C2-4D7F-BE14-5866750B76EA}"/>
+    <hyperlink ref="A161" r:id="rId187" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{0DEC1873-EA8A-4837-A600-314F517B37B3}"/>
+    <hyperlink ref="A162" r:id="rId188" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg/1280px-Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{975F1E1C-791A-4C4E-BECF-5701732F6721}"/>
+    <hyperlink ref="A163" r:id="rId189" xr:uid="{AC4529FF-6236-4187-A38E-F96F4FA87989}"/>
+    <hyperlink ref="A164" r:id="rId190" xr:uid="{6F236C01-0CD5-413D-AAF1-D13121442DC4}"/>
+    <hyperlink ref="A175" r:id="rId191" xr:uid="{5FE70125-FB71-4033-91A5-592708E66E93}"/>
+    <hyperlink ref="A179" r:id="rId192" xr:uid="{1C87A638-94E8-40B9-A0F1-C41FE40A0E7B}"/>
+    <hyperlink ref="A193" r:id="rId193" xr:uid="{66F5C3AC-AC1A-4F70-99C0-35B4342E87D9}"/>
+    <hyperlink ref="A194" r:id="rId194" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg/1280px-Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0E287FD2-4B38-4DE9-96FA-D2FE3EE0C624}"/>
+    <hyperlink ref="A195" r:id="rId195" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png/1280px-Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A8A2E502-8764-42A6-825B-73739FCA7F0A}"/>
+    <hyperlink ref="A38" r:id="rId196" xr:uid="{2E22A58C-17B1-4A26-A346-B2B74239110E}"/>
+    <hyperlink ref="A39" r:id="rId197" xr:uid="{313F2464-066F-4F8B-B7A6-8668093EF425}"/>
+    <hyperlink ref="A200" r:id="rId198" xr:uid="{19F9BE74-5375-432D-8E14-11E51B101798}"/>
+    <hyperlink ref="A201" r:id="rId199" xr:uid="{9348A9BB-FDF0-428A-974F-2DF528DEF772}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-17e-niveau3.xlsx
+++ b/quizzes/peinture-17e-niveau3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FED74F7-4E5D-4E78-BDE6-7624A71D6C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{595F9466-9054-4417-B263-C0A16B676397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="835">
   <si>
     <t>image</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/3/3d/Adriaen_Brouwer%2C_Bauernrauferei_beim_Kartenspiel_%28c._1630%E2%80%931640%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>33 × 48 cm</t>
   </si>
   <si>
+    <t>hollandaise (Pays-Bas)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/63/Adriaen_Brower_-_The_Smokers.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -190,6 +196,9 @@
     <t>L'Immaculée Conception</t>
   </si>
   <si>
+    <t>espagnole</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/f/f6/Alonso_Cano_-_St_John_the_Evangelist_-_WGA4001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -229,6 +238,9 @@
     <t>122 × 230 cm</t>
   </si>
   <si>
+    <t>italienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/1/16/Annibale_Carracci_-_Domine_quo_vadis%3F_-_WGA04444.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -292,6 +304,9 @@
     <t>266 × 207 cm</t>
   </si>
   <si>
+    <t>flamande (Belgique)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/98/Anthonis_van_Dyck_-_Equestrian_Portrait_of_Charles_I_-_National_Gallery%2C_London.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -415,6 +430,9 @@
     <t>Encre sur papier</t>
   </si>
   <si>
+    <t>chinoise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/3/31/Zhu_Da_%E6%9C%B1%E8%80%B7_-_Duck_on_a_Branch_-_y1991-62_-_Princeton_University_Art_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -667,6 +685,9 @@
     <t>298 × 453 cm</t>
   </si>
   <si>
+    <t>française</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Charles_Le_Brun_-_Pierre_S%C3%A9guier%2C_chancelier_de_France_%281655-1661%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1468,6 +1489,9 @@
     <t>63 × 31,2 cm</t>
   </si>
   <si>
+    <t>japonaise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg/1280px-Hishikawa_Moronobu_-_Scenes_from_the_Nakamura_Kabuki_Theater_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -2045,6 +2069,9 @@
   </si>
   <si>
     <t>1618-1680</t>
+  </si>
+  <si>
+    <t>allemande</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/b/be/Lely%2C_Sir_Peter_-_Nymphs_by_a_Fountain_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
@@ -2920,7 +2947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="77.85546875" customWidth="1"/>
@@ -2932,7 +2959,7 @@
     <col min="7" max="7" width="29.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="10" customFormat="1" ht="24.95" customHeight="1">
+    <row r="1" spans="1:9" s="10" customFormat="1" ht="24.95" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2957,4999 +2984,5602 @@
       <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="E5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="H5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
+      <c r="C6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="G6" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="6" t="s">
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="G10" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C11" s="7">
         <v>1650</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>71</v>
+      </c>
+      <c r="I14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>81</v>
+      </c>
+      <c r="I16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>87</v>
+      </c>
+      <c r="I17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H18" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>98</v>
+      </c>
+      <c r="I19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>103</v>
+      </c>
+      <c r="I20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>108</v>
+      </c>
+      <c r="I21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="3" customFormat="1">
+      <c r="A23" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" s="3" customFormat="1">
-      <c r="A23" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H23" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="I23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>109</v>
-      </c>
       <c r="G24" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>124</v>
+      </c>
+      <c r="I24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I26" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="C27" s="7">
         <v>1691</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>145</v>
+      </c>
+      <c r="I28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="I29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="C30" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>155</v>
+      </c>
+      <c r="I30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" s="3" customFormat="1">
+        <v>159</v>
+      </c>
+      <c r="I31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="3" customFormat="1">
       <c r="A32" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" s="3" customFormat="1">
+        <v>165</v>
+      </c>
+      <c r="I32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="3" customFormat="1">
       <c r="A33" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" s="3" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="3" customFormat="1">
       <c r="A34" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" s="3" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I34" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="3" customFormat="1">
       <c r="A35" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C36" s="2">
         <v>1600</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" s="3" customFormat="1">
+        <v>182</v>
+      </c>
+      <c r="I36" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="3" customFormat="1">
       <c r="A37" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>186</v>
+      </c>
+      <c r="I37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C38" s="7">
         <v>1610</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>190</v>
+      </c>
+      <c r="I38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C39" s="2">
         <v>1601</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" s="3" customFormat="1">
+        <v>193</v>
+      </c>
+      <c r="I39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="3" customFormat="1">
       <c r="A40" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" s="3" customFormat="1">
+        <v>200</v>
+      </c>
+      <c r="I40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="3" customFormat="1">
       <c r="A41" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="C41" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="I41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="3" customFormat="1">
+      <c r="A42" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" s="3" customFormat="1">
-      <c r="A42" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" s="3" customFormat="1">
+        <v>210</v>
+      </c>
+      <c r="I42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="3" customFormat="1">
       <c r="A43" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>214</v>
+      </c>
+      <c r="I43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>220</v>
+      </c>
+      <c r="I44" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="1" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="I45" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="5" customFormat="1">
+      <c r="A46" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F45" s="6" t="s">
+      <c r="C46" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" s="5" customFormat="1">
-      <c r="A46" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="E46" s="2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="6" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>231</v>
+      </c>
+      <c r="I46" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" s="3" customFormat="1">
+        <v>235</v>
+      </c>
+      <c r="I47" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="3" customFormat="1">
       <c r="A48" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I48" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="1" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C49" s="7">
         <v>1635</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" s="3" customFormat="1">
+        <v>210</v>
+      </c>
+      <c r="I49" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="3" customFormat="1">
       <c r="A50" s="1" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" s="3" customFormat="1">
+        <v>250</v>
+      </c>
+      <c r="I50" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="3" customFormat="1">
       <c r="A51" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E51" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="I51" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="3" customFormat="1">
+      <c r="A52" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="F51" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" s="3" customFormat="1">
-      <c r="A52" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" s="3" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I52" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="3" customFormat="1">
       <c r="A53" s="1" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>261</v>
+      </c>
+      <c r="I53" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="1" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C54" s="7">
         <v>1643</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="1" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I55" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="1" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>272</v>
+      </c>
+      <c r="I56" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" s="3" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I57" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="3" customFormat="1">
       <c r="A58" s="1" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" s="3" customFormat="1">
+        <v>281</v>
+      </c>
+      <c r="I58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="3" customFormat="1">
       <c r="A59" s="1" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E59" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="I59" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="3" customFormat="1">
+      <c r="A60" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="F59" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" s="3" customFormat="1">
-      <c r="A60" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="C60" s="2" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" s="3" customFormat="1">
+        <v>289</v>
+      </c>
+      <c r="I60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="3" customFormat="1">
       <c r="A61" s="1" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>292</v>
+      </c>
+      <c r="I61" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="1" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>298</v>
+      </c>
+      <c r="I62" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="1" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="I63" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="C64" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I64" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="F63" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="1" t="s">
+      <c r="D65" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F65" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>290</v>
-      </c>
       <c r="G65" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I65" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" s="1" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>314</v>
+      </c>
+      <c r="I66" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" s="1" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F67" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="I67" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="G67" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H67" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="C68" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+        <v>323</v>
+      </c>
+      <c r="I68" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I69" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" s="1" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+        <v>329</v>
+      </c>
+      <c r="I70" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" s="1" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
+        <v>333</v>
+      </c>
+      <c r="I71" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="C72" s="2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F72" s="6"/>
       <c r="G72" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <v>337</v>
+      </c>
+      <c r="I72" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" s="1" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+        <v>341</v>
+      </c>
+      <c r="I73" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" s="1" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
+        <v>348</v>
+      </c>
+      <c r="I74" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F75" s="6"/>
       <c r="G75" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
+        <v>353</v>
+      </c>
+      <c r="I75" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F76" s="6"/>
       <c r="G76" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
+        <v>358</v>
+      </c>
+      <c r="I76" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" s="1" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="F77" s="6"/>
       <c r="G77" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
+        <v>362</v>
+      </c>
+      <c r="I77" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" s="1" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I78" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" s="1" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I79" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>357</v>
-      </c>
       <c r="C80" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="F80" s="6"/>
       <c r="G80" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I80" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" s="1" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="F81" s="6"/>
       <c r="G81" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I81" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" s="1" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="F82" s="6"/>
       <c r="G82" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+        <v>380</v>
+      </c>
+      <c r="I82" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E83" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="I83" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="C84" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="G83" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>370</v>
-      </c>
       <c r="D84" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="F84" s="6"/>
       <c r="G84" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+        <v>388</v>
+      </c>
+      <c r="I84" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" s="1" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C85" s="8">
         <v>1662</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="F85" s="6"/>
       <c r="G85" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+        <v>391</v>
+      </c>
+      <c r="I85" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" s="1" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="F86" s="6"/>
       <c r="G86" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+        <v>395</v>
+      </c>
+      <c r="I86" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" s="1" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
+        <v>399</v>
+      </c>
+      <c r="I87" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="C88" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
+        <v>404</v>
+      </c>
+      <c r="I88" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" s="1" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="F89" s="6"/>
       <c r="G89" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
+        <v>408</v>
+      </c>
+      <c r="I89" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" s="1" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="F90" s="6"/>
       <c r="G90" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
+        <v>412</v>
+      </c>
+      <c r="I90" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" s="1" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="F91" s="6"/>
       <c r="G91" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
+        <v>416</v>
+      </c>
+      <c r="I91" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>403</v>
-      </c>
       <c r="C92" s="2" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H92" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I92" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E93" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
+        <v>210</v>
+      </c>
+      <c r="I93" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94" s="1" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="F94" s="6"/>
       <c r="G94" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
+        <v>427</v>
+      </c>
+      <c r="I94" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
       <c r="A95" s="1" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="F95" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="I95" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="G95" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
-      <c r="A96" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>417</v>
-      </c>
       <c r="C96" s="2" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="F96" s="6"/>
       <c r="G96" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I96" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" s="1" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C97" s="7">
         <v>1622</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F97" s="6"/>
       <c r="G97" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I97" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" s="1" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="F98" s="6"/>
       <c r="G98" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
+        <v>444</v>
+      </c>
+      <c r="I98" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" s="1" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="D99" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I99" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>433</v>
-      </c>
       <c r="C100" s="2" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
+        <v>124</v>
+      </c>
+      <c r="I100" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" s="1" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="F101" s="6"/>
       <c r="G101" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I101" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
+        <v>461</v>
+      </c>
+      <c r="I102" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" s="1" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="F103" s="6"/>
       <c r="G103" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
+        <v>465</v>
+      </c>
+      <c r="I103" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" s="1" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F104" s="6"/>
       <c r="G104" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
+        <v>470</v>
+      </c>
+      <c r="I104" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" s="1" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H105" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I105" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E106" s="2" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="F106" s="6"/>
       <c r="G106" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I106" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="C107" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="F107" s="6"/>
       <c r="G107" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I107" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
       <c r="A108" s="1" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
+        <v>488</v>
+      </c>
+      <c r="I108" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
       <c r="A109" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="C109" s="2" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I109" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110" s="1" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="F110" s="6"/>
       <c r="G110" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I110" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111" s="1" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="F111" s="6"/>
       <c r="G111" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I111" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
       <c r="A112" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="F112" s="6"/>
       <c r="G112" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I112" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
       <c r="A113" s="1" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
+        <v>509</v>
+      </c>
+      <c r="I113" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
       <c r="A114" s="1" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H114" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="I114" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>498</v>
-      </c>
       <c r="C115" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H115" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I115" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D116" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E116" s="2" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
+        <v>523</v>
+      </c>
+      <c r="I116" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
       <c r="A117" s="1" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H117" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="I117" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>511</v>
-      </c>
       <c r="C118" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8">
+        <v>530</v>
+      </c>
+      <c r="I118" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
       <c r="A119" s="1" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I119" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120" s="1" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C120" s="2">
         <v>1630</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H120" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I120" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="121" spans="1:8">
-      <c r="A121" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E121" s="2" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
+        <v>543</v>
+      </c>
+      <c r="I121" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
       <c r="A122" s="1" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="F122" s="6"/>
       <c r="G122" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H122" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="I122" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="123" spans="1:8">
-      <c r="A123" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>531</v>
-      </c>
       <c r="C123" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="F123" s="6"/>
       <c r="G123" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
+        <v>550</v>
+      </c>
+      <c r="I123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
       <c r="A124" s="1" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="C124" s="7">
         <v>1651</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I124" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
       <c r="A125" s="1" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="C125" s="7">
         <v>1636</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="F125" s="6"/>
       <c r="G125" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I125" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
       <c r="A126" s="1" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="C126" s="7">
         <v>1650</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="F126" s="6"/>
       <c r="G126" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I126" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
       <c r="A127" s="1" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="F127" s="6"/>
       <c r="G127" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H127" s="6" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8">
+        <v>564</v>
+      </c>
+      <c r="I127" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
       <c r="A128" s="1" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8">
+        <v>568</v>
+      </c>
+      <c r="I128" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
       <c r="A129" s="1" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G129" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8">
+        <v>205</v>
+      </c>
+      <c r="I129" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
       <c r="A130" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>554</v>
-      </c>
       <c r="C130" s="2" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="F130" s="6"/>
       <c r="G130" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8">
+        <v>574</v>
+      </c>
+      <c r="I130" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
       <c r="A131" s="1" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H131" s="6" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8">
+        <v>579</v>
+      </c>
+      <c r="I131" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
       <c r="A132" s="1" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="F132" s="6"/>
       <c r="G132" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
+        <v>583</v>
+      </c>
+      <c r="I132" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
       <c r="A133" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>568</v>
-      </c>
       <c r="C133" s="2" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="F133" s="6"/>
       <c r="G133" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
+        <v>587</v>
+      </c>
+      <c r="I133" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
       <c r="A134" s="1" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8">
+        <v>592</v>
+      </c>
+      <c r="I134" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
       <c r="A135" s="1" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G135" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H135" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
+        <v>210</v>
+      </c>
+      <c r="I135" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
       <c r="A136" s="1" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="F136" s="6"/>
       <c r="G136" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I136" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
       <c r="A137" s="1" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C137" s="7">
         <v>1634</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="G137" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H137" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I137" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
       <c r="A138" s="1" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8">
+        <v>607</v>
+      </c>
+      <c r="I138" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
       <c r="A139" s="1" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F139" s="6"/>
       <c r="G139" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8">
+        <v>610</v>
+      </c>
+      <c r="I139" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
       <c r="A140" s="1" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="C140" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="I140" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="D140" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="G140" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8">
-      <c r="A141" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>596</v>
-      </c>
       <c r="C141" s="2" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="F141" s="6"/>
       <c r="G141" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8">
+        <v>617</v>
+      </c>
+      <c r="I141" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
       <c r="A142" s="1" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="C142" s="7">
         <v>1663</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="F142" s="6"/>
       <c r="G142" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I142" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
       <c r="A143" s="1" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H143" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
+        <v>87</v>
+      </c>
+      <c r="I143" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
       <c r="A144" s="1" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I144" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
       <c r="A145" s="1" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H145" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I145" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
       <c r="A146" s="1" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="F146" s="6"/>
       <c r="G146" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8">
+        <v>637</v>
+      </c>
+      <c r="I146" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
       <c r="A147" s="1" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H147" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I147" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="I148" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H149" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="I149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D150" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="148" spans="1:8">
-      <c r="A148" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="G148" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8">
-      <c r="A149" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="G149" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H149" s="6" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8">
-      <c r="A150" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E150" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F150" s="6" t="s">
         <v>644</v>
       </c>
-      <c r="F150" s="6" t="s">
-        <v>636</v>
-      </c>
       <c r="G150" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
       <c r="A151" s="1" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G151" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H151" s="6" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
+        <v>656</v>
+      </c>
+      <c r="I151" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
       <c r="A152" s="1" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="F152" s="6"/>
       <c r="G152" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8">
+        <v>659</v>
+      </c>
+      <c r="I152" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
       <c r="A153" s="1" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="F153" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="G153" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H153" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="I153" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="G153" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H153" s="6" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8">
-      <c r="A154" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="C154" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8">
+        <v>210</v>
+      </c>
+      <c r="I154" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
       <c r="A155" s="1" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I155" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
       <c r="A156" s="1" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8">
+        <v>673</v>
+      </c>
+      <c r="I156" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
       <c r="A157" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>658</v>
-      </c>
       <c r="C157" s="2" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I157" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
       <c r="A158" s="1" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I158" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
       <c r="A159" s="1" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I159" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
       <c r="A160" s="1" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="C160" s="7">
         <v>1650</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="F160" s="6" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I160" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
       <c r="A161" s="1" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>684</v>
+        <v>693</v>
       </c>
       <c r="F161" s="6"/>
       <c r="G161" s="6" t="s">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="H161" s="6" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8">
+        <v>695</v>
+      </c>
+      <c r="I161" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
       <c r="A162" s="1" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="F162" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="I162" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="G162" s="6" t="s">
-        <v>685</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8">
-      <c r="A163" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>681</v>
-      </c>
       <c r="C163" s="2" t="s">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="F163" s="6"/>
       <c r="G163" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H163" s="6" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8">
+        <v>704</v>
+      </c>
+      <c r="I163" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
       <c r="A164" s="1" t="s">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="F164" s="6"/>
       <c r="G164" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8">
+        <v>707</v>
+      </c>
+      <c r="I164" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
       <c r="A165" s="1" t="s">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="F165" s="6"/>
       <c r="G165" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H165" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I165" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
       <c r="A166" s="1" t="s">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="F166" s="6"/>
       <c r="G166" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8">
+        <v>715</v>
+      </c>
+      <c r="I166" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
       <c r="A167" s="1" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="G167" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H167" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="I167" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B168" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="168" spans="1:8">
-      <c r="A168" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>700</v>
-      </c>
       <c r="C168" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="F168" s="6"/>
       <c r="G168" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I168" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
       <c r="A169" s="1" t="s">
-        <v>712</v>
+        <v>721</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="F169" s="6"/>
       <c r="G169" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H169" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I169" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
       <c r="A170" s="1" t="s">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="F170" s="6"/>
       <c r="G170" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I170" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
       <c r="A171" s="1" t="s">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="G171" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H171" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I171" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
       <c r="A172" s="1" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8">
+        <v>735</v>
+      </c>
+      <c r="I172" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
       <c r="A173" s="1" t="s">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="F173" s="6"/>
       <c r="G173" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H173" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I173" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="A174" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D174" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="174" spans="1:8">
-      <c r="A174" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E174" s="2" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="F174" s="6"/>
       <c r="G174" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8">
+        <v>740</v>
+      </c>
+      <c r="I174" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
       <c r="A175" s="1" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="G175" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8">
+        <v>87</v>
+      </c>
+      <c r="I175" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
       <c r="A176" s="1" t="s">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8">
+        <v>659</v>
+      </c>
+      <c r="I176" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
       <c r="A177" s="1" t="s">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>741</v>
+        <v>750</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="G177" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H177" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8">
+        <v>87</v>
+      </c>
+      <c r="I177" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
       <c r="A178" s="1" t="s">
-        <v>743</v>
+        <v>752</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8">
+        <v>756</v>
+      </c>
+      <c r="I178" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
       <c r="A179" s="1" t="s">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="G179" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H179" s="6" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8">
+        <v>759</v>
+      </c>
+      <c r="I179" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
       <c r="A180" s="1" t="s">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="F180" s="6"/>
       <c r="G180" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8">
+        <v>764</v>
+      </c>
+      <c r="I180" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
       <c r="A181" s="1" t="s">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="F181" s="6"/>
       <c r="G181" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8">
+        <v>768</v>
+      </c>
+      <c r="I181" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
       <c r="A182" s="1" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="F182" s="6"/>
       <c r="G182" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8">
+        <v>771</v>
+      </c>
+      <c r="I182" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
       <c r="A183" s="1" t="s">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="C183" s="7">
         <v>1632</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="F183" s="6"/>
       <c r="G183" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8">
+        <v>774</v>
+      </c>
+      <c r="I183" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
       <c r="A184" s="1" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="C184" s="7">
         <v>1649</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I184" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
       <c r="A185" s="1" t="s">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="C185" s="7">
         <v>1650</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="F185" s="6"/>
       <c r="G185" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H185" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I185" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
       <c r="A186" s="1" t="s">
-        <v>772</v>
+        <v>781</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I186" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
       <c r="A187" s="1" t="s">
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="G187" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8">
+        <v>788</v>
+      </c>
+      <c r="I187" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
       <c r="A188" s="1" t="s">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="F188" s="6"/>
       <c r="G188" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I188" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
       <c r="A189" s="1" t="s">
-        <v>782</v>
+        <v>791</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>785</v>
+        <v>794</v>
       </c>
       <c r="G189" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8">
+        <v>795</v>
+      </c>
+      <c r="I189" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
       <c r="A190" s="1" t="s">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="F190" s="6"/>
       <c r="G190" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8">
+        <v>798</v>
+      </c>
+      <c r="I190" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
       <c r="A191" s="1" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>791</v>
+        <v>800</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>792</v>
+        <v>801</v>
       </c>
       <c r="F191" s="6"/>
       <c r="G191" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I191" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
       <c r="A192" s="1" t="s">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="F192" s="6"/>
       <c r="G192" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H192" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I192" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="A193" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D193" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="193" spans="1:8">
-      <c r="A193" s="1" t="s">
-        <v>796</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E193" s="2" t="s">
-        <v>798</v>
+        <v>807</v>
       </c>
       <c r="F193" s="6"/>
       <c r="G193" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H193" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I193" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
       <c r="A194" s="1" t="s">
-        <v>799</v>
+        <v>808</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>800</v>
+        <v>809</v>
       </c>
       <c r="F194" s="6"/>
       <c r="G194" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8">
+        <v>810</v>
+      </c>
+      <c r="I194" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
       <c r="A195" s="1" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>803</v>
+        <v>812</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>806</v>
+        <v>815</v>
       </c>
       <c r="G195" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H195" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I195" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="F196" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="G196" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H196" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I196" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D197" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="196" spans="1:8">
-      <c r="A196" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="F196" s="6" t="s">
-        <v>806</v>
-      </c>
-      <c r="G196" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H196" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8">
-      <c r="A197" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E197" s="2" t="s">
-        <v>812</v>
+        <v>821</v>
       </c>
       <c r="F197" s="6"/>
       <c r="G197" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H197" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I197" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
       <c r="A198" s="1" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="C198" s="7">
         <v>1655</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I198" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
       <c r="A199" s="1" t="s">
-        <v>816</v>
+        <v>825</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="F199" s="6"/>
       <c r="G199" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H199" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I199" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
       <c r="A200" s="1" t="s">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>819</v>
+        <v>828</v>
       </c>
       <c r="C200" s="7">
         <v>1625</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8">
+        <v>663</v>
+      </c>
+      <c r="I200" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
       <c r="A201" s="1" t="s">
-        <v>820</v>
+        <v>829</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="C201" s="7">
         <v>1623</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>823</v>
+        <v>832</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>824</v>
+        <v>833</v>
       </c>
       <c r="G201" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H201" s="6" t="s">
-        <v>825</v>
+        <v>834</v>
+      </c>
+      <c r="I201" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
